--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6568" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{475D40F1-0C6E-4158-ABD3-C073EBD2B35E}"/>
+  <xr:revisionPtr revIDLastSave="6593" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DC5B5A8-1242-4926-A273-DCE4B3B1E325}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Uke 1-6" sheetId="7" r:id="rId1"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4785" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4792" uniqueCount="359">
   <si>
     <t>Uke 01</t>
   </si>
@@ -947,9 +947,6 @@
     <t>SF EV 4</t>
   </si>
   <si>
-    <t>SE ZV 4</t>
-  </si>
-  <si>
     <t>Uke 38</t>
   </si>
   <si>
@@ -1031,9 +1028,6 @@
     <t>9 SE AFIS gr. Utd</t>
   </si>
   <si>
-    <t>SE EV 1</t>
-  </si>
-  <si>
     <t>Uke 43</t>
   </si>
   <si>
@@ -1146,6 +1140,18 @@
   </si>
   <si>
     <t>9 SF KUT SUR OV</t>
+  </si>
+  <si>
+    <t>SE ZV 4 BH</t>
+  </si>
+  <si>
+    <t>SE ZV 4 MVO</t>
+  </si>
+  <si>
+    <t>SE EV 1 OFF</t>
+  </si>
+  <si>
+    <t>SF BR 4 GG</t>
   </si>
 </sst>
 </file>
@@ -20971,10 +20977,10 @@
       <c r="N4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O4" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="P4" s="21"/>
+      <c r="O4" s="36" t="s">
+        <v>277</v>
+      </c>
+      <c r="P4" s="37"/>
       <c r="Q4" s="50" t="s">
         <v>275</v>
       </c>
@@ -21451,14 +21457,14 @@
       <c r="N14" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="O14" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="P14" s="37"/>
-      <c r="Q14" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="R14" s="37"/>
+      <c r="O14" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="P14" s="41"/>
+      <c r="Q14" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="R14" s="41"/>
       <c r="S14" s="36" t="s">
         <v>277</v>
       </c>
@@ -21580,8 +21586,12 @@
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
+      <c r="Q17" s="36" t="s">
+        <v>358</v>
+      </c>
+      <c r="R17" s="37"/>
       <c r="S17" s="46" t="s">
-        <v>290</v>
+        <v>355</v>
       </c>
       <c r="T17" s="47"/>
     </row>
@@ -21598,7 +21608,7 @@
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
       <c r="S18" s="46" t="s">
-        <v>290</v>
+        <v>356</v>
       </c>
       <c r="T18" s="47"/>
     </row>
@@ -21630,7 +21640,7 @@
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>1</v>
@@ -21663,7 +21673,7 @@
         <v>46283</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>1</v>
@@ -21757,11 +21767,11 @@
       </c>
       <c r="E23" s="21"/>
       <c r="F23" s="24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G23" s="25"/>
       <c r="H23" s="24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I23" s="25"/>
       <c r="J23" s="36" t="s">
@@ -21805,11 +21815,11 @@
       </c>
       <c r="E24" s="29"/>
       <c r="F24" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G24" s="25"/>
       <c r="H24" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I24" s="25"/>
       <c r="J24" s="40" t="s">
@@ -21868,7 +21878,7 @@
         <v>21</v>
       </c>
       <c r="O25" s="26" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P25" s="27"/>
       <c r="Q25" s="34" t="s">
@@ -21993,38 +22003,38 @@
       </c>
       <c r="C28" s="21"/>
       <c r="D28" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E28" s="25"/>
       <c r="F28" s="26" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G28" s="27"/>
       <c r="H28" s="26" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I28" s="27"/>
       <c r="J28" s="26" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="K28" s="27"/>
       <c r="N28" s="6" t="s">
         <v>28</v>
       </c>
       <c r="O28" s="26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P28" s="27"/>
       <c r="Q28" s="26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="R28" s="27"/>
       <c r="S28" s="26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="T28" s="27"/>
       <c r="U28" s="26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="V28" s="27"/>
       <c r="W28" s="20" t="s">
@@ -22097,7 +22107,7 @@
       </c>
       <c r="G30" s="45"/>
       <c r="H30" s="52" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I30" s="53"/>
       <c r="J30" s="44" t="s">
@@ -22112,7 +22122,7 @@
       </c>
       <c r="P30" s="45"/>
       <c r="Q30" s="32" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="R30" s="33"/>
       <c r="S30" s="44" t="s">
@@ -22133,23 +22143,23 @@
         <v>37</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C31" s="25"/>
       <c r="D31" s="24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E31" s="25"/>
       <c r="F31" s="26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G31" s="27"/>
       <c r="H31" s="26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I31" s="27"/>
       <c r="J31" s="26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="K31" s="27"/>
       <c r="L31" s="7"/>
@@ -22158,23 +22168,23 @@
         <v>37</v>
       </c>
       <c r="O31" s="26" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P31" s="27"/>
       <c r="Q31" s="26" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="R31" s="27"/>
       <c r="S31" s="26" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="T31" s="27"/>
       <c r="U31" s="26" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="V31" s="27"/>
       <c r="W31" s="32" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="X31" s="33"/>
     </row>
@@ -22249,7 +22259,7 @@
       </c>
       <c r="I33" s="31"/>
       <c r="J33" s="24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="K33" s="25"/>
       <c r="L33" s="7"/>
@@ -22258,23 +22268,23 @@
         <v>45</v>
       </c>
       <c r="O33" s="34" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P33" s="35"/>
       <c r="Q33" s="34" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="R33" s="35"/>
       <c r="S33" s="34" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="T33" s="35"/>
       <c r="U33" s="34" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="V33" s="35"/>
       <c r="W33" s="34" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="X33" s="35"/>
     </row>
@@ -22283,7 +22293,7 @@
         <v>48</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C34" s="25"/>
       <c r="D34" s="36" t="s">
@@ -22349,7 +22359,7 @@
       </c>
       <c r="I35" s="47"/>
       <c r="J35" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="K35" s="25"/>
       <c r="L35" s="7"/>
@@ -22362,15 +22372,15 @@
       </c>
       <c r="P35" s="37"/>
       <c r="Q35" s="34" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="R35" s="35"/>
       <c r="S35" s="34" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="T35" s="35"/>
       <c r="U35" s="34" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="V35" s="35"/>
       <c r="W35" s="34" t="s">
@@ -22412,7 +22422,7 @@
       </c>
       <c r="P36" s="21"/>
       <c r="Q36" s="32" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="R36" s="33"/>
       <c r="S36" s="34" t="s">
@@ -22424,7 +22434,7 @@
       </c>
       <c r="V36" s="37"/>
       <c r="W36" s="32" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="X36" s="33"/>
     </row>
@@ -22518,7 +22528,7 @@
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>1</v>
@@ -22553,7 +22563,7 @@
       <c r="L40" s="7"/>
       <c r="M40" s="7"/>
       <c r="N40" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>1</v>
@@ -22641,11 +22651,11 @@
         <v>10</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C42" s="25"/>
       <c r="D42" s="24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E42" s="25"/>
       <c r="F42" s="20" t="s">
@@ -22670,7 +22680,7 @@
       </c>
       <c r="P42" s="37"/>
       <c r="Q42" s="36" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R42" s="37"/>
       <c r="S42" s="36" t="s">
@@ -22691,11 +22701,11 @@
         <v>15</v>
       </c>
       <c r="B43" s="26" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C43" s="27"/>
       <c r="D43" s="26" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E43" s="27"/>
       <c r="F43" s="20" t="s">
@@ -22703,11 +22713,11 @@
       </c>
       <c r="G43" s="21"/>
       <c r="H43" s="26" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I43" s="27"/>
       <c r="J43" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="K43" s="25"/>
       <c r="L43" s="7"/>
@@ -22720,7 +22730,7 @@
       </c>
       <c r="P43" s="37"/>
       <c r="Q43" s="36" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="R43" s="37"/>
       <c r="S43" s="36" t="s">
@@ -22728,7 +22738,7 @@
       </c>
       <c r="T43" s="37"/>
       <c r="U43" s="54" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="V43" s="55"/>
       <c r="W43" s="20" t="s">
@@ -22766,19 +22776,19 @@
         <v>21</v>
       </c>
       <c r="O44" s="26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P44" s="27"/>
       <c r="Q44" s="26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="R44" s="27"/>
       <c r="S44" s="22" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="T44" s="23"/>
       <c r="U44" s="54" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="V44" s="55"/>
       <c r="W44" s="36" t="s">
@@ -22855,14 +22865,14 @@
       </c>
       <c r="I46" s="47"/>
       <c r="J46" s="34" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="K46" s="35"/>
       <c r="N46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="O46" s="34" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P46" s="35"/>
       <c r="Q46" s="34" t="s">
@@ -22887,11 +22897,11 @@
         <v>28</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C47" s="27"/>
       <c r="D47" s="26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E47" s="27"/>
       <c r="F47" s="36" t="s">
@@ -22899,22 +22909,22 @@
       </c>
       <c r="G47" s="37"/>
       <c r="H47" s="26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I47" s="27"/>
       <c r="J47" s="24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="K47" s="25"/>
       <c r="N47" s="6" t="s">
         <v>28</v>
       </c>
       <c r="O47" s="26" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P47" s="27"/>
       <c r="Q47" s="26" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="R47" s="27"/>
       <c r="S47" s="34" t="s">
@@ -22962,19 +22972,19 @@
       </c>
       <c r="P48" s="21"/>
       <c r="Q48" s="54" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="R48" s="55"/>
       <c r="S48" s="54" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="T48" s="55"/>
       <c r="U48" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="V48" s="47"/>
       <c r="W48" s="54" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="X48" s="55"/>
     </row>
@@ -22983,15 +22993,15 @@
         <v>35</v>
       </c>
       <c r="B49" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C49" s="25"/>
       <c r="D49" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E49" s="25"/>
       <c r="F49" s="44" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G49" s="45"/>
       <c r="H49" s="46" t="s">
@@ -22999,7 +23009,7 @@
       </c>
       <c r="I49" s="47"/>
       <c r="J49" s="44" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K49" s="45"/>
       <c r="N49" s="6" t="s">
@@ -23058,19 +23068,19 @@
       </c>
       <c r="P50" s="35"/>
       <c r="Q50" s="54" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="R50" s="55"/>
       <c r="S50" s="54" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="T50" s="55"/>
       <c r="U50" s="46" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="V50" s="47"/>
       <c r="W50" s="54" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="X50" s="55"/>
     </row>
@@ -23106,15 +23116,15 @@
       </c>
       <c r="P51" s="45"/>
       <c r="Q51" s="34" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="R51" s="35"/>
       <c r="S51" s="34" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="T51" s="35"/>
       <c r="U51" s="46" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="V51" s="47"/>
       <c r="W51" s="44" t="s">
@@ -23135,38 +23145,38 @@
       </c>
       <c r="E52" s="23"/>
       <c r="F52" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G52" s="25"/>
       <c r="H52" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I52" s="25"/>
       <c r="J52" s="34" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="K52" s="35"/>
       <c r="N52" s="12" t="s">
         <v>45</v>
       </c>
       <c r="O52" s="34" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P52" s="35"/>
       <c r="Q52" s="34" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="R52" s="35"/>
       <c r="S52" s="34" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="T52" s="35"/>
       <c r="U52" s="34" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="V52" s="35"/>
       <c r="W52" s="34" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="X52" s="35"/>
     </row>
@@ -23198,7 +23208,7 @@
         <v>48</v>
       </c>
       <c r="O53" s="34" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P53" s="35"/>
       <c r="Q53" s="34" t="s">
@@ -23231,11 +23241,11 @@
       </c>
       <c r="E54" s="47"/>
       <c r="F54" s="24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G54" s="25"/>
       <c r="H54" s="24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I54" s="25"/>
       <c r="J54" s="46" t="s">
@@ -23339,7 +23349,7 @@
       </c>
       <c r="K56" s="23"/>
       <c r="S56" s="22" t="s">
-        <v>318</v>
+        <v>357</v>
       </c>
       <c r="T56" s="23"/>
     </row>
@@ -23464,8 +23474,9 @@
       <c r="X66" s="5"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="D/sbAv5uAPXBcgTGv2GcdOcmJHp1lnRyUbjcBHiVNmcnSXDKs8qTCxAiCrVywBeN3gEU8QTnMoCm7UvMzGWrUQ==" saltValue="izdUJKiIdN/ZR9tRIXeQhg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
-  <mergeCells count="468">
+  <mergeCells count="469">
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="O8:P8"/>
     <mergeCell ref="S18:T18"/>
     <mergeCell ref="S56:T56"/>
     <mergeCell ref="W54:X54"/>
@@ -23811,7 +23822,6 @@
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="H3:I3"/>
     <mergeCell ref="J3:K3"/>
-    <mergeCell ref="O4:P4"/>
     <mergeCell ref="O7:P7"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="S3:T3"/>
@@ -23840,7 +23850,7 @@
     <mergeCell ref="S6:T6"/>
     <mergeCell ref="O10:P10"/>
     <mergeCell ref="O9:P9"/>
-    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="O4:P4"/>
     <mergeCell ref="S13:T13"/>
     <mergeCell ref="U13:V13"/>
     <mergeCell ref="U30:V30"/>
@@ -23952,7 +23962,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X60"/>
+  <dimension ref="A1:X61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
@@ -23985,7 +23995,7 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -24018,7 +24028,7 @@
         <v>46318</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>1</v>
@@ -24072,7 +24082,7 @@
       </c>
       <c r="I2" s="39"/>
       <c r="J2" s="34" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="K2" s="35"/>
       <c r="N2" s="1" t="s">
@@ -24087,11 +24097,11 @@
       </c>
       <c r="R2" s="39"/>
       <c r="S2" s="38" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="T2" s="39"/>
       <c r="U2" s="38" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="V2" s="39"/>
       <c r="W2" s="38" t="s">
@@ -24135,7 +24145,7 @@
       </c>
       <c r="R3" s="21"/>
       <c r="S3" s="105" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="T3" s="106"/>
       <c r="U3" s="20" t="s">
@@ -24152,11 +24162,11 @@
         <v>15</v>
       </c>
       <c r="B4" s="76" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C4" s="77"/>
       <c r="D4" s="76" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E4" s="77"/>
       <c r="F4" s="20" t="s">
@@ -24164,11 +24174,11 @@
       </c>
       <c r="G4" s="21"/>
       <c r="H4" s="76" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="I4" s="77"/>
       <c r="J4" s="76" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="K4" s="77"/>
       <c r="N4" s="1" t="s">
@@ -24191,7 +24201,7 @@
       </c>
       <c r="V4" s="43"/>
       <c r="W4" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="X4" s="25"/>
     </row>
@@ -24200,11 +24210,11 @@
         <v>21</v>
       </c>
       <c r="B5" s="76" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C5" s="77"/>
       <c r="D5" s="76" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E5" s="77"/>
       <c r="F5" s="36" t="s">
@@ -24223,23 +24233,23 @@
         <v>21</v>
       </c>
       <c r="O5" s="34" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="P5" s="35"/>
       <c r="Q5" s="34" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="R5" s="35"/>
       <c r="S5" s="34" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="T5" s="35"/>
       <c r="U5" s="34" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="V5" s="35"/>
       <c r="W5" s="34" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="X5" s="35"/>
     </row>
@@ -24323,11 +24333,11 @@
       </c>
       <c r="P7" s="33"/>
       <c r="Q7" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="R7" s="25"/>
       <c r="S7" s="105" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="T7" s="106"/>
       <c r="U7" s="20" t="s">
@@ -24356,11 +24366,11 @@
       </c>
       <c r="G8" s="21"/>
       <c r="H8" s="34" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="I8" s="35"/>
       <c r="J8" s="34" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="K8" s="35"/>
       <c r="L8" s="7"/>
@@ -24369,23 +24379,23 @@
         <v>28</v>
       </c>
       <c r="O8" s="34" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P8" s="35"/>
       <c r="Q8" s="34" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="R8" s="35"/>
       <c r="S8" s="34" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="T8" s="35"/>
       <c r="U8" s="34" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="V8" s="35"/>
       <c r="W8" s="34" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="X8" s="35"/>
     </row>
@@ -24394,23 +24404,23 @@
         <v>32</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C9" s="35"/>
       <c r="D9" s="34" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E9" s="35"/>
       <c r="F9" s="34" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="G9" s="35"/>
       <c r="H9" s="34" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I9" s="35"/>
       <c r="J9" s="34" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="K9" s="35"/>
       <c r="L9" s="7"/>
@@ -24419,23 +24429,23 @@
         <v>32</v>
       </c>
       <c r="O9" s="24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P9" s="25"/>
       <c r="Q9" s="24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="R9" s="25"/>
       <c r="S9" s="24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T9" s="25"/>
       <c r="U9" s="24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="V9" s="25"/>
       <c r="W9" s="24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="X9" s="25"/>
     </row>
@@ -24452,7 +24462,7 @@
       </c>
       <c r="E10" s="21"/>
       <c r="F10" s="34" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G10" s="35"/>
       <c r="H10" s="20" t="s">
@@ -24469,7 +24479,7 @@
         <v>35</v>
       </c>
       <c r="O10" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P10" s="25"/>
       <c r="Q10" s="20" t="s">
@@ -24477,7 +24487,7 @@
       </c>
       <c r="R10" s="21"/>
       <c r="S10" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="T10" s="25"/>
       <c r="U10" s="20" t="s">
@@ -24529,7 +24539,7 @@
       </c>
       <c r="T11" s="47"/>
       <c r="U11" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="V11" s="25"/>
       <c r="W11" s="20" t="s">
@@ -24546,7 +24556,7 @@
       </c>
       <c r="C12" s="21"/>
       <c r="D12" s="34" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E12" s="35"/>
       <c r="F12" s="34" t="s">
@@ -24565,7 +24575,7 @@
         <v>40</v>
       </c>
       <c r="O12" s="34" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P12" s="35"/>
       <c r="Q12" s="34" t="s">
@@ -24594,19 +24604,19 @@
       </c>
       <c r="C13" s="35"/>
       <c r="D13" s="44" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E13" s="45"/>
       <c r="F13" s="34" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G13" s="35"/>
       <c r="H13" s="34" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="I13" s="35"/>
       <c r="J13" s="34" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="K13" s="35"/>
       <c r="N13" s="12" t="s">
@@ -24654,14 +24664,14 @@
       </c>
       <c r="I14" s="37"/>
       <c r="J14" s="34" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="K14" s="35"/>
       <c r="N14" s="1" t="s">
         <v>48</v>
       </c>
       <c r="O14" s="34" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P14" s="35"/>
       <c r="Q14" s="34" t="s">
@@ -24686,11 +24696,11 @@
         <v>49</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C15" s="35"/>
       <c r="D15" s="34" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E15" s="35"/>
       <c r="F15" s="36" t="s">
@@ -24721,7 +24731,7 @@
       </c>
       <c r="T15" s="47"/>
       <c r="U15" s="105" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="V15" s="106"/>
       <c r="W15" s="20" t="s">
@@ -24746,11 +24756,11 @@
       </c>
       <c r="G16" s="47"/>
       <c r="H16" s="76" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="I16" s="77"/>
       <c r="J16" s="76" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K16" s="77"/>
       <c r="N16" s="1" t="s">
@@ -24769,7 +24779,7 @@
       </c>
       <c r="T16" s="47"/>
       <c r="U16" s="105" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="V16" s="106"/>
       <c r="W16" s="20" t="s">
@@ -24824,7 +24834,7 @@
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>1</v>
@@ -24857,7 +24867,7 @@
         <v>46325</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>1</v>
@@ -24951,11 +24961,11 @@
       </c>
       <c r="E21" s="21"/>
       <c r="F21" s="78" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G21" s="79"/>
       <c r="H21" s="78" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="I21" s="79"/>
       <c r="J21" s="20" t="s">
@@ -24966,15 +24976,15 @@
         <v>10</v>
       </c>
       <c r="O21" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P21" s="25"/>
       <c r="Q21" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="R21" s="25"/>
       <c r="S21" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="T21" s="25"/>
       <c r="U21" s="20" t="s">
@@ -25014,23 +25024,23 @@
         <v>15</v>
       </c>
       <c r="O22" s="24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P22" s="25"/>
       <c r="Q22" s="24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="R22" s="25"/>
       <c r="S22" s="24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T22" s="25"/>
       <c r="U22" s="24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="V22" s="25"/>
       <c r="W22" s="24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="X22" s="25"/>
     </row>
@@ -25039,7 +25049,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="34" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C23" s="35"/>
       <c r="D23" s="34" t="s">
@@ -25062,7 +25072,7 @@
         <v>21</v>
       </c>
       <c r="O23" s="46" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="P23" s="47"/>
       <c r="Q23" s="34" t="s">
@@ -25074,11 +25084,11 @@
       </c>
       <c r="T23" s="35"/>
       <c r="U23" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="V23" s="25"/>
       <c r="W23" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="X23" s="25"/>
     </row>
@@ -25162,15 +25172,15 @@
       </c>
       <c r="P25" s="47"/>
       <c r="Q25" s="34" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="R25" s="35"/>
       <c r="S25" s="34" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="T25" s="35"/>
       <c r="U25" s="34" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="V25" s="35"/>
       <c r="W25" s="46" t="s">
@@ -25187,11 +25197,11 @@
       </c>
       <c r="C26" s="21"/>
       <c r="D26" s="44" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E26" s="45"/>
       <c r="F26" s="44" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G26" s="45"/>
       <c r="H26" s="20" t="s">
@@ -25199,7 +25209,7 @@
       </c>
       <c r="I26" s="21"/>
       <c r="J26" s="78" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="K26" s="79"/>
       <c r="L26" s="7"/>
@@ -25208,15 +25218,15 @@
         <v>28</v>
       </c>
       <c r="O26" s="105" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P26" s="106"/>
       <c r="Q26" s="105" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="R26" s="106"/>
       <c r="S26" s="105" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="T26" s="106"/>
       <c r="U26" s="46" t="s">
@@ -25224,7 +25234,7 @@
       </c>
       <c r="V26" s="47"/>
       <c r="W26" s="105" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="X26" s="106"/>
     </row>
@@ -25249,7 +25259,7 @@
       </c>
       <c r="I27" s="21"/>
       <c r="J27" s="78" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="K27" s="79"/>
       <c r="L27" s="7"/>
@@ -25257,24 +25267,24 @@
       <c r="N27" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="O27" s="34" t="s">
-        <v>350</v>
-      </c>
-      <c r="P27" s="35"/>
+      <c r="O27" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="P27" s="47"/>
       <c r="Q27" s="34" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="R27" s="35"/>
       <c r="S27" s="34" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="T27" s="35"/>
       <c r="U27" s="34" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="V27" s="35"/>
       <c r="W27" s="34" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="X27" s="35"/>
     </row>
@@ -25291,11 +25301,11 @@
       </c>
       <c r="E28" s="23"/>
       <c r="F28" s="78" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G28" s="79"/>
       <c r="H28" s="78" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="I28" s="79"/>
       <c r="J28" s="20" t="s">
@@ -25333,23 +25343,23 @@
         <v>37</v>
       </c>
       <c r="B29" s="34" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C29" s="35"/>
       <c r="D29" s="34" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E29" s="35"/>
       <c r="F29" s="34" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="G29" s="35"/>
       <c r="H29" s="34" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I29" s="35"/>
       <c r="J29" s="34" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="K29" s="35"/>
       <c r="L29" s="7"/>
@@ -25358,23 +25368,23 @@
         <v>37</v>
       </c>
       <c r="O29" s="34" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="P29" s="35"/>
       <c r="Q29" s="34" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="R29" s="35"/>
       <c r="S29" s="34" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="T29" s="35"/>
       <c r="U29" s="34" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="V29" s="35"/>
       <c r="W29" s="34" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="X29" s="35"/>
     </row>
@@ -25433,23 +25443,23 @@
         <v>45</v>
       </c>
       <c r="B31" s="34" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C31" s="35"/>
       <c r="D31" s="34" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E31" s="35"/>
       <c r="F31" s="34" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G31" s="35"/>
       <c r="H31" s="34" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I31" s="35"/>
       <c r="J31" s="34" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="K31" s="35"/>
       <c r="L31" s="7"/>
@@ -25483,7 +25493,7 @@
         <v>48</v>
       </c>
       <c r="B32" s="34" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C32" s="35"/>
       <c r="D32" s="22" t="s">
@@ -25507,10 +25517,10 @@
       <c r="N32" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="O32" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="P32" s="47"/>
+      <c r="O32" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="P32" s="41"/>
       <c r="Q32" s="34" t="s">
         <v>103</v>
       </c>
@@ -25533,11 +25543,11 @@
         <v>49</v>
       </c>
       <c r="B33" s="34" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C33" s="35"/>
       <c r="D33" s="34" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E33" s="35"/>
       <c r="F33" s="34" t="s">
@@ -25608,15 +25618,15 @@
         <v>50</v>
       </c>
       <c r="O34" s="105" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="P34" s="106"/>
       <c r="Q34" s="105" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="R34" s="106"/>
       <c r="S34" s="105" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="T34" s="106"/>
       <c r="U34" s="20" t="s">
@@ -25624,7 +25634,7 @@
       </c>
       <c r="V34" s="21"/>
       <c r="W34" s="105" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="X34" s="106"/>
     </row>
@@ -25642,168 +25652,141 @@
       <c r="K35" s="9"/>
       <c r="L35" s="7"/>
       <c r="M35" s="7"/>
-      <c r="O35" s="9"/>
-      <c r="P35" s="9"/>
+      <c r="O35" s="34" t="s">
+        <v>348</v>
+      </c>
+      <c r="P35" s="35"/>
       <c r="U35" s="9"/>
       <c r="V35" s="9"/>
       <c r="W35" s="9"/>
       <c r="X35" s="9"/>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A36" s="7"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
-      <c r="I36" s="7"/>
-      <c r="J36" s="7"/>
-      <c r="K36" s="7"/>
+    <row r="36" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="5"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="9"/>
+      <c r="K36" s="9"/>
       <c r="L36" s="7"/>
       <c r="M36" s="7"/>
+      <c r="O36" s="9"/>
+      <c r="P36" s="9"/>
+      <c r="U36" s="9"/>
+      <c r="V36" s="9"/>
+      <c r="W36" s="9"/>
+      <c r="X36" s="9"/>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A37" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C37" s="3">
-        <v>46328</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E37" s="3">
-        <v>46329</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G37" s="3">
-        <v>46330</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I37" s="3">
-        <v>46331</v>
-      </c>
-      <c r="J37" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="K37" s="3">
-        <v>46332</v>
-      </c>
+      <c r="A37" s="7"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="7"/>
+      <c r="J37" s="7"/>
+      <c r="K37" s="7"/>
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
-      <c r="N37" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="O37" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P37" s="3">
-        <v>46349</v>
-      </c>
-      <c r="Q37" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="R37" s="3">
-        <v>46350</v>
-      </c>
-      <c r="S37" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T37" s="3">
-        <v>46351</v>
-      </c>
-      <c r="U37" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="V37" s="3">
-        <v>46352</v>
-      </c>
-      <c r="W37" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="X37" s="3">
-        <v>46353</v>
-      </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B38" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="C38" s="39"/>
-      <c r="D38" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="E38" s="39"/>
-      <c r="F38" s="38" t="s">
-        <v>335</v>
-      </c>
-      <c r="G38" s="39"/>
-      <c r="H38" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I38" s="39"/>
-      <c r="J38" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="K38" s="35"/>
+        <v>331</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C38" s="3">
+        <v>46328</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E38" s="3">
+        <v>46329</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G38" s="3">
+        <v>46330</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I38" s="3">
+        <v>46331</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K38" s="3">
+        <v>46332</v>
+      </c>
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
       <c r="N38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="O38" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="P38" s="39"/>
-      <c r="Q38" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="R38" s="39"/>
-      <c r="S38" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="T38" s="39"/>
-      <c r="U38" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="V38" s="39"/>
-      <c r="W38" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="X38" s="39"/>
+        <v>332</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P38" s="3">
+        <v>46349</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="R38" s="3">
+        <v>46350</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T38" s="3">
+        <v>46351</v>
+      </c>
+      <c r="U38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="V38" s="3">
+        <v>46352</v>
+      </c>
+      <c r="W38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="X38" s="3">
+        <v>46353</v>
+      </c>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B39" s="34" t="s">
-        <v>336</v>
-      </c>
-      <c r="C39" s="35"/>
-      <c r="D39" s="34" t="s">
-        <v>336</v>
-      </c>
-      <c r="E39" s="35"/>
-      <c r="F39" s="34" t="s">
-        <v>336</v>
-      </c>
-      <c r="G39" s="35"/>
-      <c r="H39" s="34" t="s">
-        <v>336</v>
-      </c>
-      <c r="I39" s="35"/>
+        <v>7</v>
+      </c>
+      <c r="B39" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" s="39"/>
+      <c r="D39" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" s="39"/>
+      <c r="F39" s="38" t="s">
+        <v>333</v>
+      </c>
+      <c r="G39" s="39"/>
+      <c r="H39" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="I39" s="39"/>
       <c r="J39" s="34" t="s">
         <v>92</v>
       </c>
@@ -25811,118 +25794,120 @@
       <c r="L39" s="7"/>
       <c r="M39" s="7"/>
       <c r="N39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O39" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="P39" s="39"/>
+      <c r="Q39" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="R39" s="39"/>
+      <c r="S39" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="T39" s="39"/>
+      <c r="U39" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="V39" s="39"/>
+      <c r="W39" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="X39" s="39"/>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="O39" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="P39" s="21"/>
-      <c r="Q39" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="R39" s="21"/>
-      <c r="S39" s="98" t="s">
+      <c r="B40" s="34" t="s">
+        <v>334</v>
+      </c>
+      <c r="C40" s="35"/>
+      <c r="D40" s="34" t="s">
+        <v>334</v>
+      </c>
+      <c r="E40" s="35"/>
+      <c r="F40" s="34" t="s">
+        <v>334</v>
+      </c>
+      <c r="G40" s="35"/>
+      <c r="H40" s="34" t="s">
+        <v>334</v>
+      </c>
+      <c r="I40" s="35"/>
+      <c r="J40" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="K40" s="35"/>
+      <c r="L40" s="7"/>
+      <c r="M40" s="7"/>
+      <c r="N40" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O40" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="P40" s="21"/>
+      <c r="Q40" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="R40" s="21"/>
+      <c r="S40" s="98" t="s">
         <v>219</v>
       </c>
-      <c r="T39" s="99"/>
-      <c r="U39" s="98" t="s">
+      <c r="T40" s="99"/>
+      <c r="U40" s="98" t="s">
         <v>220</v>
       </c>
-      <c r="V39" s="99"/>
-      <c r="W39" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="X39" s="21"/>
-    </row>
-    <row r="40" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="1" t="s">
+      <c r="V40" s="99"/>
+      <c r="W40" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="X40" s="21"/>
+    </row>
+    <row r="41" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B40" s="34" t="s">
-        <v>312</v>
-      </c>
-      <c r="C40" s="35"/>
-      <c r="D40" s="42" t="s">
+      <c r="B41" s="34" t="s">
+        <v>311</v>
+      </c>
+      <c r="C41" s="35"/>
+      <c r="D41" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="E40" s="43"/>
-      <c r="F40" s="46" t="s">
+      <c r="E41" s="43"/>
+      <c r="F41" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="G40" s="47"/>
-      <c r="H40" s="46" t="s">
+      <c r="G41" s="47"/>
+      <c r="H41" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="I40" s="47"/>
-      <c r="J40" s="46" t="s">
+      <c r="I41" s="47"/>
+      <c r="J41" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="K40" s="47"/>
-      <c r="N40" s="1" t="s">
+      <c r="K41" s="47"/>
+      <c r="N41" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O40" s="46" t="s">
+      <c r="O41" s="46" t="s">
         <v>31</v>
-      </c>
-      <c r="P40" s="47"/>
-      <c r="Q40" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="R40" s="47"/>
-      <c r="S40" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="T40" s="21"/>
-      <c r="U40" s="98" t="s">
-        <v>219</v>
-      </c>
-      <c r="V40" s="99"/>
-      <c r="W40" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="X40" s="47"/>
-    </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A41" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B41" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="C41" s="47"/>
-      <c r="D41" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="E41" s="35"/>
-      <c r="F41" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="G41" s="35"/>
-      <c r="H41" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="I41" s="35"/>
-      <c r="J41" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="K41" s="35"/>
-      <c r="N41" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O41" s="46" t="s">
-        <v>44</v>
       </c>
       <c r="P41" s="47"/>
       <c r="Q41" s="46" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="R41" s="47"/>
-      <c r="S41" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="T41" s="25"/>
+      <c r="S41" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="T41" s="21"/>
       <c r="U41" s="98" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="V41" s="99"/>
       <c r="W41" s="46" t="s">
@@ -25932,126 +25917,126 @@
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B42" s="46" t="s">
+        <v>44</v>
+      </c>
+      <c r="C42" s="47"/>
+      <c r="D42" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="E42" s="35"/>
+      <c r="F42" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="G42" s="35"/>
+      <c r="H42" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="I42" s="35"/>
+      <c r="J42" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="K42" s="35"/>
+      <c r="N42" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O42" s="46" t="s">
+        <v>44</v>
+      </c>
+      <c r="P42" s="47"/>
+      <c r="Q42" s="46" t="s">
+        <v>44</v>
+      </c>
+      <c r="R42" s="47"/>
+      <c r="S42" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="T42" s="25"/>
+      <c r="U42" s="98" t="s">
+        <v>215</v>
+      </c>
+      <c r="V42" s="99"/>
+      <c r="W42" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="X42" s="47"/>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B42" s="44" t="s">
+      <c r="B43" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="C42" s="45"/>
-      <c r="D42" s="44" t="s">
+      <c r="C43" s="45"/>
+      <c r="D43" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="E42" s="45"/>
-      <c r="F42" s="44" t="s">
+      <c r="E43" s="45"/>
+      <c r="F43" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="G42" s="45"/>
-      <c r="H42" s="44" t="s">
+      <c r="G43" s="45"/>
+      <c r="H43" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="I42" s="45"/>
-      <c r="J42" s="44" t="s">
+      <c r="I43" s="45"/>
+      <c r="J43" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="K42" s="45"/>
-      <c r="N42" s="1" t="s">
+      <c r="K43" s="45"/>
+      <c r="N43" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="O42" s="44" t="s">
+      <c r="O43" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="P42" s="45"/>
-      <c r="Q42" s="44" t="s">
+      <c r="P43" s="45"/>
+      <c r="Q43" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="R42" s="45"/>
-      <c r="S42" s="44" t="s">
+      <c r="R43" s="45"/>
+      <c r="S43" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="T42" s="45"/>
-      <c r="U42" s="44" t="s">
+      <c r="T43" s="45"/>
+      <c r="U43" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="V42" s="45"/>
-      <c r="W42" s="44" t="s">
+      <c r="V43" s="45"/>
+      <c r="W43" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="X42" s="45"/>
-    </row>
-    <row r="43" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="6" t="s">
+      <c r="X43" s="45"/>
+    </row>
+    <row r="44" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B43" s="34" t="s">
-        <v>312</v>
-      </c>
-      <c r="C43" s="35"/>
-      <c r="D43" s="50" t="s">
+      <c r="B44" s="34" t="s">
+        <v>311</v>
+      </c>
+      <c r="C44" s="35"/>
+      <c r="D44" s="50" t="s">
         <v>275</v>
       </c>
-      <c r="E43" s="51"/>
-      <c r="F43" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="G43" s="21"/>
-      <c r="H43" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="I43" s="21"/>
-      <c r="J43" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="K43" s="35"/>
-      <c r="N43" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O43" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="P43" s="25"/>
-      <c r="Q43" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="R43" s="25"/>
-      <c r="S43" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="T43" s="25"/>
-      <c r="U43" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="V43" s="25"/>
-      <c r="W43" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="X43" s="25"/>
-    </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A44" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B44" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="47"/>
-      <c r="D44" s="34" t="s">
-        <v>337</v>
-      </c>
-      <c r="E44" s="35"/>
+      <c r="E44" s="51"/>
       <c r="F44" s="20" t="s">
         <v>9</v>
       </c>
       <c r="G44" s="21"/>
-      <c r="H44" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="I44" s="47"/>
+      <c r="H44" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="I44" s="21"/>
       <c r="J44" s="34" t="s">
         <v>92</v>
       </c>
       <c r="K44" s="35"/>
       <c r="N44" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O44" s="24" t="s">
         <v>14</v>
@@ -26061,466 +26046,509 @@
         <v>14</v>
       </c>
       <c r="R44" s="25"/>
-      <c r="S44" s="98" t="s">
-        <v>215</v>
-      </c>
-      <c r="T44" s="99"/>
-      <c r="U44" s="98" t="s">
-        <v>217</v>
-      </c>
-      <c r="V44" s="99"/>
+      <c r="S44" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="T44" s="25"/>
+      <c r="U44" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="V44" s="25"/>
       <c r="W44" s="24" t="s">
         <v>14</v>
       </c>
       <c r="X44" s="25"/>
     </row>
-    <row r="45" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B45" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="47"/>
+      <c r="D45" s="34" t="s">
+        <v>335</v>
+      </c>
+      <c r="E45" s="35"/>
+      <c r="F45" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="G45" s="21"/>
+      <c r="H45" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="I45" s="47"/>
+      <c r="J45" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="K45" s="35"/>
+      <c r="N45" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="O45" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="P45" s="25"/>
+      <c r="Q45" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="R45" s="25"/>
+      <c r="S45" s="98" t="s">
+        <v>215</v>
+      </c>
+      <c r="T45" s="99"/>
+      <c r="U45" s="98" t="s">
+        <v>217</v>
+      </c>
+      <c r="V45" s="99"/>
+      <c r="W45" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="X45" s="25"/>
+    </row>
+    <row r="46" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B45" s="78" t="s">
-        <v>331</v>
-      </c>
-      <c r="C45" s="79"/>
-      <c r="D45" s="78" t="s">
-        <v>332</v>
-      </c>
-      <c r="E45" s="79"/>
-      <c r="F45" s="34" t="s">
-        <v>337</v>
-      </c>
-      <c r="G45" s="35"/>
-      <c r="H45" s="50" t="s">
+      <c r="B46" s="78" t="s">
+        <v>329</v>
+      </c>
+      <c r="C46" s="79"/>
+      <c r="D46" s="78" t="s">
+        <v>330</v>
+      </c>
+      <c r="E46" s="79"/>
+      <c r="F46" s="34" t="s">
+        <v>335</v>
+      </c>
+      <c r="G46" s="35"/>
+      <c r="H46" s="50" t="s">
         <v>275</v>
       </c>
-      <c r="I45" s="51"/>
-      <c r="J45" s="50" t="s">
+      <c r="I46" s="51"/>
+      <c r="J46" s="50" t="s">
         <v>275</v>
       </c>
-      <c r="K45" s="51"/>
-      <c r="N45" s="6" t="s">
+      <c r="K46" s="51"/>
+      <c r="N46" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="O45" s="105" t="s">
-        <v>323</v>
-      </c>
-      <c r="P45" s="106"/>
-      <c r="Q45" s="105" t="s">
-        <v>323</v>
-      </c>
-      <c r="R45" s="106"/>
-      <c r="S45" s="24" t="s">
+      <c r="O46" s="105" t="s">
+        <v>321</v>
+      </c>
+      <c r="P46" s="106"/>
+      <c r="Q46" s="105" t="s">
+        <v>321</v>
+      </c>
+      <c r="R46" s="106"/>
+      <c r="S46" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="T45" s="25"/>
-      <c r="U45" s="24" t="s">
+      <c r="T46" s="25"/>
+      <c r="U46" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="V45" s="25"/>
-      <c r="W45" s="46" t="s">
+      <c r="V46" s="25"/>
+      <c r="W46" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="X45" s="47"/>
-    </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A46" s="6" t="s">
+      <c r="X46" s="47"/>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A47" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B46" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C46" s="21"/>
-      <c r="D46" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="E46" s="21"/>
-      <c r="F46" s="46" t="s">
+      <c r="B47" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C47" s="21"/>
+      <c r="D47" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47" s="21"/>
+      <c r="F47" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="G46" s="47"/>
-      <c r="H46" s="34" t="s">
-        <v>337</v>
-      </c>
-      <c r="I46" s="35"/>
-      <c r="J46" s="46" t="s">
+      <c r="G47" s="47"/>
+      <c r="H47" s="34" t="s">
+        <v>335</v>
+      </c>
+      <c r="I47" s="35"/>
+      <c r="J47" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="K46" s="47"/>
-      <c r="L46" s="7"/>
-      <c r="M46" s="7"/>
-      <c r="N46" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="O46" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="P46" s="45"/>
-      <c r="Q46" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="R46" s="45"/>
-      <c r="S46" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="T46" s="45"/>
-      <c r="U46" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="V46" s="45"/>
-      <c r="W46" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="X46" s="45"/>
-    </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A47" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" s="34" t="s">
-        <v>350</v>
-      </c>
-      <c r="C47" s="35"/>
-      <c r="D47" s="34" t="s">
-        <v>351</v>
-      </c>
-      <c r="E47" s="35"/>
-      <c r="F47" s="34" t="s">
-        <v>351</v>
-      </c>
-      <c r="G47" s="35"/>
-      <c r="H47" s="34" t="s">
-        <v>351</v>
-      </c>
-      <c r="I47" s="35"/>
-      <c r="J47" s="34" t="s">
-        <v>351</v>
-      </c>
-      <c r="K47" s="35"/>
+      <c r="K47" s="47"/>
       <c r="L47" s="7"/>
       <c r="M47" s="7"/>
-      <c r="N47" s="1" t="s">
+      <c r="N47" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O47" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="P47" s="45"/>
+      <c r="Q47" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="R47" s="45"/>
+      <c r="S47" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="T47" s="45"/>
+      <c r="U47" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="V47" s="45"/>
+      <c r="W47" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="X47" s="45"/>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="O47" s="105" t="s">
-        <v>354</v>
-      </c>
-      <c r="P47" s="106"/>
-      <c r="Q47" s="105" t="s">
-        <v>354</v>
-      </c>
-      <c r="R47" s="106"/>
-      <c r="S47" s="34" t="s">
-        <v>355</v>
-      </c>
-      <c r="T47" s="35"/>
-      <c r="U47" s="34" t="s">
-        <v>355</v>
-      </c>
-      <c r="V47" s="35"/>
-      <c r="W47" s="34" t="s">
-        <v>355</v>
-      </c>
-      <c r="X47" s="35"/>
-    </row>
-    <row r="48" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C48" s="21"/>
+      <c r="B48" s="34" t="s">
+        <v>348</v>
+      </c>
+      <c r="C48" s="35"/>
       <c r="D48" s="34" t="s">
-        <v>103</v>
+        <v>349</v>
       </c>
       <c r="E48" s="35"/>
       <c r="F48" s="34" t="s">
-        <v>103</v>
+        <v>349</v>
       </c>
       <c r="G48" s="35"/>
       <c r="H48" s="34" t="s">
-        <v>103</v>
+        <v>349</v>
       </c>
       <c r="I48" s="35"/>
       <c r="J48" s="34" t="s">
-        <v>103</v>
+        <v>349</v>
       </c>
       <c r="K48" s="35"/>
       <c r="L48" s="7"/>
       <c r="M48" s="7"/>
       <c r="N48" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O48" s="105" t="s">
+        <v>352</v>
+      </c>
+      <c r="P48" s="106"/>
+      <c r="Q48" s="105" t="s">
+        <v>352</v>
+      </c>
+      <c r="R48" s="106"/>
+      <c r="S48" s="34" t="s">
+        <v>353</v>
+      </c>
+      <c r="T48" s="35"/>
+      <c r="U48" s="34" t="s">
+        <v>353</v>
+      </c>
+      <c r="V48" s="35"/>
+      <c r="W48" s="34" t="s">
+        <v>353</v>
+      </c>
+      <c r="X48" s="35"/>
+    </row>
+    <row r="49" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O48" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="P48" s="45"/>
-      <c r="Q48" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="R48" s="45"/>
-      <c r="S48" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="T48" s="45"/>
-      <c r="U48" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="V48" s="45"/>
-      <c r="W48" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="X48" s="45"/>
-    </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A49" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B49" s="34" t="s">
-        <v>317</v>
-      </c>
-      <c r="C49" s="35"/>
+      <c r="B49" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C49" s="21"/>
       <c r="D49" s="34" t="s">
-        <v>301</v>
+        <v>103</v>
       </c>
       <c r="E49" s="35"/>
       <c r="F49" s="34" t="s">
-        <v>301</v>
+        <v>103</v>
       </c>
       <c r="G49" s="35"/>
       <c r="H49" s="34" t="s">
-        <v>301</v>
+        <v>103</v>
       </c>
       <c r="I49" s="35"/>
       <c r="J49" s="34" t="s">
-        <v>301</v>
+        <v>103</v>
       </c>
       <c r="K49" s="35"/>
       <c r="L49" s="7"/>
       <c r="M49" s="7"/>
-      <c r="N49" s="12" t="s">
+      <c r="N49" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O49" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="P49" s="45"/>
+      <c r="Q49" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="R49" s="45"/>
+      <c r="S49" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="T49" s="45"/>
+      <c r="U49" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="V49" s="45"/>
+      <c r="W49" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="X49" s="45"/>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A50" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="O49" s="46" t="s">
+      <c r="B50" s="34" t="s">
+        <v>316</v>
+      </c>
+      <c r="C50" s="35"/>
+      <c r="D50" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="E50" s="35"/>
+      <c r="F50" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="G50" s="35"/>
+      <c r="H50" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="I50" s="35"/>
+      <c r="J50" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="K50" s="35"/>
+      <c r="L50" s="7"/>
+      <c r="M50" s="7"/>
+      <c r="N50" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="O50" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="P49" s="47"/>
-      <c r="Q49" s="46" t="s">
+      <c r="P50" s="47"/>
+      <c r="Q50" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="R49" s="47"/>
-      <c r="S49" s="34" t="s">
-        <v>356</v>
-      </c>
-      <c r="T49" s="35"/>
-      <c r="U49" s="34" t="s">
-        <v>356</v>
-      </c>
-      <c r="V49" s="35"/>
-      <c r="W49" s="34" t="s">
-        <v>356</v>
-      </c>
-      <c r="X49" s="35"/>
-    </row>
-    <row r="50" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="1" t="s">
+      <c r="R50" s="47"/>
+      <c r="S50" s="34" t="s">
+        <v>354</v>
+      </c>
+      <c r="T50" s="35"/>
+      <c r="U50" s="34" t="s">
+        <v>354</v>
+      </c>
+      <c r="V50" s="35"/>
+      <c r="W50" s="34" t="s">
+        <v>354</v>
+      </c>
+      <c r="X50" s="35"/>
+    </row>
+    <row r="51" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B50" s="46" t="s">
+      <c r="B51" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="C50" s="47"/>
-      <c r="D50" s="50" t="s">
+      <c r="C51" s="47"/>
+      <c r="D51" s="50" t="s">
         <v>286</v>
       </c>
-      <c r="E50" s="51"/>
-      <c r="F50" s="46" t="s">
+      <c r="E51" s="51"/>
+      <c r="F51" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="G50" s="47"/>
-      <c r="H50" s="50" t="s">
+      <c r="G51" s="47"/>
+      <c r="H51" s="50" t="s">
         <v>286</v>
       </c>
-      <c r="I50" s="51"/>
-      <c r="J50" s="50" t="s">
+      <c r="I51" s="51"/>
+      <c r="J51" s="50" t="s">
         <v>286</v>
       </c>
-      <c r="K50" s="51"/>
-      <c r="N50" s="1" t="s">
+      <c r="K51" s="51"/>
+      <c r="N51" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="O50" s="76" t="s">
+      <c r="O51" s="76" t="s">
         <v>186</v>
-      </c>
-      <c r="P50" s="77"/>
-      <c r="Q50" s="76" t="s">
-        <v>186</v>
-      </c>
-      <c r="R50" s="77"/>
-      <c r="S50" s="76" t="s">
-        <v>186</v>
-      </c>
-      <c r="T50" s="77"/>
-      <c r="U50" s="76" t="s">
-        <v>186</v>
-      </c>
-      <c r="V50" s="77"/>
-      <c r="W50" s="76" t="s">
-        <v>186</v>
-      </c>
-      <c r="X50" s="77"/>
-    </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A51" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B51" s="34" t="s">
-        <v>348</v>
-      </c>
-      <c r="C51" s="35"/>
-      <c r="D51" s="34" t="s">
-        <v>349</v>
-      </c>
-      <c r="E51" s="35"/>
-      <c r="F51" s="34" t="s">
-        <v>349</v>
-      </c>
-      <c r="G51" s="35"/>
-      <c r="H51" s="34" t="s">
-        <v>349</v>
-      </c>
-      <c r="I51" s="35"/>
-      <c r="J51" s="34" t="s">
-        <v>349</v>
-      </c>
-      <c r="K51" s="35"/>
-      <c r="N51" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="O51" s="76" t="s">
-        <v>183</v>
       </c>
       <c r="P51" s="77"/>
       <c r="Q51" s="76" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="R51" s="77"/>
       <c r="S51" s="76" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="T51" s="77"/>
       <c r="U51" s="76" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="V51" s="77"/>
       <c r="W51" s="76" t="s">
+        <v>186</v>
+      </c>
+      <c r="X51" s="77"/>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A52" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B52" s="34" t="s">
+        <v>346</v>
+      </c>
+      <c r="C52" s="35"/>
+      <c r="D52" s="34" t="s">
+        <v>347</v>
+      </c>
+      <c r="E52" s="35"/>
+      <c r="F52" s="34" t="s">
+        <v>347</v>
+      </c>
+      <c r="G52" s="35"/>
+      <c r="H52" s="34" t="s">
+        <v>347</v>
+      </c>
+      <c r="I52" s="35"/>
+      <c r="J52" s="34" t="s">
+        <v>347</v>
+      </c>
+      <c r="K52" s="35"/>
+      <c r="N52" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="O52" s="76" t="s">
         <v>183</v>
       </c>
-      <c r="X51" s="77"/>
-    </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A52" s="1" t="s">
+      <c r="P52" s="77"/>
+      <c r="Q52" s="76" t="s">
+        <v>183</v>
+      </c>
+      <c r="R52" s="77"/>
+      <c r="S52" s="76" t="s">
+        <v>183</v>
+      </c>
+      <c r="T52" s="77"/>
+      <c r="U52" s="76" t="s">
+        <v>183</v>
+      </c>
+      <c r="V52" s="77"/>
+      <c r="W52" s="76" t="s">
+        <v>183</v>
+      </c>
+      <c r="X52" s="77"/>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A53" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B52" s="78" t="s">
-        <v>352</v>
-      </c>
-      <c r="C52" s="79"/>
-      <c r="D52" s="78" t="s">
-        <v>353</v>
-      </c>
-      <c r="E52" s="79"/>
-      <c r="F52" s="20" t="s">
+      <c r="B53" s="78" t="s">
+        <v>350</v>
+      </c>
+      <c r="C53" s="79"/>
+      <c r="D53" s="78" t="s">
+        <v>351</v>
+      </c>
+      <c r="E53" s="79"/>
+      <c r="F53" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="G52" s="21"/>
-      <c r="H52" s="46" t="s">
+      <c r="G53" s="21"/>
+      <c r="H53" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="I52" s="47"/>
-      <c r="J52" s="46" t="s">
+      <c r="I53" s="47"/>
+      <c r="J53" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="K52" s="47"/>
-      <c r="N52" s="1" t="s">
+      <c r="K53" s="47"/>
+      <c r="N53" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="O52" s="24" t="s">
+      <c r="O53" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="P52" s="25"/>
-      <c r="Q52" s="24" t="s">
+      <c r="P53" s="25"/>
+      <c r="Q53" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="R52" s="25"/>
-      <c r="S52" s="20" t="s">
+      <c r="R53" s="25"/>
+      <c r="S53" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="T52" s="21"/>
-      <c r="U52" s="24" t="s">
+      <c r="T53" s="21"/>
+      <c r="U53" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="V52" s="25"/>
-      <c r="W52" s="24" t="s">
+      <c r="V53" s="25"/>
+      <c r="W53" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="X52" s="25"/>
-    </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A54" s="5">
-        <v>1</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="G54" s="5">
-        <v>5</v>
-      </c>
-      <c r="H54" s="5" t="s">
-        <v>80</v>
-      </c>
+      <c r="X53" s="25"/>
     </row>
     <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="5">
+        <v>1</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="G55" s="5">
+        <v>5</v>
+      </c>
+      <c r="H55" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A56" s="5">
         <v>2</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B56" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="G55" s="8">
+      <c r="G56" s="8">
         <v>6</v>
       </c>
-      <c r="H55" s="4" t="s">
+      <c r="H56" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A56" s="8">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A57" s="8">
         <v>3</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B57" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C56" s="5"/>
-      <c r="G56" s="8">
-        <v>9</v>
-      </c>
-      <c r="H56" s="4" t="s">
+      <c r="C57" s="5"/>
+      <c r="G57" s="8">
+        <v>9</v>
+      </c>
+      <c r="H57" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A57" s="5">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A58" s="5">
         <v>4</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B58" s="4" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A58" s="5"/>
-      <c r="B58" s="5"/>
-      <c r="C58" s="5"/>
     </row>
     <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="5"/>
@@ -26532,9 +26560,14 @@
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
     </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A61" s="5"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+    </row>
   </sheetData>
-  <mergeCells count="450">
-    <mergeCell ref="U42:V42"/>
+  <mergeCells count="451">
+    <mergeCell ref="U43:V43"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="F33:G33"/>
@@ -26544,44 +26577,44 @@
     <mergeCell ref="Q33:R33"/>
     <mergeCell ref="S33:T33"/>
     <mergeCell ref="U33:V33"/>
-    <mergeCell ref="S42:T42"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="S38:T38"/>
-    <mergeCell ref="U38:V38"/>
+    <mergeCell ref="S43:T43"/>
+    <mergeCell ref="Q39:R39"/>
+    <mergeCell ref="S39:T39"/>
+    <mergeCell ref="U39:V39"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="Q41:R41"/>
+    <mergeCell ref="S41:T41"/>
+    <mergeCell ref="U41:V41"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="J40:K40"/>
     <mergeCell ref="O40:P40"/>
     <mergeCell ref="Q40:R40"/>
-    <mergeCell ref="S40:T40"/>
-    <mergeCell ref="U40:V40"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="Q39:R39"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="W51:X51"/>
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="D51:E51"/>
     <mergeCell ref="F51:G51"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="J51:K51"/>
-    <mergeCell ref="O51:P51"/>
-    <mergeCell ref="Q51:R51"/>
-    <mergeCell ref="S51:T51"/>
-    <mergeCell ref="U51:V51"/>
-    <mergeCell ref="W47:X47"/>
-    <mergeCell ref="O48:P48"/>
-    <mergeCell ref="Q48:R48"/>
-    <mergeCell ref="S48:T48"/>
-    <mergeCell ref="U48:V48"/>
-    <mergeCell ref="W50:X50"/>
-    <mergeCell ref="O47:P47"/>
-    <mergeCell ref="Q47:R47"/>
+    <mergeCell ref="W52:X52"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="O52:P52"/>
+    <mergeCell ref="Q52:R52"/>
+    <mergeCell ref="S52:T52"/>
+    <mergeCell ref="U52:V52"/>
     <mergeCell ref="W48:X48"/>
     <mergeCell ref="O49:P49"/>
     <mergeCell ref="Q49:R49"/>
+    <mergeCell ref="S49:T49"/>
+    <mergeCell ref="U49:V49"/>
+    <mergeCell ref="W51:X51"/>
+    <mergeCell ref="O48:P48"/>
+    <mergeCell ref="Q48:R48"/>
+    <mergeCell ref="W49:X49"/>
+    <mergeCell ref="O50:P50"/>
+    <mergeCell ref="Q50:R50"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="F32:G32"/>
@@ -26615,44 +26648,44 @@
     <mergeCell ref="Q15:R15"/>
     <mergeCell ref="S15:T15"/>
     <mergeCell ref="U15:V15"/>
-    <mergeCell ref="W49:X49"/>
-    <mergeCell ref="O43:P43"/>
-    <mergeCell ref="Q43:R43"/>
-    <mergeCell ref="U45:V45"/>
-    <mergeCell ref="S45:T45"/>
-    <mergeCell ref="W46:X46"/>
+    <mergeCell ref="W50:X50"/>
+    <mergeCell ref="O44:P44"/>
+    <mergeCell ref="Q44:R44"/>
+    <mergeCell ref="U46:V46"/>
+    <mergeCell ref="S46:T46"/>
+    <mergeCell ref="W47:X47"/>
+    <mergeCell ref="O47:P47"/>
+    <mergeCell ref="Q47:R47"/>
+    <mergeCell ref="S47:T47"/>
+    <mergeCell ref="U47:V47"/>
+    <mergeCell ref="W44:X44"/>
     <mergeCell ref="O46:P46"/>
     <mergeCell ref="Q46:R46"/>
-    <mergeCell ref="S46:T46"/>
-    <mergeCell ref="U46:V46"/>
-    <mergeCell ref="W43:X43"/>
+    <mergeCell ref="W45:X45"/>
+    <mergeCell ref="W46:X46"/>
+    <mergeCell ref="S44:T44"/>
+    <mergeCell ref="S45:T45"/>
+    <mergeCell ref="U45:V45"/>
     <mergeCell ref="O45:P45"/>
     <mergeCell ref="Q45:R45"/>
-    <mergeCell ref="W44:X44"/>
-    <mergeCell ref="W45:X45"/>
-    <mergeCell ref="S43:T43"/>
-    <mergeCell ref="S44:T44"/>
-    <mergeCell ref="U44:V44"/>
-    <mergeCell ref="O44:P44"/>
-    <mergeCell ref="Q44:R44"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="J50:K50"/>
-    <mergeCell ref="O50:P50"/>
-    <mergeCell ref="Q50:R50"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="J51:K51"/>
+    <mergeCell ref="O51:P51"/>
+    <mergeCell ref="Q51:R51"/>
+    <mergeCell ref="S51:T51"/>
+    <mergeCell ref="U51:V51"/>
+    <mergeCell ref="U48:V48"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="J48:K48"/>
+    <mergeCell ref="S48:T48"/>
     <mergeCell ref="S50:T50"/>
     <mergeCell ref="U50:V50"/>
-    <mergeCell ref="U47:V47"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="J47:K47"/>
-    <mergeCell ref="S47:T47"/>
-    <mergeCell ref="S49:T49"/>
-    <mergeCell ref="U49:V49"/>
-    <mergeCell ref="J48:K48"/>
-    <mergeCell ref="W40:X40"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="Q41:R41"/>
-    <mergeCell ref="S41:T41"/>
-    <mergeCell ref="U41:V41"/>
+    <mergeCell ref="J49:K49"/>
+    <mergeCell ref="W41:X41"/>
+    <mergeCell ref="O42:P42"/>
+    <mergeCell ref="Q42:R42"/>
+    <mergeCell ref="S42:T42"/>
+    <mergeCell ref="U42:V42"/>
     <mergeCell ref="O31:P31"/>
     <mergeCell ref="Q31:R31"/>
     <mergeCell ref="S31:T31"/>
@@ -26661,16 +26694,17 @@
     <mergeCell ref="W32:X32"/>
     <mergeCell ref="U32:V32"/>
     <mergeCell ref="W33:X33"/>
-    <mergeCell ref="W38:X38"/>
-    <mergeCell ref="W41:X41"/>
-    <mergeCell ref="S39:T39"/>
-    <mergeCell ref="U39:V39"/>
     <mergeCell ref="W39:X39"/>
+    <mergeCell ref="W42:X42"/>
+    <mergeCell ref="S40:T40"/>
+    <mergeCell ref="U40:V40"/>
+    <mergeCell ref="W40:X40"/>
     <mergeCell ref="W34:X34"/>
     <mergeCell ref="O34:P34"/>
     <mergeCell ref="Q34:R34"/>
     <mergeCell ref="S34:T34"/>
     <mergeCell ref="U34:V34"/>
+    <mergeCell ref="O35:P35"/>
     <mergeCell ref="O12:P12"/>
     <mergeCell ref="S12:T12"/>
     <mergeCell ref="U12:V12"/>
@@ -26821,11 +26855,11 @@
     <mergeCell ref="O3:P3"/>
     <mergeCell ref="Q3:R3"/>
     <mergeCell ref="F9:G9"/>
-    <mergeCell ref="Q42:R42"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="J42:K42"/>
-    <mergeCell ref="O42:P42"/>
+    <mergeCell ref="Q43:R43"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="O43:P43"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="F2:G2"/>
@@ -26845,18 +26879,18 @@
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="W42:X42"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="W43:X43"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="F48:G48"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="H3:I3"/>
     <mergeCell ref="J3:K3"/>
-    <mergeCell ref="U43:V43"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="U44:V44"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="D45:E45"/>
     <mergeCell ref="Q12:R12"/>
     <mergeCell ref="S10:T10"/>
     <mergeCell ref="O10:P10"/>
@@ -26868,8 +26902,8 @@
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D9:E9"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="F42:G42"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="F22:G22"/>
@@ -26894,25 +26928,25 @@
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="H9:I9"/>
     <mergeCell ref="J9:K9"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="J44:K44"/>
-    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="D43:E43"/>
     <mergeCell ref="H27:I27"/>
     <mergeCell ref="D28:E28"/>
     <mergeCell ref="J23:K23"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="J44:K44"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:E39"/>
     <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="B43:C43"/>
     <mergeCell ref="H29:I29"/>
     <mergeCell ref="H26:I26"/>
     <mergeCell ref="H28:I28"/>
@@ -26931,59 +26965,59 @@
     <mergeCell ref="J26:K26"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="D20:E20"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="F43:G43"/>
     <mergeCell ref="H34:I34"/>
     <mergeCell ref="J34:K34"/>
     <mergeCell ref="H21:I21"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="D27:E27"/>
     <mergeCell ref="F27:G27"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="B46:C46"/>
     <mergeCell ref="D46:E46"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="J46:K46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="F40:G40"/>
     <mergeCell ref="F39:G39"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="H16:I16"/>
     <mergeCell ref="J16:K16"/>
     <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="J50:K50"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="J47:K47"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B48:C48"/>
     <mergeCell ref="B49:C49"/>
     <mergeCell ref="D49:E49"/>
     <mergeCell ref="F49:G49"/>
     <mergeCell ref="H49:I49"/>
-    <mergeCell ref="J49:K49"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="J46:K46"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="D41:E41"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="D34:E34"/>
     <mergeCell ref="F34:G34"/>
-    <mergeCell ref="W52:X52"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="O52:P52"/>
-    <mergeCell ref="Q52:R52"/>
-    <mergeCell ref="S52:T52"/>
-    <mergeCell ref="U52:V52"/>
+    <mergeCell ref="W53:X53"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="J53:K53"/>
+    <mergeCell ref="O53:P53"/>
+    <mergeCell ref="Q53:R53"/>
+    <mergeCell ref="S53:T53"/>
+    <mergeCell ref="U53:V53"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -27033,7 +27067,7 @@
     <row r="1" spans="2:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>1</v>
@@ -27066,7 +27100,7 @@
         <v>46360</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>1</v>
@@ -27306,11 +27340,11 @@
         <v>26</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D8" s="35"/>
       <c r="E8" s="34" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F8" s="35"/>
       <c r="G8" s="88"/>
@@ -27340,11 +27374,11 @@
         <v>28</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D9" s="35"/>
       <c r="E9" s="34" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F9" s="35"/>
       <c r="G9" s="74"/>
@@ -27481,8 +27515,10 @@
         <v>72</v>
       </c>
       <c r="J13" s="43"/>
-      <c r="K13" s="20"/>
-      <c r="L13" s="21"/>
+      <c r="K13" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="L13" s="35"/>
       <c r="O13" s="1" t="s">
         <v>40</v>
       </c>
@@ -27540,36 +27576,44 @@
         <v>48</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D15" s="35"/>
       <c r="E15" s="34" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F15" s="35"/>
       <c r="G15" s="34" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="H15" s="35"/>
       <c r="I15" s="34" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="J15" s="35"/>
-      <c r="K15" s="34" t="s">
-        <v>342</v>
-      </c>
-      <c r="L15" s="35"/>
+      <c r="K15" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="L15" s="41"/>
       <c r="O15" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="P15" s="20"/>
-      <c r="Q15" s="21"/>
-      <c r="R15" s="20"/>
-      <c r="S15" s="21"/>
-      <c r="T15" s="20"/>
-      <c r="U15" s="21"/>
-      <c r="V15" s="20"/>
-      <c r="W15" s="21"/>
+      <c r="P15" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q15" s="41"/>
+      <c r="R15" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="S15" s="41"/>
+      <c r="T15" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="U15" s="41"/>
+      <c r="V15" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="W15" s="41"/>
       <c r="X15" s="66"/>
       <c r="Y15" s="67"/>
     </row>
@@ -27666,7 +27710,7 @@
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>1</v>
@@ -27699,7 +27743,7 @@
         <v>46367</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>1</v>
@@ -28264,7 +28308,7 @@
     </row>
     <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>1</v>
@@ -28633,7 +28677,7 @@
       <c r="C50" s="74"/>
       <c r="D50" s="75"/>
       <c r="E50" s="44" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F50" s="45"/>
       <c r="G50" s="74"/>

--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6593" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DC5B5A8-1242-4926-A273-DCE4B3B1E325}"/>
+  <xr:revisionPtr revIDLastSave="6599" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C2B6BAD-E098-4B77-BD99-970FD207BF7B}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4792" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4793" uniqueCount="360">
   <si>
     <t>Uke 01</t>
   </si>
@@ -1152,6 +1152,9 @@
   </si>
   <si>
     <t>SF BR 4 GG</t>
+  </si>
+  <si>
+    <t>SF BR 4 ORM</t>
   </si>
 </sst>
 </file>
@@ -20755,7 +20758,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X66"/>
+  <dimension ref="A1:X67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
@@ -21465,10 +21468,10 @@
         <v>20</v>
       </c>
       <c r="R14" s="41"/>
-      <c r="S14" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="T14" s="37"/>
+      <c r="S14" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="T14" s="41"/>
       <c r="U14" s="20" t="s">
         <v>9</v>
       </c>
@@ -21624,6 +21627,10 @@
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
+      <c r="S19" s="36" t="s">
+        <v>359</v>
+      </c>
+      <c r="T19" s="37"/>
     </row>
     <row r="20" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
@@ -21638,855 +21645,843 @@
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C21" s="3">
-        <v>46279</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E21" s="3">
-        <v>46280</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G21" s="3">
-        <v>46281</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I21" s="3">
-        <v>46282</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="K21" s="3">
-        <v>46283</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P21" s="3">
-        <v>46300</v>
-      </c>
-      <c r="Q21" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="R21" s="3">
-        <v>46301</v>
-      </c>
-      <c r="S21" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T21" s="3">
-        <v>46302</v>
-      </c>
-      <c r="U21" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="V21" s="3">
-        <v>46303</v>
-      </c>
-      <c r="W21" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="X21" s="3">
-        <v>46304</v>
-      </c>
+    <row r="21" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="50" t="s">
-        <v>273</v>
-      </c>
-      <c r="C22" s="51"/>
-      <c r="D22" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22" s="39"/>
-      <c r="F22" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="G22" s="39"/>
-      <c r="H22" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I22" s="39"/>
-      <c r="J22" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K22" s="39"/>
+        <v>290</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="3">
+        <v>46279</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E22" s="3">
+        <v>46280</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3">
+        <v>46281</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="3">
+        <v>46282</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K22" s="3">
+        <v>46283</v>
+      </c>
       <c r="N22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="O22" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="P22" s="39"/>
-      <c r="Q22" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="R22" s="39"/>
-      <c r="S22" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="T22" s="39"/>
-      <c r="U22" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="V22" s="39"/>
-      <c r="W22" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="X22" s="39"/>
+        <v>291</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P22" s="3">
+        <v>46300</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="R22" s="3">
+        <v>46301</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T22" s="3">
+        <v>46302</v>
+      </c>
+      <c r="U22" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="V22" s="3">
+        <v>46303</v>
+      </c>
+      <c r="W22" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="X22" s="3">
+        <v>46304</v>
+      </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B23" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" s="21"/>
-      <c r="D23" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="E23" s="21"/>
-      <c r="F23" s="24" t="s">
-        <v>292</v>
-      </c>
-      <c r="G23" s="25"/>
-      <c r="H23" s="24" t="s">
-        <v>292</v>
-      </c>
-      <c r="I23" s="25"/>
-      <c r="J23" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="K23" s="37"/>
+        <v>7</v>
+      </c>
+      <c r="B23" s="50" t="s">
+        <v>273</v>
+      </c>
+      <c r="C23" s="51"/>
+      <c r="D23" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="39"/>
+      <c r="F23" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="G23" s="39"/>
+      <c r="H23" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="I23" s="39"/>
+      <c r="J23" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="K23" s="39"/>
       <c r="N23" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="O23" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="P23" s="21"/>
-      <c r="Q23" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="R23" s="37"/>
-      <c r="S23" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="T23" s="37"/>
-      <c r="U23" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="V23" s="21"/>
-      <c r="W23" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="X23" s="21"/>
+        <v>7</v>
+      </c>
+      <c r="O23" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="P23" s="39"/>
+      <c r="Q23" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="R23" s="39"/>
+      <c r="S23" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="T23" s="39"/>
+      <c r="U23" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="V23" s="39"/>
+      <c r="W23" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="X23" s="39"/>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B24" s="20" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="21"/>
-      <c r="D24" s="28" t="s">
-        <v>253</v>
-      </c>
-      <c r="E24" s="29"/>
+      <c r="D24" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="21"/>
       <c r="F24" s="24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G24" s="25"/>
       <c r="H24" s="24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I24" s="25"/>
-      <c r="J24" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="K24" s="41"/>
+      <c r="J24" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="K24" s="37"/>
       <c r="N24" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="O24" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="P24" s="41"/>
-      <c r="Q24" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="R24" s="41"/>
-      <c r="S24" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="T24" s="41"/>
-      <c r="U24" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="V24" s="41"/>
-      <c r="W24" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="X24" s="41"/>
+        <v>10</v>
+      </c>
+      <c r="O24" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="P24" s="21"/>
+      <c r="Q24" s="36" t="s">
+        <v>277</v>
+      </c>
+      <c r="R24" s="37"/>
+      <c r="S24" s="36" t="s">
+        <v>277</v>
+      </c>
+      <c r="T24" s="37"/>
+      <c r="U24" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="V24" s="21"/>
+      <c r="W24" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="X24" s="21"/>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B25" s="22" t="s">
-        <v>285</v>
-      </c>
-      <c r="C25" s="23"/>
-      <c r="D25" s="22" t="s">
-        <v>285</v>
-      </c>
-      <c r="E25" s="23"/>
-      <c r="F25" s="22" t="s">
-        <v>285</v>
-      </c>
-      <c r="G25" s="23"/>
-      <c r="H25" s="22" t="s">
-        <v>285</v>
-      </c>
-      <c r="I25" s="23"/>
-      <c r="J25" s="22" t="s">
-        <v>285</v>
-      </c>
-      <c r="K25" s="23"/>
+        <v>15</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="21"/>
+      <c r="D25" s="28" t="s">
+        <v>253</v>
+      </c>
+      <c r="E25" s="29"/>
+      <c r="F25" s="24" t="s">
+        <v>293</v>
+      </c>
+      <c r="G25" s="25"/>
+      <c r="H25" s="24" t="s">
+        <v>293</v>
+      </c>
+      <c r="I25" s="25"/>
+      <c r="J25" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="K25" s="41"/>
       <c r="N25" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O25" s="26" t="s">
-        <v>294</v>
-      </c>
-      <c r="P25" s="27"/>
-      <c r="Q25" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="R25" s="35"/>
-      <c r="S25" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="T25" s="35"/>
-      <c r="U25" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="V25" s="35"/>
-      <c r="W25" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="X25" s="35"/>
+        <v>15</v>
+      </c>
+      <c r="O25" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="P25" s="41"/>
+      <c r="Q25" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="R25" s="41"/>
+      <c r="S25" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="T25" s="41"/>
+      <c r="U25" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="V25" s="41"/>
+      <c r="W25" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="X25" s="41"/>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="C26" s="23"/>
+      <c r="D26" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="E26" s="23"/>
+      <c r="F26" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="G26" s="23"/>
+      <c r="H26" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="I26" s="23"/>
+      <c r="J26" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="K26" s="23"/>
+      <c r="N26" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O26" s="26" t="s">
+        <v>294</v>
+      </c>
+      <c r="P26" s="27"/>
+      <c r="Q26" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R26" s="35"/>
+      <c r="S26" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T26" s="35"/>
+      <c r="U26" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="V26" s="35"/>
+      <c r="W26" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X26" s="35"/>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="44" t="s">
+      <c r="B27" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="C26" s="45"/>
-      <c r="D26" s="44" t="s">
+      <c r="C27" s="45"/>
+      <c r="D27" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="E26" s="45"/>
-      <c r="F26" s="44" t="s">
+      <c r="E27" s="45"/>
+      <c r="F27" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="G26" s="45"/>
-      <c r="H26" s="44" t="s">
+      <c r="G27" s="45"/>
+      <c r="H27" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="I26" s="45"/>
-      <c r="J26" s="44" t="s">
+      <c r="I27" s="45"/>
+      <c r="J27" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="K26" s="45"/>
-      <c r="N26" s="1" t="s">
+      <c r="K27" s="45"/>
+      <c r="N27" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="O26" s="44" t="s">
+      <c r="O27" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="P26" s="45"/>
-      <c r="Q26" s="44" t="s">
+      <c r="P27" s="45"/>
+      <c r="Q27" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="R26" s="45"/>
-      <c r="S26" s="44" t="s">
+      <c r="R27" s="45"/>
+      <c r="S27" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="T26" s="45"/>
-      <c r="U26" s="44" t="s">
+      <c r="T27" s="45"/>
+      <c r="U27" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="V26" s="45"/>
-      <c r="W26" s="44" t="s">
+      <c r="V27" s="45"/>
+      <c r="W27" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="X26" s="45"/>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A27" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="46" t="s">
-        <v>287</v>
-      </c>
-      <c r="C27" s="47"/>
-      <c r="D27" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="E27" s="21"/>
-      <c r="F27" s="46" t="s">
-        <v>287</v>
-      </c>
-      <c r="G27" s="47"/>
-      <c r="H27" s="46" t="s">
-        <v>287</v>
-      </c>
-      <c r="I27" s="47"/>
-      <c r="J27" s="34" t="s">
-        <v>281</v>
-      </c>
-      <c r="K27" s="35"/>
-      <c r="N27" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O27" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="R27" s="41"/>
-      <c r="S27" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="T27" s="41"/>
-      <c r="U27" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="V27" s="41"/>
-      <c r="W27" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="X27" s="41"/>
+      <c r="X27" s="45"/>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C28" s="21"/>
-      <c r="D28" s="24" t="s">
-        <v>293</v>
-      </c>
-      <c r="E28" s="25"/>
-      <c r="F28" s="26" t="s">
-        <v>295</v>
-      </c>
-      <c r="G28" s="27"/>
-      <c r="H28" s="26" t="s">
-        <v>295</v>
-      </c>
-      <c r="I28" s="27"/>
-      <c r="J28" s="26" t="s">
-        <v>295</v>
-      </c>
-      <c r="K28" s="27"/>
+        <v>26</v>
+      </c>
+      <c r="B28" s="46" t="s">
+        <v>287</v>
+      </c>
+      <c r="C28" s="47"/>
+      <c r="D28" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="21"/>
+      <c r="F28" s="46" t="s">
+        <v>287</v>
+      </c>
+      <c r="G28" s="47"/>
+      <c r="H28" s="46" t="s">
+        <v>287</v>
+      </c>
+      <c r="I28" s="47"/>
+      <c r="J28" s="34" t="s">
+        <v>281</v>
+      </c>
+      <c r="K28" s="35"/>
       <c r="N28" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O28" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="P28" s="27"/>
-      <c r="Q28" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="R28" s="27"/>
-      <c r="S28" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="T28" s="27"/>
-      <c r="U28" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="V28" s="27"/>
-      <c r="W28" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="X28" s="21"/>
+        <v>26</v>
+      </c>
+      <c r="O28" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="P28" s="41"/>
+      <c r="Q28" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="R28" s="41"/>
+      <c r="S28" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="T28" s="41"/>
+      <c r="U28" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="V28" s="41"/>
+      <c r="W28" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="X28" s="41"/>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B29" s="20" t="s">
         <v>9</v>
       </c>
       <c r="C29" s="21"/>
-      <c r="D29" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="E29" s="37"/>
-      <c r="F29" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="G29" s="37"/>
-      <c r="H29" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="I29" s="37"/>
-      <c r="J29" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="K29" s="37"/>
+      <c r="D29" s="24" t="s">
+        <v>293</v>
+      </c>
+      <c r="E29" s="25"/>
+      <c r="F29" s="26" t="s">
+        <v>295</v>
+      </c>
+      <c r="G29" s="27"/>
+      <c r="H29" s="26" t="s">
+        <v>295</v>
+      </c>
+      <c r="I29" s="27"/>
+      <c r="J29" s="26" t="s">
+        <v>295</v>
+      </c>
+      <c r="K29" s="27"/>
       <c r="N29" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="O29" s="34" t="s">
-        <v>283</v>
-      </c>
-      <c r="P29" s="35"/>
-      <c r="Q29" s="34" t="s">
-        <v>283</v>
-      </c>
-      <c r="R29" s="35"/>
-      <c r="S29" s="34" t="s">
-        <v>283</v>
-      </c>
-      <c r="T29" s="35"/>
-      <c r="U29" s="34" t="s">
-        <v>283</v>
-      </c>
-      <c r="V29" s="35"/>
-      <c r="W29" s="34" t="s">
-        <v>283</v>
-      </c>
-      <c r="X29" s="35"/>
+        <v>28</v>
+      </c>
+      <c r="O29" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="P29" s="27"/>
+      <c r="Q29" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="R29" s="27"/>
+      <c r="S29" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="T29" s="27"/>
+      <c r="U29" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="V29" s="27"/>
+      <c r="W29" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="X29" s="21"/>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="21"/>
+      <c r="D30" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="E30" s="37"/>
+      <c r="F30" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="G30" s="37"/>
+      <c r="H30" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="I30" s="37"/>
+      <c r="J30" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="K30" s="37"/>
+      <c r="N30" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="O30" s="34" t="s">
+        <v>283</v>
+      </c>
+      <c r="P30" s="35"/>
+      <c r="Q30" s="34" t="s">
+        <v>283</v>
+      </c>
+      <c r="R30" s="35"/>
+      <c r="S30" s="34" t="s">
+        <v>283</v>
+      </c>
+      <c r="T30" s="35"/>
+      <c r="U30" s="34" t="s">
+        <v>283</v>
+      </c>
+      <c r="V30" s="35"/>
+      <c r="W30" s="34" t="s">
+        <v>283</v>
+      </c>
+      <c r="X30" s="35"/>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A31" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B30" s="44" t="s">
+      <c r="B31" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="45"/>
-      <c r="D30" s="44" t="s">
+      <c r="C31" s="45"/>
+      <c r="D31" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="E30" s="45"/>
-      <c r="F30" s="44" t="s">
+      <c r="E31" s="45"/>
+      <c r="F31" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="G30" s="45"/>
-      <c r="H30" s="52" t="s">
+      <c r="G31" s="45"/>
+      <c r="H31" s="52" t="s">
         <v>297</v>
       </c>
-      <c r="I30" s="53"/>
-      <c r="J30" s="44" t="s">
+      <c r="I31" s="53"/>
+      <c r="J31" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="K30" s="45"/>
-      <c r="N30" s="6" t="s">
+      <c r="K31" s="45"/>
+      <c r="N31" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="O30" s="44" t="s">
+      <c r="O31" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="P30" s="45"/>
-      <c r="Q30" s="32" t="s">
+      <c r="P31" s="45"/>
+      <c r="Q31" s="32" t="s">
         <v>298</v>
       </c>
-      <c r="R30" s="33"/>
-      <c r="S30" s="44" t="s">
+      <c r="R31" s="33"/>
+      <c r="S31" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="T30" s="45"/>
-      <c r="U30" s="44" t="s">
+      <c r="T31" s="45"/>
+      <c r="U31" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="V30" s="45"/>
-      <c r="W30" s="44" t="s">
+      <c r="V31" s="45"/>
+      <c r="W31" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="X30" s="45"/>
-    </row>
-    <row r="31" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="1" t="s">
+      <c r="X31" s="45"/>
+    </row>
+    <row r="32" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="24" t="s">
+      <c r="B32" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="C31" s="25"/>
-      <c r="D31" s="24" t="s">
+      <c r="C32" s="25"/>
+      <c r="D32" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="E31" s="25"/>
-      <c r="F31" s="26" t="s">
+      <c r="E32" s="25"/>
+      <c r="F32" s="26" t="s">
         <v>296</v>
       </c>
-      <c r="G31" s="27"/>
-      <c r="H31" s="26" t="s">
+      <c r="G32" s="27"/>
+      <c r="H32" s="26" t="s">
         <v>296</v>
       </c>
-      <c r="I31" s="27"/>
-      <c r="J31" s="26" t="s">
+      <c r="I32" s="27"/>
+      <c r="J32" s="26" t="s">
         <v>296</v>
       </c>
-      <c r="K31" s="27"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
-      <c r="N31" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="O31" s="26" t="s">
-        <v>295</v>
-      </c>
-      <c r="P31" s="27"/>
-      <c r="Q31" s="26" t="s">
-        <v>295</v>
-      </c>
-      <c r="R31" s="27"/>
-      <c r="S31" s="26" t="s">
-        <v>295</v>
-      </c>
-      <c r="T31" s="27"/>
-      <c r="U31" s="26" t="s">
-        <v>295</v>
-      </c>
-      <c r="V31" s="27"/>
-      <c r="W31" s="32" t="s">
-        <v>299</v>
-      </c>
-      <c r="X31" s="33"/>
-    </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="C32" s="45"/>
-      <c r="D32" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="E32" s="45"/>
-      <c r="F32" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="G32" s="45"/>
-      <c r="H32" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="I32" s="31"/>
-      <c r="J32" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="K32" s="45"/>
+      <c r="K32" s="27"/>
       <c r="L32" s="7"/>
       <c r="M32" s="7"/>
       <c r="N32" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O32" s="26" t="s">
+        <v>295</v>
+      </c>
+      <c r="P32" s="27"/>
+      <c r="Q32" s="26" t="s">
+        <v>295</v>
+      </c>
+      <c r="R32" s="27"/>
+      <c r="S32" s="26" t="s">
+        <v>295</v>
+      </c>
+      <c r="T32" s="27"/>
+      <c r="U32" s="26" t="s">
+        <v>295</v>
+      </c>
+      <c r="V32" s="27"/>
+      <c r="W32" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="X32" s="33"/>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O32" s="44" t="s">
+      <c r="B33" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="P32" s="45"/>
-      <c r="Q32" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="R32" s="35"/>
-      <c r="S32" s="44" t="s">
+      <c r="C33" s="45"/>
+      <c r="D33" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="T32" s="45"/>
-      <c r="U32" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="V32" s="35"/>
-      <c r="W32" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="X32" s="35"/>
-    </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A33" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="28" t="s">
-        <v>254</v>
-      </c>
-      <c r="C33" s="29"/>
-      <c r="D33" s="28" t="s">
-        <v>254</v>
-      </c>
-      <c r="E33" s="29"/>
-      <c r="F33" s="28" t="s">
-        <v>254</v>
-      </c>
-      <c r="G33" s="29"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="G33" s="45"/>
       <c r="H33" s="30" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I33" s="31"/>
-      <c r="J33" s="24" t="s">
-        <v>292</v>
-      </c>
-      <c r="K33" s="25"/>
+      <c r="J33" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="K33" s="45"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
-      <c r="N33" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="O33" s="34" t="s">
-        <v>300</v>
-      </c>
-      <c r="P33" s="35"/>
+      <c r="N33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O33" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="P33" s="45"/>
       <c r="Q33" s="34" t="s">
-        <v>300</v>
+        <v>103</v>
       </c>
       <c r="R33" s="35"/>
-      <c r="S33" s="34" t="s">
-        <v>300</v>
-      </c>
-      <c r="T33" s="35"/>
+      <c r="S33" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="T33" s="45"/>
       <c r="U33" s="34" t="s">
-        <v>300</v>
+        <v>103</v>
       </c>
       <c r="V33" s="35"/>
       <c r="W33" s="34" t="s">
-        <v>300</v>
+        <v>103</v>
       </c>
       <c r="X33" s="35"/>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B34" s="24" t="s">
-        <v>293</v>
-      </c>
-      <c r="C34" s="25"/>
-      <c r="D34" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="E34" s="37"/>
-      <c r="F34" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="G34" s="37"/>
-      <c r="H34" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="I34" s="37"/>
-      <c r="J34" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="K34" s="37"/>
+      <c r="A34" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="28" t="s">
+        <v>254</v>
+      </c>
+      <c r="C34" s="29"/>
+      <c r="D34" s="28" t="s">
+        <v>254</v>
+      </c>
+      <c r="E34" s="29"/>
+      <c r="F34" s="28" t="s">
+        <v>254</v>
+      </c>
+      <c r="G34" s="29"/>
+      <c r="H34" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="I34" s="31"/>
+      <c r="J34" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="K34" s="25"/>
       <c r="L34" s="7"/>
       <c r="M34" s="7"/>
-      <c r="N34" s="1" t="s">
+      <c r="N34" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="O34" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="P34" s="35"/>
+      <c r="Q34" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="R34" s="35"/>
+      <c r="S34" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="T34" s="35"/>
+      <c r="U34" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="V34" s="35"/>
+      <c r="W34" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="X34" s="35"/>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="O34" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="P34" s="37"/>
-      <c r="Q34" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="R34" s="37"/>
-      <c r="S34" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="T34" s="37"/>
-      <c r="U34" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="V34" s="37"/>
-      <c r="W34" s="34" t="s">
-        <v>279</v>
-      </c>
-      <c r="X34" s="35"/>
-    </row>
-    <row r="35" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B35" s="46" t="s">
-        <v>288</v>
-      </c>
-      <c r="C35" s="47"/>
-      <c r="D35" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="E35" s="21"/>
-      <c r="F35" s="46" t="s">
-        <v>288</v>
-      </c>
-      <c r="G35" s="47"/>
-      <c r="H35" s="46" t="s">
-        <v>288</v>
-      </c>
-      <c r="I35" s="47"/>
-      <c r="J35" s="24" t="s">
+      <c r="B35" s="24" t="s">
         <v>293</v>
       </c>
-      <c r="K35" s="25"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="36" t="s">
+        <v>277</v>
+      </c>
+      <c r="E35" s="37"/>
+      <c r="F35" s="36" t="s">
+        <v>277</v>
+      </c>
+      <c r="G35" s="37"/>
+      <c r="H35" s="36" t="s">
+        <v>277</v>
+      </c>
+      <c r="I35" s="37"/>
+      <c r="J35" s="36" t="s">
+        <v>277</v>
+      </c>
+      <c r="K35" s="37"/>
       <c r="L35" s="7"/>
       <c r="M35" s="7"/>
-      <c r="N35" s="12" t="s">
+      <c r="N35" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O35" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="P35" s="37"/>
+      <c r="Q35" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="R35" s="37"/>
+      <c r="S35" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="T35" s="37"/>
+      <c r="U35" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="V35" s="37"/>
+      <c r="W35" s="34" t="s">
+        <v>279</v>
+      </c>
+      <c r="X35" s="35"/>
+    </row>
+    <row r="36" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="O35" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="P35" s="37"/>
-      <c r="Q35" s="34" t="s">
-        <v>301</v>
-      </c>
-      <c r="R35" s="35"/>
-      <c r="S35" s="34" t="s">
-        <v>301</v>
-      </c>
-      <c r="T35" s="35"/>
-      <c r="U35" s="34" t="s">
-        <v>301</v>
-      </c>
-      <c r="V35" s="35"/>
-      <c r="W35" s="34" t="s">
-        <v>124</v>
-      </c>
-      <c r="X35" s="35"/>
-    </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A36" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B36" s="28" t="s">
-        <v>253</v>
-      </c>
-      <c r="C36" s="29"/>
-      <c r="D36" s="28" t="s">
-        <v>253</v>
-      </c>
-      <c r="E36" s="29"/>
-      <c r="F36" s="28" t="s">
-        <v>253</v>
-      </c>
-      <c r="G36" s="29"/>
-      <c r="H36" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="I36" s="31"/>
-      <c r="J36" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="K36" s="21"/>
+      <c r="B36" s="46" t="s">
+        <v>288</v>
+      </c>
+      <c r="C36" s="47"/>
+      <c r="D36" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" s="21"/>
+      <c r="F36" s="46" t="s">
+        <v>288</v>
+      </c>
+      <c r="G36" s="47"/>
+      <c r="H36" s="46" t="s">
+        <v>288</v>
+      </c>
+      <c r="I36" s="47"/>
+      <c r="J36" s="24" t="s">
+        <v>293</v>
+      </c>
+      <c r="K36" s="25"/>
       <c r="L36" s="7"/>
       <c r="M36" s="7"/>
-      <c r="N36" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="O36" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="P36" s="21"/>
-      <c r="Q36" s="32" t="s">
-        <v>302</v>
-      </c>
-      <c r="R36" s="33"/>
+      <c r="N36" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="O36" s="36" t="s">
+        <v>277</v>
+      </c>
+      <c r="P36" s="37"/>
+      <c r="Q36" s="34" t="s">
+        <v>301</v>
+      </c>
+      <c r="R36" s="35"/>
       <c r="S36" s="34" t="s">
-        <v>103</v>
+        <v>301</v>
       </c>
       <c r="T36" s="35"/>
-      <c r="U36" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="V36" s="37"/>
-      <c r="W36" s="32" t="s">
-        <v>299</v>
-      </c>
-      <c r="X36" s="33"/>
+      <c r="U36" s="34" t="s">
+        <v>301</v>
+      </c>
+      <c r="V36" s="35"/>
+      <c r="W36" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="X36" s="35"/>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B37" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="C37" s="23"/>
-      <c r="D37" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="E37" s="23"/>
-      <c r="F37" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="G37" s="23"/>
-      <c r="H37" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="I37" s="23"/>
-      <c r="J37" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="K37" s="23"/>
+        <v>50</v>
+      </c>
+      <c r="B37" s="28" t="s">
+        <v>253</v>
+      </c>
+      <c r="C37" s="29"/>
+      <c r="D37" s="28" t="s">
+        <v>253</v>
+      </c>
+      <c r="E37" s="29"/>
+      <c r="F37" s="28" t="s">
+        <v>253</v>
+      </c>
+      <c r="G37" s="29"/>
+      <c r="H37" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="I37" s="31"/>
+      <c r="J37" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="K37" s="21"/>
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
-      <c r="O37" s="9"/>
-      <c r="P37" s="9"/>
-      <c r="Q37" s="9"/>
-      <c r="R37" s="9"/>
-      <c r="S37" s="9"/>
-      <c r="T37" s="9"/>
-      <c r="U37" s="9"/>
-      <c r="V37" s="9"/>
-      <c r="W37" s="9"/>
-      <c r="X37" s="9"/>
+      <c r="N37" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O37" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="P37" s="21"/>
+      <c r="Q37" s="32" t="s">
+        <v>302</v>
+      </c>
+      <c r="R37" s="33"/>
+      <c r="S37" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="T37" s="35"/>
+      <c r="U37" s="36" t="s">
+        <v>277</v>
+      </c>
+      <c r="V37" s="37"/>
+      <c r="W37" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="X37" s="33"/>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A38" s="5"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-      <c r="J38" s="9"/>
-      <c r="K38" s="9"/>
+      <c r="A38" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B38" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="C38" s="23"/>
+      <c r="D38" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="E38" s="23"/>
+      <c r="F38" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="G38" s="23"/>
+      <c r="H38" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="I38" s="23"/>
+      <c r="J38" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="K38" s="23"/>
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
       <c r="O38" s="9"/>
@@ -22502,245 +22497,220 @@
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39" s="5"/>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
-      <c r="I39" s="5"/>
-      <c r="J39" s="5"/>
-      <c r="K39" s="5"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9"/>
+      <c r="K39" s="9"/>
       <c r="L39" s="7"/>
       <c r="M39" s="7"/>
-      <c r="N39" s="4"/>
-      <c r="O39" s="4"/>
-      <c r="P39" s="4"/>
-      <c r="Q39" s="4"/>
-      <c r="R39" s="4"/>
-      <c r="S39" s="4"/>
-      <c r="T39" s="4"/>
-      <c r="U39" s="4"/>
-      <c r="V39" s="4"/>
-      <c r="W39" s="4"/>
-      <c r="X39" s="4"/>
+      <c r="O39" s="9"/>
+      <c r="P39" s="9"/>
+      <c r="Q39" s="9"/>
+      <c r="R39" s="9"/>
+      <c r="S39" s="9"/>
+      <c r="T39" s="9"/>
+      <c r="U39" s="9"/>
+      <c r="V39" s="9"/>
+      <c r="W39" s="9"/>
+      <c r="X39" s="9"/>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A40" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="3">
-        <v>46286</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E40" s="3">
-        <v>46287</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G40" s="3">
-        <v>46288</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I40" s="3">
-        <v>46289</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="K40" s="3">
-        <v>46290</v>
-      </c>
+      <c r="A40" s="5"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
       <c r="L40" s="7"/>
       <c r="M40" s="7"/>
-      <c r="N40" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="O40" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P40" s="3">
-        <v>46307</v>
-      </c>
-      <c r="Q40" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="R40" s="3">
-        <v>46308</v>
-      </c>
-      <c r="S40" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T40" s="3">
-        <v>46309</v>
-      </c>
-      <c r="U40" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="V40" s="3">
-        <v>46310</v>
-      </c>
-      <c r="W40" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="X40" s="3">
-        <v>46311</v>
-      </c>
+      <c r="N40" s="4"/>
+      <c r="O40" s="4"/>
+      <c r="P40" s="4"/>
+      <c r="Q40" s="4"/>
+      <c r="R40" s="4"/>
+      <c r="S40" s="4"/>
+      <c r="T40" s="4"/>
+      <c r="U40" s="4"/>
+      <c r="V40" s="4"/>
+      <c r="W40" s="4"/>
+      <c r="X40" s="4"/>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B41" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="C41" s="39"/>
-      <c r="D41" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="E41" s="39"/>
-      <c r="F41" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="G41" s="39"/>
-      <c r="H41" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I41" s="39"/>
-      <c r="J41" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K41" s="39"/>
+        <v>303</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" s="3">
+        <v>46286</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E41" s="3">
+        <v>46287</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G41" s="3">
+        <v>46288</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I41" s="3">
+        <v>46289</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K41" s="3">
+        <v>46290</v>
+      </c>
       <c r="L41" s="7"/>
       <c r="M41" s="7"/>
       <c r="N41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="O41" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="P41" s="39"/>
-      <c r="Q41" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="R41" s="39"/>
-      <c r="S41" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="T41" s="39"/>
-      <c r="U41" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="V41" s="39"/>
-      <c r="W41" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="X41" s="39"/>
+        <v>304</v>
+      </c>
+      <c r="O41" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P41" s="3">
+        <v>46307</v>
+      </c>
+      <c r="Q41" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="R41" s="3">
+        <v>46308</v>
+      </c>
+      <c r="S41" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T41" s="3">
+        <v>46309</v>
+      </c>
+      <c r="U41" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="V41" s="3">
+        <v>46310</v>
+      </c>
+      <c r="W41" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="X41" s="3">
+        <v>46311</v>
+      </c>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B42" s="24" t="s">
-        <v>292</v>
-      </c>
-      <c r="C42" s="25"/>
-      <c r="D42" s="24" t="s">
-        <v>292</v>
-      </c>
-      <c r="E42" s="25"/>
-      <c r="F42" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="G42" s="21"/>
-      <c r="H42" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="I42" s="41"/>
-      <c r="J42" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="K42" s="41"/>
+        <v>7</v>
+      </c>
+      <c r="B42" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="39"/>
+      <c r="D42" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" s="39"/>
+      <c r="F42" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="G42" s="39"/>
+      <c r="H42" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="I42" s="39"/>
+      <c r="J42" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="K42" s="39"/>
       <c r="L42" s="7"/>
       <c r="M42" s="7"/>
       <c r="N42" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="O42" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="P42" s="37"/>
-      <c r="Q42" s="36" t="s">
-        <v>305</v>
-      </c>
-      <c r="R42" s="37"/>
-      <c r="S42" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="T42" s="37"/>
-      <c r="U42" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="V42" s="21"/>
-      <c r="W42" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="X42" s="21"/>
+        <v>7</v>
+      </c>
+      <c r="O42" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="P42" s="39"/>
+      <c r="Q42" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="R42" s="39"/>
+      <c r="S42" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="T42" s="39"/>
+      <c r="U42" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="V42" s="39"/>
+      <c r="W42" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="X42" s="39"/>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" s="26" t="s">
-        <v>295</v>
-      </c>
-      <c r="C43" s="27"/>
-      <c r="D43" s="26" t="s">
-        <v>295</v>
-      </c>
-      <c r="E43" s="27"/>
+        <v>10</v>
+      </c>
+      <c r="B43" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="C43" s="25"/>
+      <c r="D43" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="E43" s="25"/>
       <c r="F43" s="20" t="s">
         <v>9</v>
       </c>
       <c r="G43" s="21"/>
-      <c r="H43" s="26" t="s">
-        <v>295</v>
-      </c>
-      <c r="I43" s="27"/>
-      <c r="J43" s="24" t="s">
-        <v>293</v>
-      </c>
-      <c r="K43" s="25"/>
+      <c r="H43" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="I43" s="41"/>
+      <c r="J43" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="K43" s="41"/>
       <c r="L43" s="7"/>
       <c r="M43" s="7"/>
       <c r="N43" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="O43" s="36" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="P43" s="37"/>
       <c r="Q43" s="36" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R43" s="37"/>
       <c r="S43" s="36" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="T43" s="37"/>
-      <c r="U43" s="54" t="s">
-        <v>307</v>
-      </c>
-      <c r="V43" s="55"/>
+      <c r="U43" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="V43" s="21"/>
       <c r="W43" s="20" t="s">
         <v>9</v>
       </c>
@@ -22748,619 +22718,644 @@
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B44" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="C44" s="25"/>
-      <c r="D44" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="E44" s="25"/>
-      <c r="F44" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="G44" s="25"/>
-      <c r="H44" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="I44" s="25"/>
+        <v>15</v>
+      </c>
+      <c r="B44" s="26" t="s">
+        <v>295</v>
+      </c>
+      <c r="C44" s="27"/>
+      <c r="D44" s="26" t="s">
+        <v>295</v>
+      </c>
+      <c r="E44" s="27"/>
+      <c r="F44" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="G44" s="21"/>
+      <c r="H44" s="26" t="s">
+        <v>295</v>
+      </c>
+      <c r="I44" s="27"/>
       <c r="J44" s="24" t="s">
-        <v>65</v>
+        <v>293</v>
       </c>
       <c r="K44" s="25"/>
       <c r="L44" s="7"/>
       <c r="M44" s="7"/>
       <c r="N44" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O44" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="P44" s="27"/>
-      <c r="Q44" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="R44" s="27"/>
-      <c r="S44" s="22" t="s">
-        <v>308</v>
-      </c>
-      <c r="T44" s="23"/>
+        <v>15</v>
+      </c>
+      <c r="O44" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="P44" s="37"/>
+      <c r="Q44" s="36" t="s">
+        <v>306</v>
+      </c>
+      <c r="R44" s="37"/>
+      <c r="S44" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="T44" s="37"/>
       <c r="U44" s="54" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="V44" s="55"/>
-      <c r="W44" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="X44" s="37"/>
+      <c r="W44" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="X44" s="21"/>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B45" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="C45" s="25"/>
+      <c r="D45" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="E45" s="25"/>
+      <c r="F45" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="G45" s="25"/>
+      <c r="H45" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="I45" s="25"/>
+      <c r="J45" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="K45" s="25"/>
+      <c r="L45" s="7"/>
+      <c r="M45" s="7"/>
+      <c r="N45" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O45" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="P45" s="27"/>
+      <c r="Q45" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="R45" s="27"/>
+      <c r="S45" s="22" t="s">
+        <v>308</v>
+      </c>
+      <c r="T45" s="23"/>
+      <c r="U45" s="54" t="s">
+        <v>309</v>
+      </c>
+      <c r="V45" s="55"/>
+      <c r="W45" s="36" t="s">
+        <v>277</v>
+      </c>
+      <c r="X45" s="37"/>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B45" s="46" t="s">
+      <c r="B46" s="46" t="s">
         <v>288</v>
       </c>
-      <c r="C45" s="47"/>
-      <c r="D45" s="44" t="s">
+      <c r="C46" s="47"/>
+      <c r="D46" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="E45" s="45"/>
-      <c r="F45" s="44" t="s">
+      <c r="E46" s="45"/>
+      <c r="F46" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="G45" s="45"/>
-      <c r="H45" s="28" t="s">
+      <c r="G46" s="45"/>
+      <c r="H46" s="28" t="s">
         <v>253</v>
       </c>
-      <c r="I45" s="29"/>
-      <c r="J45" s="44" t="s">
+      <c r="I46" s="29"/>
+      <c r="J46" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="K45" s="45"/>
-      <c r="N45" s="1" t="s">
+      <c r="K46" s="45"/>
+      <c r="N46" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="O45" s="44" t="s">
+      <c r="O46" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="P45" s="45"/>
-      <c r="Q45" s="44" t="s">
+      <c r="P46" s="45"/>
+      <c r="Q46" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="R45" s="45"/>
-      <c r="S45" s="44" t="s">
+      <c r="R46" s="45"/>
+      <c r="S46" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="T45" s="45"/>
-      <c r="U45" s="44" t="s">
+      <c r="T46" s="45"/>
+      <c r="U46" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="V45" s="45"/>
-      <c r="W45" s="44" t="s">
+      <c r="V46" s="45"/>
+      <c r="W46" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="X45" s="45"/>
-    </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B46" s="46" t="s">
-        <v>287</v>
-      </c>
-      <c r="C46" s="47"/>
-      <c r="D46" s="46" t="s">
-        <v>287</v>
-      </c>
-      <c r="E46" s="47"/>
-      <c r="F46" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="G46" s="21"/>
-      <c r="H46" s="46" t="s">
-        <v>288</v>
-      </c>
-      <c r="I46" s="47"/>
-      <c r="J46" s="34" t="s">
-        <v>310</v>
-      </c>
-      <c r="K46" s="35"/>
-      <c r="N46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O46" s="34" t="s">
-        <v>311</v>
-      </c>
-      <c r="P46" s="35"/>
-      <c r="Q46" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="R46" s="35"/>
-      <c r="S46" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="T46" s="35"/>
-      <c r="U46" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="V46" s="35"/>
-      <c r="W46" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="X46" s="35"/>
+      <c r="X46" s="45"/>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B47" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="C47" s="27"/>
-      <c r="D47" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="E47" s="27"/>
-      <c r="F47" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="G47" s="37"/>
-      <c r="H47" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="I47" s="27"/>
-      <c r="J47" s="24" t="s">
-        <v>292</v>
-      </c>
-      <c r="K47" s="25"/>
+        <v>26</v>
+      </c>
+      <c r="B47" s="46" t="s">
+        <v>287</v>
+      </c>
+      <c r="C47" s="47"/>
+      <c r="D47" s="46" t="s">
+        <v>287</v>
+      </c>
+      <c r="E47" s="47"/>
+      <c r="F47" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="G47" s="21"/>
+      <c r="H47" s="46" t="s">
+        <v>288</v>
+      </c>
+      <c r="I47" s="47"/>
+      <c r="J47" s="34" t="s">
+        <v>310</v>
+      </c>
+      <c r="K47" s="35"/>
       <c r="N47" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O47" s="26" t="s">
-        <v>295</v>
-      </c>
-      <c r="P47" s="27"/>
-      <c r="Q47" s="26" t="s">
-        <v>295</v>
-      </c>
-      <c r="R47" s="27"/>
+        <v>26</v>
+      </c>
+      <c r="O47" s="34" t="s">
+        <v>311</v>
+      </c>
+      <c r="P47" s="35"/>
+      <c r="Q47" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R47" s="35"/>
       <c r="S47" s="34" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="T47" s="35"/>
       <c r="U47" s="34" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="V47" s="35"/>
-      <c r="W47" s="40" t="s">
-        <v>20</v>
-      </c>
-      <c r="X47" s="41"/>
+      <c r="W47" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X47" s="35"/>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B48" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="C48" s="37"/>
-      <c r="D48" s="28" t="s">
-        <v>253</v>
-      </c>
-      <c r="E48" s="29"/>
+        <v>28</v>
+      </c>
+      <c r="B48" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="C48" s="27"/>
+      <c r="D48" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="E48" s="27"/>
       <c r="F48" s="36" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="G48" s="37"/>
-      <c r="H48" s="46" t="s">
-        <v>288</v>
-      </c>
-      <c r="I48" s="47"/>
-      <c r="J48" s="46" t="s">
-        <v>287</v>
-      </c>
-      <c r="K48" s="47"/>
+      <c r="H48" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="I48" s="27"/>
+      <c r="J48" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="K48" s="25"/>
       <c r="N48" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="O48" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="P48" s="21"/>
-      <c r="Q48" s="54" t="s">
-        <v>307</v>
-      </c>
-      <c r="R48" s="55"/>
-      <c r="S48" s="54" t="s">
-        <v>307</v>
-      </c>
-      <c r="T48" s="55"/>
-      <c r="U48" s="46" t="s">
-        <v>312</v>
-      </c>
-      <c r="V48" s="47"/>
-      <c r="W48" s="54" t="s">
-        <v>307</v>
-      </c>
-      <c r="X48" s="55"/>
+        <v>28</v>
+      </c>
+      <c r="O48" s="26" t="s">
+        <v>295</v>
+      </c>
+      <c r="P48" s="27"/>
+      <c r="Q48" s="26" t="s">
+        <v>295</v>
+      </c>
+      <c r="R48" s="27"/>
+      <c r="S48" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="T48" s="35"/>
+      <c r="U48" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="V48" s="35"/>
+      <c r="W48" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="X48" s="41"/>
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B49" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="C49" s="37"/>
+      <c r="D49" s="28" t="s">
+        <v>253</v>
+      </c>
+      <c r="E49" s="29"/>
+      <c r="F49" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="G49" s="37"/>
+      <c r="H49" s="46" t="s">
+        <v>288</v>
+      </c>
+      <c r="I49" s="47"/>
+      <c r="J49" s="46" t="s">
+        <v>287</v>
+      </c>
+      <c r="K49" s="47"/>
+      <c r="N49" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="O49" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="P49" s="21"/>
+      <c r="Q49" s="54" t="s">
+        <v>307</v>
+      </c>
+      <c r="R49" s="55"/>
+      <c r="S49" s="54" t="s">
+        <v>307</v>
+      </c>
+      <c r="T49" s="55"/>
+      <c r="U49" s="46" t="s">
+        <v>312</v>
+      </c>
+      <c r="V49" s="47"/>
+      <c r="W49" s="54" t="s">
+        <v>307</v>
+      </c>
+      <c r="X49" s="55"/>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A50" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B49" s="24" t="s">
+      <c r="B50" s="24" t="s">
         <v>293</v>
       </c>
-      <c r="C49" s="25"/>
-      <c r="D49" s="24" t="s">
+      <c r="C50" s="25"/>
+      <c r="D50" s="24" t="s">
         <v>293</v>
       </c>
-      <c r="E49" s="25"/>
-      <c r="F49" s="44" t="s">
+      <c r="E50" s="25"/>
+      <c r="F50" s="44" t="s">
         <v>313</v>
       </c>
-      <c r="G49" s="45"/>
-      <c r="H49" s="46" t="s">
+      <c r="G50" s="45"/>
+      <c r="H50" s="46" t="s">
         <v>287</v>
       </c>
-      <c r="I49" s="47"/>
-      <c r="J49" s="44" t="s">
+      <c r="I50" s="47"/>
+      <c r="J50" s="44" t="s">
         <v>313</v>
       </c>
-      <c r="K49" s="45"/>
-      <c r="N49" s="6" t="s">
+      <c r="K50" s="45"/>
+      <c r="N50" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="O49" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="P49" s="41"/>
-      <c r="Q49" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="R49" s="41"/>
-      <c r="S49" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="T49" s="41"/>
-      <c r="U49" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="V49" s="41"/>
-      <c r="W49" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="X49" s="41"/>
-    </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A50" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B50" s="28" t="s">
-        <v>254</v>
-      </c>
-      <c r="C50" s="29"/>
-      <c r="D50" s="28" t="s">
-        <v>254</v>
-      </c>
-      <c r="E50" s="29"/>
-      <c r="F50" s="28" t="s">
-        <v>254</v>
-      </c>
-      <c r="G50" s="29"/>
-      <c r="H50" s="28" t="s">
-        <v>254</v>
-      </c>
-      <c r="I50" s="29"/>
-      <c r="J50" s="46" t="s">
-        <v>288</v>
-      </c>
-      <c r="K50" s="47"/>
-      <c r="N50" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="O50" s="34" t="s">
-        <v>124</v>
-      </c>
-      <c r="P50" s="35"/>
-      <c r="Q50" s="54" t="s">
-        <v>309</v>
-      </c>
-      <c r="R50" s="55"/>
-      <c r="S50" s="54" t="s">
-        <v>309</v>
-      </c>
-      <c r="T50" s="55"/>
-      <c r="U50" s="46" t="s">
-        <v>314</v>
-      </c>
-      <c r="V50" s="47"/>
-      <c r="W50" s="54" t="s">
-        <v>309</v>
-      </c>
-      <c r="X50" s="55"/>
+      <c r="O50" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="P50" s="41"/>
+      <c r="Q50" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="R50" s="41"/>
+      <c r="S50" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="T50" s="41"/>
+      <c r="U50" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="V50" s="41"/>
+      <c r="W50" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="X50" s="41"/>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B51" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="C51" s="37"/>
-      <c r="D51" s="46" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" s="28" t="s">
+        <v>254</v>
+      </c>
+      <c r="C51" s="29"/>
+      <c r="D51" s="28" t="s">
+        <v>254</v>
+      </c>
+      <c r="E51" s="29"/>
+      <c r="F51" s="28" t="s">
+        <v>254</v>
+      </c>
+      <c r="G51" s="29"/>
+      <c r="H51" s="28" t="s">
+        <v>254</v>
+      </c>
+      <c r="I51" s="29"/>
+      <c r="J51" s="46" t="s">
         <v>288</v>
       </c>
-      <c r="E51" s="47"/>
-      <c r="F51" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="G51" s="45"/>
-      <c r="H51" s="46" t="s">
-        <v>288</v>
-      </c>
-      <c r="I51" s="47"/>
-      <c r="J51" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="K51" s="45"/>
+      <c r="K51" s="47"/>
       <c r="N51" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O51" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="P51" s="45"/>
-      <c r="Q51" s="34" t="s">
-        <v>301</v>
-      </c>
-      <c r="R51" s="35"/>
-      <c r="S51" s="34" t="s">
-        <v>301</v>
-      </c>
-      <c r="T51" s="35"/>
+        <v>37</v>
+      </c>
+      <c r="O51" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="P51" s="35"/>
+      <c r="Q51" s="54" t="s">
+        <v>309</v>
+      </c>
+      <c r="R51" s="55"/>
+      <c r="S51" s="54" t="s">
+        <v>309</v>
+      </c>
+      <c r="T51" s="55"/>
       <c r="U51" s="46" t="s">
         <v>314</v>
       </c>
       <c r="V51" s="47"/>
-      <c r="W51" s="44" t="s">
+      <c r="W51" s="54" t="s">
+        <v>309</v>
+      </c>
+      <c r="X51" s="55"/>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A52" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B52" s="36" t="s">
+        <v>277</v>
+      </c>
+      <c r="C52" s="37"/>
+      <c r="D52" s="46" t="s">
+        <v>288</v>
+      </c>
+      <c r="E52" s="47"/>
+      <c r="F52" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="X51" s="45"/>
-    </row>
-    <row r="52" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="22" t="s">
-        <v>285</v>
-      </c>
-      <c r="C52" s="23"/>
-      <c r="D52" s="22" t="s">
-        <v>285</v>
-      </c>
-      <c r="E52" s="23"/>
-      <c r="F52" s="24" t="s">
-        <v>293</v>
-      </c>
-      <c r="G52" s="25"/>
-      <c r="H52" s="24" t="s">
-        <v>293</v>
-      </c>
-      <c r="I52" s="25"/>
-      <c r="J52" s="34" t="s">
-        <v>315</v>
-      </c>
-      <c r="K52" s="35"/>
-      <c r="N52" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="O52" s="34" t="s">
-        <v>316</v>
-      </c>
-      <c r="P52" s="35"/>
+      <c r="G52" s="45"/>
+      <c r="H52" s="46" t="s">
+        <v>288</v>
+      </c>
+      <c r="I52" s="47"/>
+      <c r="J52" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="K52" s="45"/>
+      <c r="N52" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O52" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="P52" s="45"/>
       <c r="Q52" s="34" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="R52" s="35"/>
       <c r="S52" s="34" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="T52" s="35"/>
-      <c r="U52" s="34" t="s">
-        <v>300</v>
-      </c>
-      <c r="V52" s="35"/>
-      <c r="W52" s="34" t="s">
-        <v>300</v>
-      </c>
-      <c r="X52" s="35"/>
-    </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A53" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B53" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="C53" s="25"/>
-      <c r="D53" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="E53" s="25"/>
+      <c r="U52" s="46" t="s">
+        <v>314</v>
+      </c>
+      <c r="V52" s="47"/>
+      <c r="W52" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="X52" s="45"/>
+    </row>
+    <row r="53" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B53" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="C53" s="23"/>
+      <c r="D53" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="E53" s="23"/>
       <c r="F53" s="24" t="s">
-        <v>68</v>
+        <v>293</v>
       </c>
       <c r="G53" s="25"/>
       <c r="H53" s="24" t="s">
-        <v>68</v>
+        <v>293</v>
       </c>
       <c r="I53" s="25"/>
-      <c r="J53" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="K53" s="25"/>
-      <c r="N53" s="1" t="s">
-        <v>48</v>
+      <c r="J53" s="34" t="s">
+        <v>315</v>
+      </c>
+      <c r="K53" s="35"/>
+      <c r="N53" s="12" t="s">
+        <v>45</v>
       </c>
       <c r="O53" s="34" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="P53" s="35"/>
       <c r="Q53" s="34" t="s">
-        <v>103</v>
+        <v>300</v>
       </c>
       <c r="R53" s="35"/>
       <c r="S53" s="34" t="s">
-        <v>103</v>
+        <v>300</v>
       </c>
       <c r="T53" s="35"/>
       <c r="U53" s="34" t="s">
-        <v>103</v>
+        <v>300</v>
       </c>
       <c r="V53" s="35"/>
       <c r="W53" s="34" t="s">
-        <v>103</v>
+        <v>300</v>
       </c>
       <c r="X53" s="35"/>
     </row>
     <row r="54" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A54" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B54" s="46" t="s">
-        <v>288</v>
-      </c>
-      <c r="C54" s="47"/>
-      <c r="D54" s="46" t="s">
-        <v>288</v>
-      </c>
-      <c r="E54" s="47"/>
+      <c r="A54" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B54" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="C54" s="25"/>
+      <c r="D54" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="E54" s="25"/>
       <c r="F54" s="24" t="s">
-        <v>292</v>
+        <v>68</v>
       </c>
       <c r="G54" s="25"/>
       <c r="H54" s="24" t="s">
-        <v>292</v>
+        <v>68</v>
       </c>
       <c r="I54" s="25"/>
-      <c r="J54" s="46" t="s">
-        <v>288</v>
-      </c>
-      <c r="K54" s="47"/>
-      <c r="N54" s="12" t="s">
-        <v>49</v>
+      <c r="J54" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="K54" s="25"/>
+      <c r="N54" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="O54" s="34" t="s">
-        <v>142</v>
+        <v>311</v>
       </c>
       <c r="P54" s="35"/>
       <c r="Q54" s="34" t="s">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="R54" s="35"/>
       <c r="S54" s="34" t="s">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="T54" s="35"/>
       <c r="U54" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="V54" s="35"/>
+      <c r="W54" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="X54" s="35"/>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A55" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B55" s="46" t="s">
+        <v>288</v>
+      </c>
+      <c r="C55" s="47"/>
+      <c r="D55" s="46" t="s">
+        <v>288</v>
+      </c>
+      <c r="E55" s="47"/>
+      <c r="F55" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="G55" s="25"/>
+      <c r="H55" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="I55" s="25"/>
+      <c r="J55" s="46" t="s">
+        <v>288</v>
+      </c>
+      <c r="K55" s="47"/>
+      <c r="N55" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="O55" s="34" t="s">
         <v>142</v>
-      </c>
-      <c r="V54" s="35"/>
-      <c r="W54" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="X54" s="37"/>
-    </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A55" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B55" s="28" t="s">
-        <v>253</v>
-      </c>
-      <c r="C55" s="29"/>
-      <c r="D55" s="28" t="s">
-        <v>253</v>
-      </c>
-      <c r="E55" s="29"/>
-      <c r="F55" s="28" t="s">
-        <v>253</v>
-      </c>
-      <c r="G55" s="29"/>
-      <c r="H55" s="28" t="s">
-        <v>253</v>
-      </c>
-      <c r="I55" s="29"/>
-      <c r="J55" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="K55" s="21"/>
-      <c r="N55" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="O55" s="34" t="s">
-        <v>124</v>
       </c>
       <c r="P55" s="35"/>
       <c r="Q55" s="34" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="R55" s="35"/>
       <c r="S55" s="34" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="T55" s="35"/>
       <c r="U55" s="34" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="V55" s="35"/>
-      <c r="W55" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="X55" s="21"/>
+      <c r="W55" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="X55" s="37"/>
     </row>
     <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B56" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="C56" s="23"/>
-      <c r="D56" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="E56" s="23"/>
-      <c r="F56" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="G56" s="23"/>
-      <c r="H56" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="I56" s="23"/>
-      <c r="J56" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="K56" s="23"/>
-      <c r="S56" s="22" t="s">
-        <v>357</v>
-      </c>
-      <c r="T56" s="23"/>
+        <v>50</v>
+      </c>
+      <c r="B56" s="28" t="s">
+        <v>253</v>
+      </c>
+      <c r="C56" s="29"/>
+      <c r="D56" s="28" t="s">
+        <v>253</v>
+      </c>
+      <c r="E56" s="29"/>
+      <c r="F56" s="28" t="s">
+        <v>253</v>
+      </c>
+      <c r="G56" s="29"/>
+      <c r="H56" s="28" t="s">
+        <v>253</v>
+      </c>
+      <c r="I56" s="29"/>
+      <c r="J56" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="K56" s="21"/>
+      <c r="N56" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O56" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="P56" s="35"/>
+      <c r="Q56" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="R56" s="35"/>
+      <c r="S56" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="T56" s="35"/>
+      <c r="U56" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="V56" s="35"/>
+      <c r="W56" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="X56" s="21"/>
     </row>
     <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B57" s="20"/>
-      <c r="C57" s="21"/>
-      <c r="D57" s="20"/>
-      <c r="E57" s="21"/>
+      <c r="B57" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="C57" s="23"/>
+      <c r="D57" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="E57" s="23"/>
       <c r="F57" s="22" t="s">
         <v>289</v>
       </c>
@@ -23373,79 +23368,91 @@
         <v>289</v>
       </c>
       <c r="K57" s="23"/>
+      <c r="S57" s="22" t="s">
+        <v>357</v>
+      </c>
+      <c r="T57" s="23"/>
     </row>
     <row r="58" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A58" s="7"/>
+      <c r="A58" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B58" s="20"/>
+      <c r="C58" s="21"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="21"/>
+      <c r="F58" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="G58" s="23"/>
+      <c r="H58" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="I58" s="23"/>
+      <c r="J58" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="K58" s="23"/>
     </row>
     <row r="59" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A59" s="5">
-        <v>1</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="G59" s="5">
-        <v>5</v>
-      </c>
-      <c r="H59" s="5" t="s">
-        <v>80</v>
-      </c>
+      <c r="A59" s="7"/>
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="5">
+        <v>1</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="G60" s="5">
+        <v>5</v>
+      </c>
+      <c r="H60" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A61" s="5">
         <v>2</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B61" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="G60" s="8">
+      <c r="G61" s="8">
         <v>6</v>
       </c>
-      <c r="H60" s="4" t="s">
+      <c r="H61" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A61" s="8">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A62" s="8">
         <v>3</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B62" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C61" s="5"/>
-      <c r="G61" s="8">
-        <v>9</v>
-      </c>
-      <c r="H61" s="4" t="s">
+      <c r="C62" s="5"/>
+      <c r="G62" s="8">
+        <v>9</v>
+      </c>
+      <c r="H62" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A62" s="5">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A63" s="5">
         <v>4</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B63" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A63" s="5"/>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-    </row>
-    <row r="64" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="N64" s="5"/>
-      <c r="O64" s="5"/>
-      <c r="P64" s="5"/>
-      <c r="Q64" s="5"/>
-      <c r="R64" s="5"/>
-      <c r="S64" s="5"/>
-      <c r="T64" s="5"/>
-      <c r="U64" s="5"/>
-      <c r="V64" s="5"/>
-      <c r="W64" s="5"/>
-      <c r="X64" s="5"/>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A64" s="5"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
     </row>
     <row r="65" spans="14:24" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="N65" s="5"/>
@@ -23473,78 +23480,83 @@
       <c r="W66" s="5"/>
       <c r="X66" s="5"/>
     </row>
+    <row r="67" spans="14:24" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="N67" s="5"/>
+      <c r="O67" s="5"/>
+      <c r="P67" s="5"/>
+      <c r="Q67" s="5"/>
+      <c r="R67" s="5"/>
+      <c r="S67" s="5"/>
+      <c r="T67" s="5"/>
+      <c r="U67" s="5"/>
+      <c r="V67" s="5"/>
+      <c r="W67" s="5"/>
+      <c r="X67" s="5"/>
+    </row>
   </sheetData>
-  <mergeCells count="469">
+  <sheetProtection algorithmName="SHA-512" hashValue="7zuI8mtWLJ0cScQwaPEdRbqs3lZltpHs7fVjc6L7FE0EMqqNROKy1N67vCgF50xpx3CviHjfJYLJHroahPJ6MA==" saltValue="xq6xrbFAO028DRwVvfxKsQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="470">
     <mergeCell ref="Q17:R17"/>
     <mergeCell ref="O8:P8"/>
+    <mergeCell ref="S19:T19"/>
     <mergeCell ref="S18:T18"/>
-    <mergeCell ref="S56:T56"/>
+    <mergeCell ref="S57:T57"/>
+    <mergeCell ref="W55:X55"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="J55:K55"/>
+    <mergeCell ref="O55:P55"/>
+    <mergeCell ref="Q55:R55"/>
+    <mergeCell ref="S55:T55"/>
+    <mergeCell ref="U55:V55"/>
+    <mergeCell ref="S49:T49"/>
+    <mergeCell ref="U54:V54"/>
     <mergeCell ref="W54:X54"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="O54:P54"/>
+    <mergeCell ref="S54:T54"/>
+    <mergeCell ref="Q48:R48"/>
+    <mergeCell ref="S48:T48"/>
+    <mergeCell ref="U48:V48"/>
+    <mergeCell ref="W53:X53"/>
+    <mergeCell ref="Q54:R54"/>
+    <mergeCell ref="S53:T53"/>
+    <mergeCell ref="U53:V53"/>
+    <mergeCell ref="W52:X52"/>
+    <mergeCell ref="W50:X50"/>
+    <mergeCell ref="S52:T52"/>
+    <mergeCell ref="U52:V52"/>
+    <mergeCell ref="Q50:R50"/>
+    <mergeCell ref="S50:T50"/>
+    <mergeCell ref="U50:V50"/>
+    <mergeCell ref="S51:T51"/>
     <mergeCell ref="B54:C54"/>
     <mergeCell ref="D54:E54"/>
     <mergeCell ref="F54:G54"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="J54:K54"/>
-    <mergeCell ref="O54:P54"/>
-    <mergeCell ref="Q54:R54"/>
-    <mergeCell ref="S54:T54"/>
-    <mergeCell ref="U54:V54"/>
-    <mergeCell ref="S48:T48"/>
-    <mergeCell ref="U53:V53"/>
-    <mergeCell ref="W53:X53"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="J53:K53"/>
-    <mergeCell ref="O53:P53"/>
-    <mergeCell ref="S53:T53"/>
-    <mergeCell ref="Q47:R47"/>
-    <mergeCell ref="S47:T47"/>
-    <mergeCell ref="U47:V47"/>
-    <mergeCell ref="W52:X52"/>
-    <mergeCell ref="Q53:R53"/>
-    <mergeCell ref="S52:T52"/>
-    <mergeCell ref="U52:V52"/>
-    <mergeCell ref="W51:X51"/>
-    <mergeCell ref="W49:X49"/>
-    <mergeCell ref="S51:T51"/>
-    <mergeCell ref="U51:V51"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="Q42:R42"/>
     <mergeCell ref="Q49:R49"/>
-    <mergeCell ref="S49:T49"/>
-    <mergeCell ref="U49:V49"/>
-    <mergeCell ref="S50:T50"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="Q41:R41"/>
-    <mergeCell ref="Q48:R48"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="O49:P49"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="O46:P46"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="J47:K47"/>
+    <mergeCell ref="J44:K44"/>
+    <mergeCell ref="O45:P45"/>
+    <mergeCell ref="Q45:R45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="D47:E47"/>
     <mergeCell ref="B47:C47"/>
-    <mergeCell ref="O48:P48"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="O45:P45"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="H46:I46"/>
     <mergeCell ref="J46:K46"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="O44:P44"/>
-    <mergeCell ref="Q44:R44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="Q42:R42"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="J50:K50"/>
-    <mergeCell ref="O50:P50"/>
-    <mergeCell ref="Q50:R50"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="Q43:R43"/>
+    <mergeCell ref="B49:C49"/>
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="D51:E51"/>
     <mergeCell ref="F51:G51"/>
@@ -23552,172 +23564,182 @@
     <mergeCell ref="J51:K51"/>
     <mergeCell ref="O51:P51"/>
     <mergeCell ref="Q51:R51"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="F52:G52"/>
     <mergeCell ref="H52:I52"/>
     <mergeCell ref="J52:K52"/>
     <mergeCell ref="O52:P52"/>
     <mergeCell ref="Q52:R52"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="U48:V48"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="J53:K53"/>
+    <mergeCell ref="O53:P53"/>
+    <mergeCell ref="Q53:R53"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="U49:V49"/>
+    <mergeCell ref="W49:X49"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="U51:V51"/>
+    <mergeCell ref="W51:X51"/>
     <mergeCell ref="W48:X48"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="U50:V50"/>
-    <mergeCell ref="W50:X50"/>
-    <mergeCell ref="W47:X47"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="Q35:R35"/>
-    <mergeCell ref="S35:T35"/>
-    <mergeCell ref="S41:T41"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="J47:K47"/>
-    <mergeCell ref="O47:P47"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="J49:K49"/>
-    <mergeCell ref="O49:P49"/>
+    <mergeCell ref="O42:P42"/>
+    <mergeCell ref="Q36:R36"/>
+    <mergeCell ref="S36:T36"/>
+    <mergeCell ref="S42:T42"/>
     <mergeCell ref="D48:E48"/>
     <mergeCell ref="F48:G48"/>
     <mergeCell ref="H48:I48"/>
     <mergeCell ref="J48:K48"/>
-    <mergeCell ref="W27:X27"/>
-    <mergeCell ref="U26:V26"/>
+    <mergeCell ref="O48:P48"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="J50:K50"/>
+    <mergeCell ref="O50:P50"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="J49:K49"/>
+    <mergeCell ref="W28:X28"/>
     <mergeCell ref="U27:V27"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="U28:V28"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="W46:X46"/>
+    <mergeCell ref="O47:P47"/>
+    <mergeCell ref="Q47:R47"/>
+    <mergeCell ref="Q46:R46"/>
+    <mergeCell ref="S46:T46"/>
+    <mergeCell ref="W47:X47"/>
+    <mergeCell ref="U46:V46"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="S43:T43"/>
+    <mergeCell ref="O43:P43"/>
+    <mergeCell ref="U42:V42"/>
+    <mergeCell ref="U30:V30"/>
+    <mergeCell ref="W36:X36"/>
+    <mergeCell ref="W32:X32"/>
+    <mergeCell ref="W31:X31"/>
     <mergeCell ref="W45:X45"/>
-    <mergeCell ref="O46:P46"/>
-    <mergeCell ref="Q46:R46"/>
-    <mergeCell ref="Q45:R45"/>
+    <mergeCell ref="W43:X43"/>
     <mergeCell ref="S45:T45"/>
-    <mergeCell ref="W46:X46"/>
-    <mergeCell ref="U45:V45"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="Q34:R34"/>
-    <mergeCell ref="S42:T42"/>
-    <mergeCell ref="O42:P42"/>
-    <mergeCell ref="U41:V41"/>
-    <mergeCell ref="U29:V29"/>
+    <mergeCell ref="U43:V43"/>
     <mergeCell ref="W35:X35"/>
-    <mergeCell ref="W31:X31"/>
-    <mergeCell ref="W30:X30"/>
-    <mergeCell ref="W44:X44"/>
-    <mergeCell ref="W42:X42"/>
-    <mergeCell ref="S44:T44"/>
-    <mergeCell ref="U42:V42"/>
-    <mergeCell ref="W34:X34"/>
-    <mergeCell ref="Q32:R32"/>
-    <mergeCell ref="S32:T32"/>
-    <mergeCell ref="U32:V32"/>
-    <mergeCell ref="W32:X32"/>
-    <mergeCell ref="W36:X36"/>
-    <mergeCell ref="W33:X33"/>
-    <mergeCell ref="U46:V46"/>
-    <mergeCell ref="S28:T28"/>
-    <mergeCell ref="S26:T26"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="S27:T27"/>
-    <mergeCell ref="Q26:R26"/>
     <mergeCell ref="Q33:R33"/>
     <mergeCell ref="S33:T33"/>
+    <mergeCell ref="U33:V33"/>
+    <mergeCell ref="W33:X33"/>
+    <mergeCell ref="W37:X37"/>
+    <mergeCell ref="W34:X34"/>
+    <mergeCell ref="U47:V47"/>
+    <mergeCell ref="S29:T29"/>
+    <mergeCell ref="S27:T27"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="S28:T28"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="Q34:R34"/>
+    <mergeCell ref="S34:T34"/>
+    <mergeCell ref="U36:V36"/>
+    <mergeCell ref="S35:T35"/>
+    <mergeCell ref="S47:T47"/>
+    <mergeCell ref="U44:V44"/>
+    <mergeCell ref="U45:V45"/>
     <mergeCell ref="U35:V35"/>
-    <mergeCell ref="S34:T34"/>
-    <mergeCell ref="S46:T46"/>
-    <mergeCell ref="U43:V43"/>
-    <mergeCell ref="U44:V44"/>
+    <mergeCell ref="U32:V32"/>
     <mergeCell ref="U34:V34"/>
-    <mergeCell ref="U31:V31"/>
-    <mergeCell ref="U33:V33"/>
+    <mergeCell ref="H44:I44"/>
     <mergeCell ref="H43:I43"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="S30:T30"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="S31:T31"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:G31"/>
     <mergeCell ref="F42:G42"/>
-    <mergeCell ref="S29:T29"/>
-    <mergeCell ref="Q30:R30"/>
-    <mergeCell ref="S30:T30"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="S43:T43"/>
-    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="S44:T44"/>
+    <mergeCell ref="Q32:R32"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="S32:T32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:E33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="H33:I33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="S31:T31"/>
-    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="F32:G32"/>
     <mergeCell ref="H32:I32"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="O23:P23"/>
     <mergeCell ref="J31:K31"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="H30:I30"/>
     <mergeCell ref="O31:P31"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="O35:P35"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="O22:P22"/>
-    <mergeCell ref="J30:K30"/>
     <mergeCell ref="F29:G29"/>
     <mergeCell ref="H29:I29"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="H28:I28"/>
     <mergeCell ref="O30:P30"/>
     <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="Q30:R30"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="J26:K26"/>
     <mergeCell ref="J29:K29"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="O23:P23"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="O25:P25"/>
     <mergeCell ref="O28:P28"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="B27:C27"/>
     <mergeCell ref="D27:E27"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="O27:P27"/>
     <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="B25:C25"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D13:E13"/>
-    <mergeCell ref="H23:I23"/>
     <mergeCell ref="H24:I24"/>
+    <mergeCell ref="H25:I25"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="F9:G9"/>
     <mergeCell ref="H9:I9"/>
@@ -23736,13 +23758,13 @@
     <mergeCell ref="F15:G15"/>
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="F14:G14"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="H12:I12"/>
-    <mergeCell ref="B23:C23"/>
     <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="D15:E15"/>
@@ -23750,12 +23772,12 @@
     <mergeCell ref="H14:I14"/>
     <mergeCell ref="H13:I13"/>
     <mergeCell ref="B16:C16"/>
-    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="H16:I16"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
     <mergeCell ref="O14:P14"/>
     <mergeCell ref="Q14:R14"/>
     <mergeCell ref="S14:T14"/>
@@ -23785,11 +23807,11 @@
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="J2:K2"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="J23:K23"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B4:C4"/>
@@ -23853,27 +23875,27 @@
     <mergeCell ref="O4:P4"/>
     <mergeCell ref="S13:T13"/>
     <mergeCell ref="U13:V13"/>
-    <mergeCell ref="U30:V30"/>
-    <mergeCell ref="S25:T25"/>
-    <mergeCell ref="W29:X29"/>
+    <mergeCell ref="U31:V31"/>
+    <mergeCell ref="S26:T26"/>
+    <mergeCell ref="W30:X30"/>
     <mergeCell ref="Q16:R16"/>
     <mergeCell ref="U14:V14"/>
-    <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="S22:T22"/>
-    <mergeCell ref="U28:V28"/>
-    <mergeCell ref="U25:V25"/>
     <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="U23:V23"/>
-    <mergeCell ref="W23:X23"/>
-    <mergeCell ref="W25:X25"/>
-    <mergeCell ref="W28:X28"/>
+    <mergeCell ref="S23:T23"/>
+    <mergeCell ref="U29:V29"/>
+    <mergeCell ref="U26:V26"/>
+    <mergeCell ref="Q24:R24"/>
     <mergeCell ref="U24:V24"/>
     <mergeCell ref="W24:X24"/>
+    <mergeCell ref="W26:X26"/>
+    <mergeCell ref="W29:X29"/>
+    <mergeCell ref="U25:V25"/>
+    <mergeCell ref="W25:X25"/>
     <mergeCell ref="U16:V16"/>
     <mergeCell ref="W16:X16"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="S23:T23"/>
+    <mergeCell ref="Q26:R26"/>
     <mergeCell ref="S24:T24"/>
+    <mergeCell ref="S25:T25"/>
     <mergeCell ref="S17:T17"/>
     <mergeCell ref="W2:X2"/>
     <mergeCell ref="W7:X7"/>
@@ -23881,8 +23903,8 @@
     <mergeCell ref="U4:V4"/>
     <mergeCell ref="W4:X4"/>
     <mergeCell ref="U7:V7"/>
-    <mergeCell ref="W26:X26"/>
-    <mergeCell ref="W22:X22"/>
+    <mergeCell ref="W27:X27"/>
+    <mergeCell ref="W23:X23"/>
     <mergeCell ref="W15:X15"/>
     <mergeCell ref="W13:X13"/>
     <mergeCell ref="U15:V15"/>
@@ -23895,55 +23917,55 @@
     <mergeCell ref="W9:X9"/>
     <mergeCell ref="U8:V8"/>
     <mergeCell ref="U5:V5"/>
-    <mergeCell ref="U22:V22"/>
-    <mergeCell ref="W55:X55"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="Q36:R36"/>
-    <mergeCell ref="S36:T36"/>
-    <mergeCell ref="U36:V36"/>
-    <mergeCell ref="W41:X41"/>
-    <mergeCell ref="W43:X43"/>
-    <mergeCell ref="O43:P43"/>
-    <mergeCell ref="Q43:R43"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="H55:I55"/>
-    <mergeCell ref="J55:K55"/>
-    <mergeCell ref="O55:P55"/>
-    <mergeCell ref="Q55:R55"/>
-    <mergeCell ref="S55:T55"/>
-    <mergeCell ref="U55:V55"/>
-    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="U23:V23"/>
+    <mergeCell ref="W56:X56"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="O37:P37"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="S37:T37"/>
+    <mergeCell ref="U37:V37"/>
+    <mergeCell ref="W42:X42"/>
+    <mergeCell ref="W44:X44"/>
+    <mergeCell ref="O44:P44"/>
+    <mergeCell ref="Q44:R44"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="J56:K56"/>
+    <mergeCell ref="O56:P56"/>
+    <mergeCell ref="Q56:R56"/>
+    <mergeCell ref="S56:T56"/>
+    <mergeCell ref="U56:V56"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="J58:K58"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="J38:K38"/>
     <mergeCell ref="B57:C57"/>
     <mergeCell ref="D57:E57"/>
     <mergeCell ref="F57:G57"/>
     <mergeCell ref="H57:I57"/>
     <mergeCell ref="J57:K57"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="H56:I56"/>
-    <mergeCell ref="J56:K56"/>
-    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="J45:K45"/>
     <mergeCell ref="B44:C44"/>
     <mergeCell ref="D44:E44"/>
     <mergeCell ref="F44:G44"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="J44:K44"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="F43:G43"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -26566,6 +26588,7 @@
       <c r="C61" s="5"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="YDHEte83kyqnC7ZR9ZZfQ8IvzLa/yB09U8ekubMk9oqXavQ6mSamHW2xUAdkl+0SjTCISEffbjONY3nCIFpg5w==" saltValue="01uos7zOzt/rePlOmeoWGg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="451">
     <mergeCell ref="U43:V43"/>
     <mergeCell ref="B33:C33"/>

--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6638" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E48B34C3-A4DE-4758-8584-1D5552404B0C}"/>
+  <xr:revisionPtr revIDLastSave="6642" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63469F86-7A1C-455F-AD0C-A9F2C8F0DAEE}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Uke 1-6" sheetId="7" r:id="rId1"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4793" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4798" uniqueCount="362">
   <si>
     <t>Uke 01</t>
   </si>
@@ -1158,6 +1158,9 @@
   </si>
   <si>
     <t>Uke 51</t>
+  </si>
+  <si>
+    <t>Kurs simverktøy</t>
   </si>
 </sst>
 </file>
@@ -1455,7 +1458,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1775,6 +1778,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="23" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -28447,16 +28456,26 @@
       <c r="B41" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C41" s="76"/>
-      <c r="D41" s="77"/>
-      <c r="E41" s="76"/>
-      <c r="F41" s="77"/>
-      <c r="G41" s="76"/>
-      <c r="H41" s="77"/>
-      <c r="I41" s="20"/>
-      <c r="J41" s="21"/>
-      <c r="K41" s="20"/>
-      <c r="L41" s="21"/>
+      <c r="C41" s="109" t="s">
+        <v>361</v>
+      </c>
+      <c r="D41" s="110"/>
+      <c r="E41" s="109" t="s">
+        <v>361</v>
+      </c>
+      <c r="F41" s="110"/>
+      <c r="G41" s="109" t="s">
+        <v>361</v>
+      </c>
+      <c r="H41" s="110"/>
+      <c r="I41" s="109" t="s">
+        <v>361</v>
+      </c>
+      <c r="J41" s="110"/>
+      <c r="K41" s="109" t="s">
+        <v>361</v>
+      </c>
+      <c r="L41" s="110"/>
       <c r="M41" s="7"/>
       <c r="N41" s="7"/>
       <c r="P41" s="9"/>

--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30602"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6676" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4930041E-D210-48D6-AD5D-759A437CF58A}"/>
+  <xr:revisionPtr revIDLastSave="6689" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D4AC054-524F-48CD-A7A3-D0024279092C}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38235" yWindow="-165" windowWidth="29130" windowHeight="15810" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Uke 1-6" sheetId="7" r:id="rId1"/>
@@ -56,17 +56,17 @@
   <commentList>
     <comment ref="U37" authorId="0" shapeId="0" xr:uid="{65E4B43F-4DA4-4023-9E8A-D4F24A3B2C8C}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentartråd]
+Din versjon av Excel lar deg lese denne kommentartråden. Eventuelle endringer i den vil imidlertid bli fjernet hvis filen åpnes i en nyere versjon av Excel. Finn ut mer: https://go.microsoft.com/fwlink/?linkid=870924
+Kommentar:
     RTC SUR KURS</t>
       </text>
     </comment>
     <comment ref="W37" authorId="1" shapeId="0" xr:uid="{BC2FB818-859F-40F5-95A2-BC57CF0AD42E}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentartråd]
+Din versjon av Excel lar deg lese denne kommentartråden. Eventuelle endringer i den vil imidlertid bli fjernet hvis filen åpnes i en nyere versjon av Excel. Finn ut mer: https://go.microsoft.com/fwlink/?linkid=870924
+Kommentar:
     KUT SUR (RTC)?</t>
       </text>
     </comment>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4808" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4810" uniqueCount="368">
   <si>
     <t>Uke 01</t>
   </si>
@@ -1170,13 +1170,22 @@
   </si>
   <si>
     <t>Kurs simverktøy</t>
+  </si>
+  <si>
+    <t>9 SE MS SUR JHH</t>
+  </si>
+  <si>
+    <t>SE AFIS gr. Utd PA</t>
+  </si>
+  <si>
+    <t>SF AFIS gr. Utd HS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2166,7 +2175,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AA61"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="5" customWidth="1"/>
     <col min="2" max="2" width="6.85546875" style="5" bestFit="1" customWidth="1"/>
@@ -2195,7 +2204,7 @@
     <col min="28" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2268,7 +2277,7 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -2319,7 +2328,7 @@
       </c>
       <c r="AA2" s="39"/>
     </row>
-    <row r="3" spans="1:27" ht="9.9499999999999993" customHeight="1">
+    <row r="3" spans="1:27" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -2370,7 +2379,7 @@
       </c>
       <c r="AA3" s="29"/>
     </row>
-    <row r="4" spans="1:27">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -2421,7 +2430,7 @@
       </c>
       <c r="AA4" s="39"/>
     </row>
-    <row r="5" spans="1:27" ht="9.9499999999999993" customHeight="1">
+    <row r="5" spans="1:27" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -2472,7 +2481,7 @@
       </c>
       <c r="AA5" s="63"/>
     </row>
-    <row r="6" spans="1:27">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -2523,7 +2532,7 @@
       </c>
       <c r="AA6" s="37"/>
     </row>
-    <row r="7" spans="1:27">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -2574,7 +2583,7 @@
       </c>
       <c r="AA7" s="31"/>
     </row>
-    <row r="8" spans="1:27">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -2625,7 +2634,7 @@
       </c>
       <c r="AA8" s="25"/>
     </row>
-    <row r="9" spans="1:27">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -2676,7 +2685,7 @@
       </c>
       <c r="AA9" s="63"/>
     </row>
-    <row r="10" spans="1:27">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -2727,7 +2736,7 @@
       </c>
       <c r="AA10" s="37"/>
     </row>
-    <row r="11" spans="1:27">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -2778,7 +2787,7 @@
       </c>
       <c r="AA11" s="29"/>
     </row>
-    <row r="12" spans="1:27">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -2829,7 +2838,7 @@
       </c>
       <c r="AA12" s="25"/>
     </row>
-    <row r="13" spans="1:27">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -2880,7 +2889,7 @@
       </c>
       <c r="AA13" s="25"/>
     </row>
-    <row r="14" spans="1:27">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -2931,7 +2940,7 @@
       </c>
       <c r="AA14" s="63"/>
     </row>
-    <row r="15" spans="1:27">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -2982,7 +2991,7 @@
       </c>
       <c r="AA15" s="39"/>
     </row>
-    <row r="16" spans="1:27">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -3029,7 +3038,7 @@
       <c r="Z16" s="22"/>
       <c r="AA16" s="23"/>
     </row>
-    <row r="17" spans="1:27">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" s="7"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -3064,7 +3073,7 @@
       <c r="Z17" s="22"/>
       <c r="AA17" s="23"/>
     </row>
-    <row r="18" spans="1:27">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" s="7"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -3099,7 +3108,7 @@
       <c r="Z18" s="22"/>
       <c r="AA18" s="23"/>
     </row>
-    <row r="19" spans="1:27">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
@@ -3120,7 +3129,7 @@
       </c>
       <c r="U19" s="21"/>
     </row>
-    <row r="20" spans="1:27">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -3141,7 +3150,7 @@
       </c>
       <c r="U20" s="63"/>
     </row>
-    <row r="21" spans="1:27">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -3159,7 +3168,7 @@
       <c r="O21" s="4"/>
       <c r="P21" s="4"/>
     </row>
-    <row r="22" spans="1:27">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -3177,7 +3186,7 @@
       <c r="O22" s="4"/>
       <c r="P22" s="4"/>
     </row>
-    <row r="23" spans="1:27">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>54</v>
       </c>
@@ -3250,7 +3259,7 @@
         <v>46052</v>
       </c>
     </row>
-    <row r="24" spans="1:27">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>7</v>
       </c>
@@ -3303,7 +3312,7 @@
       </c>
       <c r="AA24" s="37"/>
     </row>
-    <row r="25" spans="1:27">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>10</v>
       </c>
@@ -3356,7 +3365,7 @@
       </c>
       <c r="AA25" s="37"/>
     </row>
-    <row r="26" spans="1:27">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>15</v>
       </c>
@@ -3409,7 +3418,7 @@
       </c>
       <c r="AA26" s="63"/>
     </row>
-    <row r="27" spans="1:27">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>21</v>
       </c>
@@ -3462,7 +3471,7 @@
       </c>
       <c r="AA27" s="31"/>
     </row>
-    <row r="28" spans="1:27">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>24</v>
       </c>
@@ -3515,7 +3524,7 @@
       </c>
       <c r="AA28" s="23"/>
     </row>
-    <row r="29" spans="1:27">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>26</v>
       </c>
@@ -3568,7 +3577,7 @@
       </c>
       <c r="AA29" s="27"/>
     </row>
-    <row r="30" spans="1:27">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>28</v>
       </c>
@@ -3621,7 +3630,7 @@
       </c>
       <c r="AA30" s="23"/>
     </row>
-    <row r="31" spans="1:27">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
         <v>32</v>
       </c>
@@ -3674,7 +3683,7 @@
       </c>
       <c r="AA31" s="31"/>
     </row>
-    <row r="32" spans="1:27">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
         <v>35</v>
       </c>
@@ -3727,7 +3736,7 @@
       </c>
       <c r="AA32" s="63"/>
     </row>
-    <row r="33" spans="1:27">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>37</v>
       </c>
@@ -3780,7 +3789,7 @@
       </c>
       <c r="AA33" s="31"/>
     </row>
-    <row r="34" spans="1:27">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>40</v>
       </c>
@@ -3833,7 +3842,7 @@
       </c>
       <c r="AA34" s="63"/>
     </row>
-    <row r="35" spans="1:27">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
         <v>45</v>
       </c>
@@ -3886,7 +3895,7 @@
       </c>
       <c r="AA35" s="25"/>
     </row>
-    <row r="36" spans="1:27">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>48</v>
       </c>
@@ -3939,7 +3948,7 @@
       </c>
       <c r="AA36" s="25"/>
     </row>
-    <row r="37" spans="1:27">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
         <v>49</v>
       </c>
@@ -3992,7 +4001,7 @@
       </c>
       <c r="AA37" s="25"/>
     </row>
-    <row r="38" spans="1:27" ht="9.9499999999999993" customHeight="1">
+    <row r="38" spans="1:27" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>50</v>
       </c>
@@ -4041,7 +4050,7 @@
       <c r="Z38" s="22"/>
       <c r="AA38" s="23"/>
     </row>
-    <row r="39" spans="1:27">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A39" s="4"/>
       <c r="F39" s="7"/>
       <c r="G39" s="7"/>
@@ -4062,7 +4071,7 @@
       <c r="Z39" s="7"/>
       <c r="AA39" s="7"/>
     </row>
-    <row r="40" spans="1:27">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A40" s="7"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
@@ -4080,7 +4089,7 @@
       <c r="O40" s="4"/>
       <c r="P40" s="4"/>
     </row>
-    <row r="41" spans="1:27">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>69</v>
       </c>
@@ -4153,7 +4162,7 @@
         <v>46059</v>
       </c>
     </row>
-    <row r="42" spans="1:27">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>7</v>
       </c>
@@ -4206,7 +4215,7 @@
       </c>
       <c r="AA42" s="41"/>
     </row>
-    <row r="43" spans="1:27">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>10</v>
       </c>
@@ -4259,7 +4268,7 @@
       </c>
       <c r="AA43" s="23"/>
     </row>
-    <row r="44" spans="1:27">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>15</v>
       </c>
@@ -4312,7 +4321,7 @@
       </c>
       <c r="AA44" s="53"/>
     </row>
-    <row r="45" spans="1:27" ht="15" customHeight="1">
+    <row r="45" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>21</v>
       </c>
@@ -4365,7 +4374,7 @@
       </c>
       <c r="AA45" s="31"/>
     </row>
-    <row r="46" spans="1:27">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>24</v>
       </c>
@@ -4418,7 +4427,7 @@
       </c>
       <c r="AA46" s="37"/>
     </row>
-    <row r="47" spans="1:27">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>26</v>
       </c>
@@ -4471,7 +4480,7 @@
       </c>
       <c r="AA47" s="23"/>
     </row>
-    <row r="48" spans="1:27">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>28</v>
       </c>
@@ -4524,7 +4533,7 @@
       </c>
       <c r="AA48" s="31"/>
     </row>
-    <row r="49" spans="1:27">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>32</v>
       </c>
@@ -4577,7 +4586,7 @@
       </c>
       <c r="AA49" s="25"/>
     </row>
-    <row r="50" spans="1:27">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
         <v>35</v>
       </c>
@@ -4630,7 +4639,7 @@
       </c>
       <c r="AA50" s="23"/>
     </row>
-    <row r="51" spans="1:27">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>37</v>
       </c>
@@ -4678,7 +4687,7 @@
       </c>
       <c r="AA51" s="53"/>
     </row>
-    <row r="52" spans="1:27">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>40</v>
       </c>
@@ -4726,7 +4735,7 @@
       </c>
       <c r="AA52" s="25"/>
     </row>
-    <row r="53" spans="1:27">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>45</v>
       </c>
@@ -4774,7 +4783,7 @@
       </c>
       <c r="AA53" s="37"/>
     </row>
-    <row r="54" spans="1:27">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>48</v>
       </c>
@@ -4822,7 +4831,7 @@
       </c>
       <c r="AA54" s="25"/>
     </row>
-    <row r="55" spans="1:27">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
         <v>49</v>
       </c>
@@ -4870,7 +4879,7 @@
       </c>
       <c r="AA55" s="53"/>
     </row>
-    <row r="56" spans="1:27">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>50</v>
       </c>
@@ -4910,7 +4919,7 @@
       <c r="Z56" s="22"/>
       <c r="AA56" s="23"/>
     </row>
-    <row r="58" spans="1:27">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
         <v>1</v>
       </c>
@@ -4924,7 +4933,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="59" spans="1:27">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <v>2</v>
       </c>
@@ -4938,7 +4947,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60" spans="1:27">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A60" s="8">
         <v>3</v>
       </c>
@@ -4952,7 +4961,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="61" spans="1:27">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <v>4</v>
       </c>
@@ -5446,7 +5455,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X78"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -5475,7 +5484,7 @@
     <col min="25" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>86</v>
       </c>
@@ -5543,7 +5552,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -5591,7 +5600,7 @@
       </c>
       <c r="X2" s="37"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -5639,7 +5648,7 @@
       </c>
       <c r="X3" s="37"/>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -5687,7 +5696,7 @@
       </c>
       <c r="X4" s="37"/>
     </row>
-    <row r="5" spans="1:24" ht="11.25" customHeight="1">
+    <row r="5" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -5735,7 +5744,7 @@
       </c>
       <c r="X5" s="37"/>
     </row>
-    <row r="6" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="6" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -5783,7 +5792,7 @@
       </c>
       <c r="X6" s="37"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -5831,7 +5840,7 @@
       </c>
       <c r="X7" s="57"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -5879,7 +5888,7 @@
       </c>
       <c r="X8" s="25"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -5927,7 +5936,7 @@
       </c>
       <c r="X9" s="37"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -5975,7 +5984,7 @@
       </c>
       <c r="X10" s="23"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -6023,7 +6032,7 @@
       </c>
       <c r="X11" s="31"/>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -6071,7 +6080,7 @@
       </c>
       <c r="X12" s="25"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -6119,7 +6128,7 @@
       </c>
       <c r="X13" s="31"/>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -6167,7 +6176,7 @@
       </c>
       <c r="X14" s="25"/>
     </row>
-    <row r="15" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="15" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -6215,7 +6224,7 @@
       </c>
       <c r="X15" s="37"/>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -6255,7 +6264,7 @@
       <c r="W16" s="22"/>
       <c r="X16" s="23"/>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="7"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -6279,7 +6288,7 @@
       <c r="W17" s="13"/>
       <c r="X17" s="13"/>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" s="7"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -6303,7 +6312,7 @@
       <c r="W18" s="9"/>
       <c r="X18" s="9"/>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="7"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -6327,7 +6336,7 @@
       <c r="W19" s="9"/>
       <c r="X19" s="9"/>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>97</v>
       </c>
@@ -6395,7 +6404,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>7</v>
       </c>
@@ -6443,7 +6452,7 @@
       </c>
       <c r="X21" s="85"/>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>10</v>
       </c>
@@ -6491,7 +6500,7 @@
       </c>
       <c r="X22" s="37"/>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>15</v>
       </c>
@@ -6539,7 +6548,7 @@
       </c>
       <c r="X23" s="25"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>21</v>
       </c>
@@ -6587,7 +6596,7 @@
       </c>
       <c r="X24" s="25"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
@@ -6635,7 +6644,7 @@
       </c>
       <c r="X25" s="37"/>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>26</v>
       </c>
@@ -6683,7 +6692,7 @@
       </c>
       <c r="X26" s="25"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>28</v>
       </c>
@@ -6731,7 +6740,7 @@
       </c>
       <c r="X27" s="31"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>32</v>
       </c>
@@ -6779,7 +6788,7 @@
       </c>
       <c r="X28" s="43"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>35</v>
       </c>
@@ -6827,7 +6836,7 @@
       </c>
       <c r="X29" s="21"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>37</v>
       </c>
@@ -6877,7 +6886,7 @@
       </c>
       <c r="X30" s="43"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>40</v>
       </c>
@@ -6927,7 +6936,7 @@
       </c>
       <c r="X31" s="31"/>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="s">
         <v>45</v>
       </c>
@@ -6977,7 +6986,7 @@
       </c>
       <c r="X32" s="21"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>48</v>
       </c>
@@ -7027,7 +7036,7 @@
       </c>
       <c r="X33" s="21"/>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
         <v>49</v>
       </c>
@@ -7077,7 +7086,7 @@
       </c>
       <c r="X34" s="43"/>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>50</v>
       </c>
@@ -7117,7 +7126,7 @@
       </c>
       <c r="X35" s="21"/>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>51</v>
       </c>
@@ -7152,7 +7161,7 @@
       <c r="W36" s="9"/>
       <c r="X36" s="9"/>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37" s="5"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
@@ -7175,7 +7184,7 @@
       <c r="W37" s="9"/>
       <c r="X37" s="9"/>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38" s="5"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
@@ -7198,12 +7207,12 @@
       <c r="W38" s="9"/>
       <c r="X38" s="9"/>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="M39" s="7"/>
       <c r="S39" s="9"/>
       <c r="T39" s="9"/>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>109</v>
       </c>
@@ -7272,7 +7281,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>7</v>
       </c>
@@ -7321,7 +7330,7 @@
       </c>
       <c r="X41" s="37"/>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>10</v>
       </c>
@@ -7369,7 +7378,7 @@
       </c>
       <c r="X42" s="37"/>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>15</v>
       </c>
@@ -7417,7 +7426,7 @@
       </c>
       <c r="X43" s="37"/>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>21</v>
       </c>
@@ -7465,7 +7474,7 @@
       </c>
       <c r="X44" s="29"/>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>24</v>
       </c>
@@ -7513,7 +7522,7 @@
       </c>
       <c r="X45" s="37"/>
     </row>
-    <row r="46" spans="1:24" ht="10.5" customHeight="1">
+    <row r="46" spans="1:24" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>26</v>
       </c>
@@ -7562,7 +7571,7 @@
       </c>
       <c r="X46" s="25"/>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>28</v>
       </c>
@@ -7611,7 +7620,7 @@
       </c>
       <c r="X47" s="25"/>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>32</v>
       </c>
@@ -7660,7 +7669,7 @@
       </c>
       <c r="X48" s="21"/>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>35</v>
       </c>
@@ -7709,7 +7718,7 @@
       </c>
       <c r="X49" s="29"/>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>37</v>
       </c>
@@ -7758,7 +7767,7 @@
       </c>
       <c r="X50" s="21"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>40</v>
       </c>
@@ -7806,7 +7815,7 @@
       </c>
       <c r="X51" s="31"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>45</v>
       </c>
@@ -7854,7 +7863,7 @@
       </c>
       <c r="X52" s="25"/>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>48</v>
       </c>
@@ -7902,7 +7911,7 @@
       </c>
       <c r="X53" s="31"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>49</v>
       </c>
@@ -7951,7 +7960,7 @@
       </c>
       <c r="X54" s="31"/>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>50</v>
       </c>
@@ -7994,7 +8003,7 @@
       </c>
       <c r="X55" s="21"/>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>51</v>
       </c>
@@ -8031,7 +8040,7 @@
       <c r="W56" s="9"/>
       <c r="X56" s="9"/>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="7"/>
       <c r="B57" s="9"/>
       <c r="C57" s="9"/>
@@ -8056,7 +8065,7 @@
       <c r="W57" s="9"/>
       <c r="X57" s="9"/>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
         <v>1</v>
       </c>
@@ -8070,7 +8079,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <v>2</v>
       </c>
@@ -8084,7 +8093,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="8">
         <v>3</v>
       </c>
@@ -8104,7 +8113,7 @@
       <c r="W60" s="9"/>
       <c r="X60" s="9"/>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <v>4</v>
       </c>
@@ -8116,34 +8125,34 @@
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
       <c r="O62" s="9"/>
       <c r="P62" s="9"/>
       <c r="Q62" s="9"/>
       <c r="R62" s="9"/>
     </row>
-    <row r="71" spans="13:13">
+    <row r="71" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M71" s="5"/>
     </row>
-    <row r="72" spans="13:13">
+    <row r="72" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M72" s="5"/>
     </row>
-    <row r="73" spans="13:13">
+    <row r="73" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M73" s="5"/>
     </row>
-    <row r="74" spans="13:13">
+    <row r="74" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M74" s="5"/>
     </row>
-    <row r="75" spans="13:13">
+    <row r="75" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M75" s="5"/>
     </row>
-    <row r="76" spans="13:13">
+    <row r="76" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M76" s="5"/>
     </row>
-    <row r="77" spans="13:13">
+    <row r="77" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M77" s="5"/>
     </row>
-    <row r="78" spans="13:13">
+    <row r="78" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M78" s="5"/>
     </row>
   </sheetData>
@@ -8627,7 +8636,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X66"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -8657,7 +8666,7 @@
     <col min="27" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>116</v>
       </c>
@@ -8725,7 +8734,7 @@
         <v>46129</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -8773,7 +8782,7 @@
       </c>
       <c r="X2" s="41"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -8821,7 +8830,7 @@
       </c>
       <c r="X3" s="77"/>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -8869,7 +8878,7 @@
       </c>
       <c r="X4" s="31"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -8917,7 +8926,7 @@
       </c>
       <c r="X5" s="77"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -8965,7 +8974,7 @@
       </c>
       <c r="X6" s="37"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -9013,7 +9022,7 @@
       </c>
       <c r="X7" s="31"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -9061,7 +9070,7 @@
       </c>
       <c r="X8" s="43"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -9109,7 +9118,7 @@
       </c>
       <c r="X9" s="31"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -9157,7 +9166,7 @@
       </c>
       <c r="X10" s="43"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -9205,7 +9214,7 @@
       </c>
       <c r="X11" s="31"/>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -9253,7 +9262,7 @@
       </c>
       <c r="X12" s="31"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -9301,7 +9310,7 @@
       </c>
       <c r="X13" s="31"/>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -9349,7 +9358,7 @@
       </c>
       <c r="X14" s="77"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -9397,7 +9406,7 @@
       </c>
       <c r="X15" s="77"/>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -9437,7 +9446,7 @@
       <c r="W16" s="22"/>
       <c r="X16" s="23"/>
     </row>
-    <row r="17" spans="1:24" ht="11.25" customHeight="1">
+    <row r="17" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
       <c r="N17" s="7"/>
@@ -9450,7 +9459,7 @@
       </c>
       <c r="V17" s="31"/>
     </row>
-    <row r="18" spans="1:24" ht="11.25" customHeight="1">
+    <row r="18" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
       <c r="N18" s="7"/>
@@ -9459,7 +9468,7 @@
       </c>
       <c r="P18" s="31"/>
     </row>
-    <row r="19" spans="1:24" ht="11.25" customHeight="1">
+    <row r="19" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
       <c r="N19" s="7"/>
@@ -9468,7 +9477,7 @@
       </c>
       <c r="P19" s="77"/>
     </row>
-    <row r="20" spans="1:24" ht="11.25" customHeight="1">
+    <row r="20" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
       <c r="N20" s="7"/>
@@ -9477,7 +9486,7 @@
       </c>
       <c r="P20" s="77"/>
     </row>
-    <row r="21" spans="1:24" ht="11.25" customHeight="1">
+    <row r="21" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
       <c r="N21" s="7"/>
@@ -9486,7 +9495,7 @@
       </c>
       <c r="P21" s="77"/>
     </row>
-    <row r="22" spans="1:24" ht="11.25" customHeight="1">
+    <row r="22" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
       <c r="N22" s="7"/>
@@ -9495,17 +9504,17 @@
       </c>
       <c r="P22" s="77"/>
     </row>
-    <row r="23" spans="1:24" ht="11.25" customHeight="1">
+    <row r="23" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
       <c r="N23" s="7"/>
     </row>
-    <row r="24" spans="1:24" ht="11.25" customHeight="1">
+    <row r="24" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
       <c r="N24" s="7"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>154</v>
       </c>
@@ -9575,7 +9584,7 @@
         <v>46136</v>
       </c>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>7</v>
       </c>
@@ -9621,7 +9630,7 @@
       </c>
       <c r="X26" s="37"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>10</v>
       </c>
@@ -9667,7 +9676,7 @@
       </c>
       <c r="X27" s="39"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>15</v>
       </c>
@@ -9713,7 +9722,7 @@
       </c>
       <c r="X28" s="35"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>21</v>
       </c>
@@ -9759,7 +9768,7 @@
       </c>
       <c r="X29" s="25"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>24</v>
       </c>
@@ -9805,7 +9814,7 @@
       </c>
       <c r="X30" s="37"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
         <v>26</v>
       </c>
@@ -9851,7 +9860,7 @@
       </c>
       <c r="X31" s="25"/>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
         <v>28</v>
       </c>
@@ -9897,7 +9906,7 @@
       </c>
       <c r="X32" s="35"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
         <v>32</v>
       </c>
@@ -9939,7 +9948,7 @@
       </c>
       <c r="X33" s="63"/>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
         <v>35</v>
       </c>
@@ -9985,7 +9994,7 @@
       </c>
       <c r="X34" s="37"/>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>37</v>
       </c>
@@ -10031,7 +10040,7 @@
       </c>
       <c r="X35" s="31"/>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>40</v>
       </c>
@@ -10077,7 +10086,7 @@
       </c>
       <c r="X36" s="63"/>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
         <v>45</v>
       </c>
@@ -10123,7 +10132,7 @@
       </c>
       <c r="X37" s="31"/>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>48</v>
       </c>
@@ -10169,7 +10178,7 @@
       </c>
       <c r="X38" s="25"/>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39" s="12" t="s">
         <v>49</v>
       </c>
@@ -10215,7 +10224,7 @@
       </c>
       <c r="X39" s="63"/>
     </row>
-    <row r="40" spans="1:24" ht="11.25" customHeight="1">
+    <row r="40" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>50</v>
       </c>
@@ -10257,7 +10266,7 @@
       <c r="W40" s="22"/>
       <c r="X40" s="23"/>
     </row>
-    <row r="41" spans="1:24" ht="11.25" customHeight="1">
+    <row r="41" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -10272,7 +10281,7 @@
       <c r="L41" s="5"/>
       <c r="M41" s="5"/>
     </row>
-    <row r="42" spans="1:24" ht="11.25" customHeight="1">
+    <row r="42" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -10287,7 +10296,7 @@
       <c r="L42" s="5"/>
       <c r="M42" s="5"/>
     </row>
-    <row r="43" spans="1:24" ht="11.25" customHeight="1">
+    <row r="43" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>166</v>
       </c>
@@ -10357,7 +10366,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="44" spans="1:24" ht="11.25" customHeight="1">
+    <row r="44" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>7</v>
       </c>
@@ -10403,7 +10412,7 @@
       <c r="W44" s="64"/>
       <c r="X44" s="65"/>
     </row>
-    <row r="45" spans="1:24" ht="11.25" customHeight="1">
+    <row r="45" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>10</v>
       </c>
@@ -10449,7 +10458,7 @@
       <c r="W45" s="64"/>
       <c r="X45" s="65"/>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>15</v>
       </c>
@@ -10495,7 +10504,7 @@
       <c r="W46" s="64"/>
       <c r="X46" s="65"/>
     </row>
-    <row r="47" spans="1:24" ht="11.25" customHeight="1">
+    <row r="47" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>21</v>
       </c>
@@ -10539,7 +10548,7 @@
       <c r="W47" s="64"/>
       <c r="X47" s="65"/>
     </row>
-    <row r="48" spans="1:24" ht="11.25" customHeight="1">
+    <row r="48" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>24</v>
       </c>
@@ -10583,7 +10592,7 @@
       <c r="W48" s="64"/>
       <c r="X48" s="65"/>
     </row>
-    <row r="49" spans="1:24" ht="11.25" customHeight="1">
+    <row r="49" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>26</v>
       </c>
@@ -10627,7 +10636,7 @@
       <c r="W49" s="64"/>
       <c r="X49" s="65"/>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
         <v>28</v>
       </c>
@@ -10671,7 +10680,7 @@
       <c r="W50" s="64"/>
       <c r="X50" s="65"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
         <v>32</v>
       </c>
@@ -10717,7 +10726,7 @@
       <c r="W51" s="64"/>
       <c r="X51" s="65"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
         <v>35</v>
       </c>
@@ -10763,7 +10772,7 @@
       <c r="W52" s="64"/>
       <c r="X52" s="65"/>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>37</v>
       </c>
@@ -10809,7 +10818,7 @@
       <c r="W53" s="64"/>
       <c r="X53" s="65"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>40</v>
       </c>
@@ -10855,7 +10864,7 @@
       <c r="W54" s="64"/>
       <c r="X54" s="65"/>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
         <v>45</v>
       </c>
@@ -10901,7 +10910,7 @@
       <c r="W55" s="64"/>
       <c r="X55" s="65"/>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>48</v>
       </c>
@@ -10947,7 +10956,7 @@
       <c r="W56" s="64"/>
       <c r="X56" s="65"/>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
         <v>49</v>
       </c>
@@ -10993,7 +11002,7 @@
       <c r="W57" s="64"/>
       <c r="X57" s="65"/>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>50</v>
       </c>
@@ -11033,7 +11042,7 @@
       <c r="W58" s="64"/>
       <c r="X58" s="65"/>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="O59" s="28" t="s">
@@ -11049,7 +11058,7 @@
       </c>
       <c r="T59" s="29"/>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="5">
         <v>1</v>
       </c>
@@ -11067,7 +11076,7 @@
       </c>
       <c r="P60" s="25"/>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <v>2</v>
       </c>
@@ -11081,7 +11090,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A62" s="8">
         <v>3</v>
       </c>
@@ -11095,7 +11104,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="63" spans="1:24">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A63" s="5">
         <v>4</v>
       </c>
@@ -11103,17 +11112,17 @@
         <v>85</v>
       </c>
     </row>
-    <row r="64" spans="1:24">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
@@ -11601,7 +11610,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X62"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -11630,7 +11639,7 @@
     <col min="25" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>178</v>
       </c>
@@ -11698,7 +11707,7 @@
         <v>46171</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -11744,7 +11753,7 @@
       </c>
       <c r="X2" s="41"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -11790,7 +11799,7 @@
       </c>
       <c r="X3" s="37"/>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -11836,7 +11845,7 @@
       </c>
       <c r="X4" s="23"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -11883,7 +11892,7 @@
       </c>
       <c r="X5" s="29"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -11929,7 +11938,7 @@
       </c>
       <c r="X6" s="37"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -11975,7 +11984,7 @@
       </c>
       <c r="X7" s="35"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -12021,7 +12030,7 @@
       </c>
       <c r="X8" s="35"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -12067,7 +12076,7 @@
       </c>
       <c r="X9" s="45"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -12113,7 +12122,7 @@
       </c>
       <c r="X10" s="43"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -12159,7 +12168,7 @@
       </c>
       <c r="X11" s="29"/>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -12205,7 +12214,7 @@
       </c>
       <c r="X12" s="43"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -12251,7 +12260,7 @@
       </c>
       <c r="X13" s="45"/>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -12297,7 +12306,7 @@
       </c>
       <c r="X14" s="43"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -12343,7 +12352,7 @@
       </c>
       <c r="X15" s="29"/>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -12383,7 +12392,7 @@
       <c r="W16" s="22"/>
       <c r="X16" s="23"/>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>195</v>
       </c>
@@ -12410,7 +12419,7 @@
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B18" s="30" t="s">
         <v>196</v>
       </c>
@@ -12422,7 +12431,7 @@
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
@@ -12431,7 +12440,7 @@
       <c r="R19" s="4"/>
       <c r="S19" s="4"/>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -12442,7 +12451,7 @@
       <c r="R20" s="4"/>
       <c r="S20" s="4"/>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>197</v>
       </c>
@@ -12510,7 +12519,7 @@
         <v>46178</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
@@ -12556,7 +12565,7 @@
       </c>
       <c r="X22" s="41"/>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>10</v>
       </c>
@@ -12602,7 +12611,7 @@
       </c>
       <c r="X23" s="39"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>15</v>
       </c>
@@ -12648,7 +12657,7 @@
       </c>
       <c r="X24" s="23"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>21</v>
       </c>
@@ -12694,7 +12703,7 @@
       </c>
       <c r="X25" s="45"/>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
@@ -12740,7 +12749,7 @@
       </c>
       <c r="X26" s="37"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
@@ -12786,7 +12795,7 @@
       </c>
       <c r="X27" s="43"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>28</v>
       </c>
@@ -12832,7 +12841,7 @@
       </c>
       <c r="X28" s="45"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>32</v>
       </c>
@@ -12878,7 +12887,7 @@
       </c>
       <c r="X29" s="37"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>35</v>
       </c>
@@ -12924,7 +12933,7 @@
       </c>
       <c r="X30" s="37"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
@@ -12970,7 +12979,7 @@
       </c>
       <c r="X31" s="29"/>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>40</v>
       </c>
@@ -13018,7 +13027,7 @@
       </c>
       <c r="X32" s="31"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>45</v>
       </c>
@@ -13066,7 +13075,7 @@
       </c>
       <c r="X33" s="43"/>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>48</v>
       </c>
@@ -13114,7 +13123,7 @@
       </c>
       <c r="X34" s="29"/>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
         <v>49</v>
       </c>
@@ -13162,7 +13171,7 @@
       </c>
       <c r="X35" s="43"/>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>50</v>
       </c>
@@ -13204,7 +13213,7 @@
       </c>
       <c r="X36" s="29"/>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
       <c r="N37" s="4"/>
@@ -13212,7 +13221,7 @@
       <c r="Q37" s="4"/>
       <c r="R37" s="4"/>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
       <c r="N38" s="4"/>
@@ -13220,7 +13229,7 @@
       <c r="Q38" s="4"/>
       <c r="R38" s="4"/>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L39" s="7"/>
       <c r="M39" s="7"/>
       <c r="N39" s="4"/>
@@ -13228,7 +13237,7 @@
       <c r="Q39" s="4"/>
       <c r="R39" s="4"/>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>212</v>
       </c>
@@ -13298,7 +13307,7 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>7</v>
       </c>
@@ -13348,7 +13357,7 @@
       </c>
       <c r="X41" s="41"/>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>10</v>
       </c>
@@ -13398,7 +13407,7 @@
       </c>
       <c r="X42" s="23"/>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>15</v>
       </c>
@@ -13448,7 +13457,7 @@
       </c>
       <c r="X43" s="23"/>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>21</v>
       </c>
@@ -13496,7 +13505,7 @@
       </c>
       <c r="X44" s="63"/>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>24</v>
       </c>
@@ -13544,7 +13553,7 @@
       </c>
       <c r="X45" s="37"/>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>26</v>
       </c>
@@ -13592,7 +13601,7 @@
       </c>
       <c r="X46" s="37"/>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>28</v>
       </c>
@@ -13640,7 +13649,7 @@
       </c>
       <c r="X47" s="49"/>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>32</v>
       </c>
@@ -13688,7 +13697,7 @@
       </c>
       <c r="X48" s="39"/>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>35</v>
       </c>
@@ -13736,7 +13745,7 @@
       </c>
       <c r="X49" s="37"/>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>37</v>
       </c>
@@ -13784,7 +13793,7 @@
       </c>
       <c r="X50" s="37"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>40</v>
       </c>
@@ -13834,7 +13843,7 @@
       </c>
       <c r="X51" s="37"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>45</v>
       </c>
@@ -13884,7 +13893,7 @@
       </c>
       <c r="X52" s="63"/>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>48</v>
       </c>
@@ -13934,7 +13943,7 @@
       </c>
       <c r="X53" s="63"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>49</v>
       </c>
@@ -13982,7 +13991,7 @@
       </c>
       <c r="X54" s="39"/>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>50</v>
       </c>
@@ -14024,7 +14033,7 @@
       <c r="W55" s="22"/>
       <c r="X55" s="23"/>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="8"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -14054,7 +14063,7 @@
       <c r="W56" s="22"/>
       <c r="X56" s="23"/>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="8"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -14079,7 +14088,7 @@
       <c r="W57" s="9"/>
       <c r="X57" s="9"/>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="8"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -14092,7 +14101,7 @@
       <c r="L58" s="7"/>
       <c r="M58" s="7"/>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <v>1</v>
       </c>
@@ -14117,7 +14126,7 @@
       <c r="W59" s="4"/>
       <c r="X59" s="4"/>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="5">
         <v>2</v>
       </c>
@@ -14131,7 +14140,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="8">
         <v>3</v>
       </c>
@@ -14145,7 +14154,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A62" s="5">
         <v>4</v>
       </c>
@@ -14637,7 +14646,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X61"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -14666,7 +14675,7 @@
     <col min="25" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>229</v>
       </c>
@@ -14734,7 +14743,7 @@
         <v>46213</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -14782,7 +14791,7 @@
       </c>
       <c r="X2" s="39"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -14830,7 +14839,7 @@
       </c>
       <c r="X3" s="39"/>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -14878,7 +14887,7 @@
       </c>
       <c r="X4" s="57"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -14926,7 +14935,7 @@
       </c>
       <c r="X5" s="39"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -14974,7 +14983,7 @@
       </c>
       <c r="X6" s="57"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -15022,7 +15031,7 @@
       </c>
       <c r="X7" s="23"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -15070,7 +15079,7 @@
       </c>
       <c r="X8" s="23"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -15118,7 +15127,7 @@
       </c>
       <c r="X9" s="23"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -15166,7 +15175,7 @@
       </c>
       <c r="X10" s="39"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -15214,7 +15223,7 @@
       </c>
       <c r="X11" s="39"/>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -15262,7 +15271,7 @@
       </c>
       <c r="X12" s="23"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -15310,7 +15319,7 @@
       </c>
       <c r="X13" s="23"/>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -15358,7 +15367,7 @@
       </c>
       <c r="X14" s="23"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -15406,7 +15415,7 @@
       </c>
       <c r="X15" s="23"/>
     </row>
-    <row r="16" spans="1:24" ht="11.25" customHeight="1">
+    <row r="16" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -15450,9 +15459,9 @@
       </c>
       <c r="X16" s="39"/>
     </row>
-    <row r="17" spans="1:24" ht="11.25" customHeight="1"/>
-    <row r="18" spans="1:24" ht="11.25" customHeight="1"/>
-    <row r="19" spans="1:24" ht="11.25" customHeight="1">
+    <row r="17" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>233</v>
       </c>
@@ -15520,7 +15529,7 @@
         <v>46220</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="11.25" customHeight="1">
+    <row r="20" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>7</v>
       </c>
@@ -15568,7 +15577,7 @@
       </c>
       <c r="X20" s="39"/>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -15616,7 +15625,7 @@
       </c>
       <c r="X21" s="39"/>
     </row>
-    <row r="22" spans="1:24" ht="11.25" customHeight="1">
+    <row r="22" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>15</v>
       </c>
@@ -15664,7 +15673,7 @@
       </c>
       <c r="X22" s="39"/>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -15712,7 +15721,7 @@
       </c>
       <c r="X23" s="39"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>24</v>
       </c>
@@ -15760,7 +15769,7 @@
       </c>
       <c r="X24" s="39"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>26</v>
       </c>
@@ -15808,7 +15817,7 @@
       </c>
       <c r="X25" s="39"/>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>28</v>
       </c>
@@ -15856,7 +15865,7 @@
       </c>
       <c r="X26" s="23"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>32</v>
       </c>
@@ -15904,7 +15913,7 @@
       </c>
       <c r="X27" s="23"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>35</v>
       </c>
@@ -15952,7 +15961,7 @@
       </c>
       <c r="X28" s="39"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>37</v>
       </c>
@@ -16002,7 +16011,7 @@
       </c>
       <c r="X29" s="39"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>40</v>
       </c>
@@ -16052,7 +16061,7 @@
       </c>
       <c r="X30" s="39"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
         <v>45</v>
       </c>
@@ -16102,7 +16111,7 @@
       </c>
       <c r="X31" s="23"/>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>48</v>
       </c>
@@ -16152,7 +16161,7 @@
       </c>
       <c r="X32" s="39"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>49</v>
       </c>
@@ -16202,7 +16211,7 @@
       </c>
       <c r="X33" s="23"/>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>50</v>
       </c>
@@ -16252,7 +16261,7 @@
       </c>
       <c r="X34" s="39"/>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="5"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -16277,11 +16286,11 @@
       <c r="W35" s="9"/>
       <c r="X35" s="9"/>
     </row>
-    <row r="36" spans="1:24" ht="11.25" customHeight="1">
+    <row r="36" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L36" s="7"/>
       <c r="M36" s="7"/>
     </row>
-    <row r="37" spans="1:24" ht="11.25" customHeight="1">
+    <row r="37" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>236</v>
       </c>
@@ -16351,7 +16360,7 @@
         <v>46227</v>
       </c>
     </row>
-    <row r="38" spans="1:24" ht="11.25" customHeight="1">
+    <row r="38" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>7</v>
       </c>
@@ -16401,7 +16410,7 @@
       </c>
       <c r="X38" s="39"/>
     </row>
-    <row r="39" spans="1:24" ht="10.5" customHeight="1">
+    <row r="39" spans="1:24" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>10</v>
       </c>
@@ -16451,7 +16460,7 @@
       </c>
       <c r="X39" s="39"/>
     </row>
-    <row r="40" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="40" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>15</v>
       </c>
@@ -16501,7 +16510,7 @@
       </c>
       <c r="X40" s="39"/>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>21</v>
       </c>
@@ -16549,7 +16558,7 @@
       </c>
       <c r="X41" s="39"/>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>24</v>
       </c>
@@ -16597,7 +16606,7 @@
       </c>
       <c r="X42" s="39"/>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
         <v>26</v>
       </c>
@@ -16645,7 +16654,7 @@
       </c>
       <c r="X43" s="39"/>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
         <v>28</v>
       </c>
@@ -16693,7 +16702,7 @@
       </c>
       <c r="X44" s="23"/>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
         <v>32</v>
       </c>
@@ -16741,7 +16750,7 @@
       </c>
       <c r="X45" s="23"/>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>35</v>
       </c>
@@ -16789,7 +16798,7 @@
       </c>
       <c r="X46" s="39"/>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>37</v>
       </c>
@@ -16837,7 +16846,7 @@
       </c>
       <c r="X47" s="23"/>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>40</v>
       </c>
@@ -16885,7 +16894,7 @@
       </c>
       <c r="X48" s="39"/>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>45</v>
       </c>
@@ -16933,7 +16942,7 @@
       </c>
       <c r="X49" s="23"/>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>48</v>
       </c>
@@ -16981,7 +16990,7 @@
       </c>
       <c r="X50" s="39"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>49</v>
       </c>
@@ -17029,7 +17038,7 @@
       </c>
       <c r="X51" s="23"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>50</v>
       </c>
@@ -17077,7 +17086,7 @@
       </c>
       <c r="X52" s="39"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="5">
         <v>1</v>
       </c>
@@ -17091,7 +17100,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="5">
         <v>2</v>
       </c>
@@ -17107,7 +17116,7 @@
       <c r="L55" s="7"/>
       <c r="M55" s="7"/>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="8">
         <v>3</v>
       </c>
@@ -17123,7 +17132,7 @@
       <c r="L56" s="7"/>
       <c r="M56" s="7"/>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="5">
         <v>4</v>
       </c>
@@ -17133,15 +17142,15 @@
       <c r="L57" s="7"/>
       <c r="M57" s="7"/>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L59" s="7"/>
       <c r="M59" s="7"/>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L60" s="7"/>
       <c r="M60" s="7"/>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -17624,7 +17633,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X65"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -17653,7 +17662,7 @@
     <col min="25" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>240</v>
       </c>
@@ -17721,7 +17730,7 @@
         <v>46255</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -17769,7 +17778,7 @@
       </c>
       <c r="X2" s="41"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -17817,7 +17826,7 @@
       </c>
       <c r="X3" s="23"/>
     </row>
-    <row r="4" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="4" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -17865,7 +17874,7 @@
       </c>
       <c r="X4" s="37"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -17913,7 +17922,7 @@
       </c>
       <c r="X5" s="25"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -17961,7 +17970,7 @@
       </c>
       <c r="X6" s="37"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -18009,7 +18018,7 @@
       </c>
       <c r="X7" s="23"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -18057,7 +18066,7 @@
       </c>
       <c r="X8" s="23"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -18105,7 +18114,7 @@
       </c>
       <c r="X9" s="39"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -18153,7 +18162,7 @@
       </c>
       <c r="X10" s="37"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -18201,7 +18210,7 @@
       </c>
       <c r="X11" s="37"/>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -18249,7 +18258,7 @@
       </c>
       <c r="X12" s="39"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -18297,7 +18306,7 @@
       </c>
       <c r="X13" s="39"/>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -18345,7 +18354,7 @@
       </c>
       <c r="X14" s="37"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -18393,7 +18402,7 @@
       </c>
       <c r="X15" s="39"/>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -18439,7 +18448,7 @@
       </c>
       <c r="X16" s="25"/>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -18467,7 +18476,7 @@
       <c r="W17" s="22"/>
       <c r="X17" s="23"/>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -18495,7 +18504,7 @@
       <c r="W18" s="22"/>
       <c r="X18" s="23"/>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -18519,7 +18528,7 @@
       <c r="W19" s="4"/>
       <c r="X19" s="4"/>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -18543,7 +18552,7 @@
       <c r="W20" s="4"/>
       <c r="X20" s="4"/>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>249</v>
       </c>
@@ -18611,7 +18620,7 @@
         <v>46262</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
@@ -18659,7 +18668,7 @@
       </c>
       <c r="X22" s="41"/>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>10</v>
       </c>
@@ -18707,7 +18716,7 @@
       </c>
       <c r="X23" s="23"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>15</v>
       </c>
@@ -18755,7 +18764,7 @@
       </c>
       <c r="X24" s="25"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>21</v>
       </c>
@@ -18803,7 +18812,7 @@
       </c>
       <c r="X25" s="25"/>
     </row>
-    <row r="26" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="26" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
@@ -18851,7 +18860,7 @@
       </c>
       <c r="X26" s="102"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
@@ -18899,7 +18908,7 @@
       </c>
       <c r="X27" s="77"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>28</v>
       </c>
@@ -18947,7 +18956,7 @@
       </c>
       <c r="X28" s="37"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>32</v>
       </c>
@@ -18995,7 +19004,7 @@
       </c>
       <c r="X29" s="39"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>35</v>
       </c>
@@ -19043,7 +19052,7 @@
       </c>
       <c r="X30" s="77"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
@@ -19091,7 +19100,7 @@
       </c>
       <c r="X31" s="37"/>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>40</v>
       </c>
@@ -19139,7 +19148,7 @@
       </c>
       <c r="X32" s="21"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>45</v>
       </c>
@@ -19187,7 +19196,7 @@
       </c>
       <c r="X33" s="21"/>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>48</v>
       </c>
@@ -19235,7 +19244,7 @@
       </c>
       <c r="X34" s="21"/>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
         <v>49</v>
       </c>
@@ -19283,7 +19292,7 @@
       </c>
       <c r="X35" s="39"/>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>50</v>
       </c>
@@ -19331,15 +19340,15 @@
       <c r="W36" s="22"/>
       <c r="X36" s="23"/>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>264</v>
       </c>
@@ -19409,7 +19418,7 @@
         <v>46269</v>
       </c>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>7</v>
       </c>
@@ -19459,7 +19468,7 @@
       </c>
       <c r="X40" s="53"/>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>10</v>
       </c>
@@ -19509,7 +19518,7 @@
       </c>
       <c r="X41" s="23"/>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>15</v>
       </c>
@@ -19557,7 +19566,7 @@
       </c>
       <c r="X42" s="21"/>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>21</v>
       </c>
@@ -19605,7 +19614,7 @@
       </c>
       <c r="X43" s="77"/>
     </row>
-    <row r="44" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="44" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>24</v>
       </c>
@@ -19653,7 +19662,7 @@
       </c>
       <c r="X44" s="37"/>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
         <v>26</v>
       </c>
@@ -19701,7 +19710,7 @@
       </c>
       <c r="X45" s="21"/>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>28</v>
       </c>
@@ -19751,7 +19760,7 @@
       </c>
       <c r="X46" s="25"/>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>32</v>
       </c>
@@ -19799,7 +19808,7 @@
       </c>
       <c r="X47" s="21"/>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>35</v>
       </c>
@@ -19847,7 +19856,7 @@
       </c>
       <c r="X48" s="25"/>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>37</v>
       </c>
@@ -19895,7 +19904,7 @@
       </c>
       <c r="X49" s="43"/>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>40</v>
       </c>
@@ -19943,7 +19952,7 @@
       </c>
       <c r="X50" s="31"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>45</v>
       </c>
@@ -19991,7 +20000,7 @@
       </c>
       <c r="X51" s="27"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>48</v>
       </c>
@@ -20039,7 +20048,7 @@
       </c>
       <c r="X52" s="77"/>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>49</v>
       </c>
@@ -20087,7 +20096,7 @@
       </c>
       <c r="X53" s="43"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>50</v>
       </c>
@@ -20133,7 +20142,7 @@
       </c>
       <c r="X54" s="43"/>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="5"/>
       <c r="B55" s="9"/>
       <c r="C55" s="9"/>
@@ -20169,7 +20178,7 @@
       </c>
       <c r="X55" s="27"/>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="5"/>
       <c r="B56" s="9"/>
       <c r="C56" s="9"/>
@@ -20197,7 +20206,7 @@
       <c r="W56" s="22"/>
       <c r="X56" s="23"/>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="5"/>
       <c r="B57" s="9"/>
       <c r="C57" s="9"/>
@@ -20220,7 +20229,7 @@
       <c r="W57" s="9"/>
       <c r="X57" s="9"/>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
         <v>1</v>
       </c>
@@ -20234,7 +20243,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <v>2</v>
       </c>
@@ -20248,7 +20257,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="8">
         <v>3</v>
       </c>
@@ -20262,7 +20271,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <v>4</v>
       </c>
@@ -20270,22 +20279,22 @@
         <v>85</v>
       </c>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
     </row>
-    <row r="63" spans="1:24">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
     </row>
-    <row r="64" spans="1:24">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
     </row>
-    <row r="65" spans="1:1">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A65" s="8"/>
     </row>
   </sheetData>
@@ -20780,7 +20789,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X67"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -20810,7 +20819,7 @@
     <col min="26" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>271</v>
       </c>
@@ -20878,7 +20887,7 @@
         <v>46297</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -20926,7 +20935,7 @@
       </c>
       <c r="X2" s="41"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -20974,7 +20983,7 @@
       </c>
       <c r="X3" s="23"/>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -21022,7 +21031,7 @@
       </c>
       <c r="X4" s="31"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -21070,7 +21079,7 @@
       </c>
       <c r="X5" s="31"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -21118,7 +21127,7 @@
       </c>
       <c r="X6" s="37"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -21166,7 +21175,7 @@
       </c>
       <c r="X7" s="39"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -21214,7 +21223,7 @@
       </c>
       <c r="X8" s="23"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -21262,7 +21271,7 @@
       </c>
       <c r="X9" s="29"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -21310,7 +21319,7 @@
       </c>
       <c r="X10" s="37"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -21358,7 +21367,7 @@
       </c>
       <c r="X11" s="23"/>
     </row>
-    <row r="12" spans="1:24" ht="11.25" customHeight="1">
+    <row r="12" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -21406,7 +21415,7 @@
       </c>
       <c r="X12" s="37"/>
     </row>
-    <row r="13" spans="1:24" ht="11.25" customHeight="1">
+    <row r="13" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -21454,7 +21463,7 @@
       </c>
       <c r="X13" s="31"/>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -21502,7 +21511,7 @@
       </c>
       <c r="X14" s="29"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -21550,7 +21559,7 @@
       </c>
       <c r="X15" s="23"/>
     </row>
-    <row r="16" spans="1:24" ht="11.25" customHeight="1">
+    <row r="16" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -21598,7 +21607,7 @@
       </c>
       <c r="X16" s="23"/>
     </row>
-    <row r="17" spans="1:24" ht="11.25" customHeight="1">
+    <row r="17" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -21619,7 +21628,7 @@
       </c>
       <c r="T17" s="25"/>
     </row>
-    <row r="18" spans="1:24" ht="11.25" customHeight="1">
+    <row r="18" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -21636,7 +21645,7 @@
       </c>
       <c r="T18" s="25"/>
     </row>
-    <row r="19" spans="1:24" ht="11.25" customHeight="1">
+    <row r="19" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -21653,7 +21662,7 @@
       </c>
       <c r="T19" s="21"/>
     </row>
-    <row r="20" spans="1:24" ht="11.25" customHeight="1">
+    <row r="20" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -21666,7 +21675,7 @@
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
     </row>
-    <row r="21" spans="1:24" ht="11.25" customHeight="1">
+    <row r="21" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -21679,7 +21688,7 @@
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>295</v>
       </c>
@@ -21747,7 +21756,7 @@
         <v>46304</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>7</v>
       </c>
@@ -21795,7 +21804,7 @@
       </c>
       <c r="X23" s="41"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>10</v>
       </c>
@@ -21843,7 +21852,7 @@
       </c>
       <c r="X24" s="23"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>15</v>
       </c>
@@ -21891,7 +21900,7 @@
       </c>
       <c r="X25" s="39"/>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>21</v>
       </c>
@@ -21939,7 +21948,7 @@
       </c>
       <c r="X26" s="31"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>24</v>
       </c>
@@ -21987,7 +21996,7 @@
       </c>
       <c r="X27" s="37"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>26</v>
       </c>
@@ -22035,7 +22044,7 @@
       </c>
       <c r="X28" s="39"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>28</v>
       </c>
@@ -22083,7 +22092,7 @@
       </c>
       <c r="X29" s="37"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>32</v>
       </c>
@@ -22131,7 +22140,7 @@
       </c>
       <c r="X30" s="31"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
         <v>35</v>
       </c>
@@ -22179,7 +22188,7 @@
       </c>
       <c r="X31" s="37"/>
     </row>
-    <row r="32" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="32" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>37</v>
       </c>
@@ -22229,7 +22238,7 @@
       </c>
       <c r="X32" s="45"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>40</v>
       </c>
@@ -22279,7 +22288,7 @@
       </c>
       <c r="X33" s="31"/>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
         <v>45</v>
       </c>
@@ -22329,7 +22338,7 @@
       </c>
       <c r="X34" s="31"/>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>48</v>
       </c>
@@ -22379,7 +22388,7 @@
       </c>
       <c r="X35" s="31"/>
     </row>
-    <row r="36" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="36" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="12" t="s">
         <v>49</v>
       </c>
@@ -22429,7 +22438,7 @@
       </c>
       <c r="X36" s="31"/>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>50</v>
       </c>
@@ -22479,7 +22488,7 @@
       </c>
       <c r="X37" s="45"/>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>51</v>
       </c>
@@ -22516,7 +22525,7 @@
       <c r="W38" s="9"/>
       <c r="X38" s="9"/>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39" s="5"/>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
@@ -22541,7 +22550,7 @@
       <c r="W39" s="9"/>
       <c r="X39" s="9"/>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -22567,7 +22576,7 @@
       <c r="W40" s="4"/>
       <c r="X40" s="4"/>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>310</v>
       </c>
@@ -22637,7 +22646,7 @@
         <v>46311</v>
       </c>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>7</v>
       </c>
@@ -22687,7 +22696,7 @@
       </c>
       <c r="X42" s="41"/>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>10</v>
       </c>
@@ -22737,7 +22746,7 @@
       </c>
       <c r="X43" s="23"/>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>15</v>
       </c>
@@ -22766,10 +22775,10 @@
       <c r="N44" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O44" s="20" t="s">
-        <v>282</v>
-      </c>
-      <c r="P44" s="21"/>
+      <c r="O44" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="P44" s="31"/>
       <c r="Q44" s="20" t="s">
         <v>313</v>
       </c>
@@ -22787,7 +22796,7 @@
       </c>
       <c r="X44" s="23"/>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>21</v>
       </c>
@@ -22837,7 +22846,7 @@
       </c>
       <c r="X45" s="21"/>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>24</v>
       </c>
@@ -22885,7 +22894,7 @@
       </c>
       <c r="X46" s="37"/>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>26</v>
       </c>
@@ -22917,15 +22926,15 @@
       </c>
       <c r="P47" s="31"/>
       <c r="Q47" s="30" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="R47" s="31"/>
       <c r="S47" s="30" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="T47" s="31"/>
       <c r="U47" s="30" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="V47" s="31"/>
       <c r="W47" s="30" t="s">
@@ -22933,7 +22942,7 @@
       </c>
       <c r="X47" s="31"/>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>28</v>
       </c>
@@ -22981,7 +22990,7 @@
       </c>
       <c r="X48" s="39"/>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>32</v>
       </c>
@@ -23008,10 +23017,10 @@
       <c r="N49" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="O49" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="P49" s="23"/>
+      <c r="O49" s="34" t="s">
+        <v>301</v>
+      </c>
+      <c r="P49" s="35"/>
       <c r="Q49" s="32" t="s">
         <v>314</v>
       </c>
@@ -23029,7 +23038,7 @@
       </c>
       <c r="X49" s="33"/>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
         <v>35</v>
       </c>
@@ -23077,7 +23086,7 @@
       </c>
       <c r="X50" s="39"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>37</v>
       </c>
@@ -23125,7 +23134,7 @@
       </c>
       <c r="X51" s="33"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>40</v>
       </c>
@@ -23173,7 +23182,7 @@
       </c>
       <c r="X52" s="37"/>
     </row>
-    <row r="53" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="53" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>45</v>
       </c>
@@ -23221,7 +23230,7 @@
       </c>
       <c r="X53" s="31"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>48</v>
       </c>
@@ -23269,7 +23278,7 @@
       </c>
       <c r="X54" s="31"/>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
         <v>49</v>
       </c>
@@ -23317,7 +23326,7 @@
       </c>
       <c r="X55" s="21"/>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>50</v>
       </c>
@@ -23344,20 +23353,20 @@
       <c r="N56" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="O56" s="30" t="s">
-        <v>124</v>
-      </c>
-      <c r="P56" s="31"/>
+      <c r="O56" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="P56" s="21"/>
       <c r="Q56" s="30" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="R56" s="31"/>
       <c r="S56" s="30" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="T56" s="31"/>
       <c r="U56" s="30" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="V56" s="31"/>
       <c r="W56" s="22" t="s">
@@ -23365,7 +23374,7 @@
       </c>
       <c r="X56" s="23"/>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>51</v>
       </c>
@@ -23389,12 +23398,20 @@
         <v>290</v>
       </c>
       <c r="K57" s="27"/>
+      <c r="O57" s="30" t="s">
+        <v>366</v>
+      </c>
+      <c r="P57" s="31"/>
+      <c r="Q57" s="30" t="s">
+        <v>367</v>
+      </c>
+      <c r="R57" s="31"/>
       <c r="S57" s="26" t="s">
         <v>324</v>
       </c>
       <c r="T57" s="27"/>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>51</v>
       </c>
@@ -23415,10 +23432,10 @@
       </c>
       <c r="K58" s="27"/>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="7"/>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="5">
         <v>1</v>
       </c>
@@ -23432,7 +23449,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <v>2</v>
       </c>
@@ -23446,7 +23463,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A62" s="8">
         <v>3</v>
       </c>
@@ -23461,7 +23478,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="63" spans="1:24">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A63" s="5">
         <v>4</v>
       </c>
@@ -23469,13 +23486,13 @@
         <v>85</v>
       </c>
     </row>
-    <row r="64" spans="1:24">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
       <c r="D64" s="5"/>
     </row>
-    <row r="65" spans="14:24" s="4" customFormat="1">
+    <row r="65" spans="14:24" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="N65" s="5"/>
       <c r="O65" s="5"/>
       <c r="P65" s="5"/>
@@ -23488,7 +23505,7 @@
       <c r="W65" s="5"/>
       <c r="X65" s="5"/>
     </row>
-    <row r="66" spans="14:24" s="4" customFormat="1">
+    <row r="66" spans="14:24" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="N66" s="5"/>
       <c r="O66" s="5"/>
       <c r="P66" s="5"/>
@@ -23501,7 +23518,7 @@
       <c r="W66" s="5"/>
       <c r="X66" s="5"/>
     </row>
-    <row r="67" spans="14:24" s="4" customFormat="1">
+    <row r="67" spans="14:24" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="N67" s="5"/>
       <c r="O67" s="5"/>
       <c r="P67" s="5"/>
@@ -23515,8 +23532,10 @@
       <c r="X67" s="5"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
-  <mergeCells count="470">
+  <sheetProtection algorithmName="SHA-512" hashValue="iBbUXWVWeBTq38dXkg9xB1DHH1X7oQKg6GIA86wNL7HNLS8tA+fUQxX9i0u4SmcMBwGcl5hz5qj/7JuCXyqTAg==" saltValue="rj2A+dYt3UlIb52oUmp0eg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="472">
+    <mergeCell ref="O57:P57"/>
+    <mergeCell ref="Q57:R57"/>
     <mergeCell ref="B58:C58"/>
     <mergeCell ref="D58:E58"/>
     <mergeCell ref="F58:G58"/>
@@ -24006,7 +24025,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X61"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -24036,7 +24055,7 @@
     <col min="26" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>325</v>
       </c>
@@ -24104,7 +24123,7 @@
         <v>46339</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -24152,7 +24171,7 @@
       </c>
       <c r="X2" s="41"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -24200,7 +24219,7 @@
       </c>
       <c r="X3" s="23"/>
     </row>
-    <row r="4" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="4" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -24248,7 +24267,7 @@
       </c>
       <c r="X4" s="29"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -24296,7 +24315,7 @@
       </c>
       <c r="X5" s="31"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -24344,7 +24363,7 @@
       </c>
       <c r="X6" s="37"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -24392,7 +24411,7 @@
       </c>
       <c r="X7" s="23"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -24442,7 +24461,7 @@
       </c>
       <c r="X8" s="31"/>
     </row>
-    <row r="9" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="9" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -24492,7 +24511,7 @@
       </c>
       <c r="X9" s="29"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -24542,7 +24561,7 @@
       </c>
       <c r="X10" s="37"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -24590,7 +24609,7 @@
       </c>
       <c r="X11" s="23"/>
     </row>
-    <row r="12" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="12" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -24638,7 +24657,7 @@
       </c>
       <c r="X12" s="37"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -24686,7 +24705,7 @@
       </c>
       <c r="X13" s="108"/>
     </row>
-    <row r="14" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="14" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -24734,7 +24753,7 @@
       </c>
       <c r="X14" s="31"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -24782,7 +24801,7 @@
       </c>
       <c r="X15" s="23"/>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -24830,7 +24849,7 @@
       </c>
       <c r="X16" s="23"/>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -24851,7 +24870,7 @@
       <c r="W17" s="9"/>
       <c r="X17" s="9"/>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -24875,7 +24894,7 @@
       <c r="W18" s="7"/>
       <c r="X18" s="7"/>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>342</v>
       </c>
@@ -24943,7 +24962,7 @@
         <v>46346</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="20" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>7</v>
       </c>
@@ -24991,7 +25010,7 @@
       </c>
       <c r="X20" s="41"/>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -25030,16 +25049,16 @@
         <v>9</v>
       </c>
       <c r="T21" s="23"/>
-      <c r="U21" s="30" t="s">
+      <c r="U21" s="107" t="s">
         <v>103</v>
       </c>
-      <c r="V21" s="31"/>
-      <c r="W21" s="30" t="s">
+      <c r="V21" s="108"/>
+      <c r="W21" s="107" t="s">
         <v>103</v>
       </c>
-      <c r="X21" s="31"/>
-    </row>
-    <row r="22" spans="1:24">
+      <c r="X21" s="108"/>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>15</v>
       </c>
@@ -25087,7 +25106,7 @@
       </c>
       <c r="X22" s="29"/>
     </row>
-    <row r="23" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="23" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -25135,7 +25154,7 @@
       </c>
       <c r="X23" s="29"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>24</v>
       </c>
@@ -25183,7 +25202,7 @@
       </c>
       <c r="X24" s="37"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>26</v>
       </c>
@@ -25231,7 +25250,7 @@
       </c>
       <c r="X25" s="25"/>
     </row>
-    <row r="26" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="26" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>28</v>
       </c>
@@ -25281,7 +25300,7 @@
       </c>
       <c r="X26" s="106"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>32</v>
       </c>
@@ -25331,7 +25350,7 @@
       </c>
       <c r="X27" s="31"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>35</v>
       </c>
@@ -25381,7 +25400,7 @@
       </c>
       <c r="X28" s="37"/>
     </row>
-    <row r="29" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="29" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>37</v>
       </c>
@@ -25431,7 +25450,7 @@
       </c>
       <c r="X29" s="25"/>
     </row>
-    <row r="30" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="30" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>40</v>
       </c>
@@ -25472,16 +25491,16 @@
         <v>346</v>
       </c>
       <c r="T30" s="37"/>
-      <c r="U30" s="36" t="s">
+      <c r="U30" s="56" t="s">
         <v>346</v>
       </c>
-      <c r="V30" s="37"/>
-      <c r="W30" s="36" t="s">
+      <c r="V30" s="57"/>
+      <c r="W30" s="56" t="s">
         <v>346</v>
       </c>
-      <c r="X30" s="37"/>
-    </row>
-    <row r="31" spans="1:24">
+      <c r="X30" s="57"/>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
         <v>45</v>
       </c>
@@ -25531,7 +25550,7 @@
       </c>
       <c r="X31" s="31"/>
     </row>
-    <row r="32" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="32" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>48</v>
       </c>
@@ -25581,7 +25600,7 @@
       </c>
       <c r="X32" s="25"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>49</v>
       </c>
@@ -25631,7 +25650,7 @@
       </c>
       <c r="X33" s="31"/>
     </row>
-    <row r="34" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="34" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>50</v>
       </c>
@@ -25681,7 +25700,7 @@
       </c>
       <c r="X34" s="106"/>
     </row>
-    <row r="35" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="35" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -25696,7 +25715,7 @@
       <c r="L35" s="7"/>
       <c r="M35" s="7"/>
       <c r="O35" s="30" t="s">
-        <v>336</v>
+        <v>365</v>
       </c>
       <c r="P35" s="31"/>
       <c r="U35" s="9"/>
@@ -25704,7 +25723,7 @@
       <c r="W35" s="9"/>
       <c r="X35" s="9"/>
     </row>
-    <row r="36" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="36" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
@@ -25725,7 +25744,7 @@
       <c r="W36" s="9"/>
       <c r="X36" s="9"/>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -25740,7 +25759,7 @@
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>349</v>
       </c>
@@ -25810,7 +25829,7 @@
         <v>46353</v>
       </c>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>7</v>
       </c>
@@ -25860,7 +25879,7 @@
       </c>
       <c r="X39" s="41"/>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>10</v>
       </c>
@@ -25910,7 +25929,7 @@
       </c>
       <c r="X40" s="23"/>
     </row>
-    <row r="41" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="41" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>15</v>
       </c>
@@ -25958,7 +25977,7 @@
       </c>
       <c r="X41" s="25"/>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>21</v>
       </c>
@@ -26006,7 +26025,7 @@
       </c>
       <c r="X42" s="25"/>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>24</v>
       </c>
@@ -26054,7 +26073,7 @@
       </c>
       <c r="X43" s="37"/>
     </row>
-    <row r="44" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="44" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
         <v>26</v>
       </c>
@@ -26102,7 +26121,7 @@
       </c>
       <c r="X44" s="29"/>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
         <v>28</v>
       </c>
@@ -26150,7 +26169,7 @@
       </c>
       <c r="X45" s="29"/>
     </row>
-    <row r="46" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="46" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>32</v>
       </c>
@@ -26198,7 +26217,7 @@
       </c>
       <c r="X46" s="25"/>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>35</v>
       </c>
@@ -26248,7 +26267,7 @@
       </c>
       <c r="X47" s="37"/>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>37</v>
       </c>
@@ -26298,7 +26317,7 @@
       </c>
       <c r="X48" s="31"/>
     </row>
-    <row r="49" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="49" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>40</v>
       </c>
@@ -26348,7 +26367,7 @@
       </c>
       <c r="X49" s="37"/>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
         <v>45</v>
       </c>
@@ -26398,7 +26417,7 @@
       </c>
       <c r="X50" s="31"/>
     </row>
-    <row r="51" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="51" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>48</v>
       </c>
@@ -26446,7 +26465,7 @@
       </c>
       <c r="X51" s="77"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>49</v>
       </c>
@@ -26494,7 +26513,7 @@
       </c>
       <c r="X52" s="77"/>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>50</v>
       </c>
@@ -26542,7 +26561,7 @@
       </c>
       <c r="X53" s="29"/>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="5">
         <v>1</v>
       </c>
@@ -26556,7 +26575,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="5">
         <v>2</v>
       </c>
@@ -26570,7 +26589,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="8">
         <v>3</v>
       </c>
@@ -26585,7 +26604,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
         <v>4</v>
       </c>
@@ -26593,23 +26612,23 @@
         <v>85</v>
       </c>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Css33PBPgs2Vf5fLt8ZXZ1bpjPxJwAsWoE6hSqLq3JYRfd4wyZjNlRxc7vxOEarRpTzjfOunl/zqOue1feLRaA==" saltValue="XHkNcgZrP2AhbnQqsr4Gxw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="451">
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="F16:G16"/>
@@ -27078,12 +27097,12 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="B1:Y61"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1" style="5" customWidth="1"/>
     <col min="2" max="2" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.140625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="5.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.7109375" style="4" customWidth="1"/>
     <col min="5" max="5" width="6" style="4" customWidth="1"/>
     <col min="6" max="6" width="5.7109375" style="4" customWidth="1"/>
     <col min="7" max="7" width="6.42578125" style="4" bestFit="1" customWidth="1"/>
@@ -27108,8 +27127,8 @@
     <col min="26" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:25" ht="6.75" customHeight="1"/>
-    <row r="2" spans="2:25">
+    <row r="1" spans="2:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>356</v>
       </c>
@@ -27177,7 +27196,7 @@
         <v>46381</v>
       </c>
     </row>
-    <row r="3" spans="2:25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B3" s="17" t="s">
         <v>7</v>
       </c>
@@ -27223,7 +27242,7 @@
       <c r="X3" s="64"/>
       <c r="Y3" s="65"/>
     </row>
-    <row r="4" spans="2:25">
+    <row r="4" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B4" s="17" t="s">
         <v>10</v>
       </c>
@@ -27259,7 +27278,7 @@
       <c r="X4" s="64"/>
       <c r="Y4" s="65"/>
     </row>
-    <row r="5" spans="2:25">
+    <row r="5" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B5" s="17" t="s">
         <v>15</v>
       </c>
@@ -27297,7 +27316,7 @@
       <c r="X5" s="64"/>
       <c r="Y5" s="65"/>
     </row>
-    <row r="6" spans="2:25">
+    <row r="6" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B6" s="17" t="s">
         <v>21</v>
       </c>
@@ -27333,7 +27352,7 @@
       <c r="X6" s="64"/>
       <c r="Y6" s="65"/>
     </row>
-    <row r="7" spans="2:25">
+    <row r="7" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B7" s="17" t="s">
         <v>24</v>
       </c>
@@ -27379,7 +27398,7 @@
       <c r="X7" s="64"/>
       <c r="Y7" s="65"/>
     </row>
-    <row r="8" spans="2:25">
+    <row r="8" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B8" s="18" t="s">
         <v>26</v>
       </c>
@@ -27413,7 +27432,7 @@
       <c r="X8" s="64"/>
       <c r="Y8" s="65"/>
     </row>
-    <row r="9" spans="2:25">
+    <row r="9" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B9" s="18" t="s">
         <v>28</v>
       </c>
@@ -27447,7 +27466,7 @@
       <c r="X9" s="64"/>
       <c r="Y9" s="65"/>
     </row>
-    <row r="10" spans="2:25">
+    <row r="10" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B10" s="18" t="s">
         <v>32</v>
       </c>
@@ -27485,18 +27504,18 @@
       <c r="X10" s="64"/>
       <c r="Y10" s="65"/>
     </row>
-    <row r="11" spans="2:25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B11" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="D11" s="37"/>
-      <c r="E11" s="36" t="s">
+      <c r="D11" s="57"/>
+      <c r="E11" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="F11" s="37"/>
+      <c r="F11" s="57"/>
       <c r="G11" s="30" t="s">
         <v>125</v>
       </c>
@@ -27523,7 +27542,7 @@
       <c r="X11" s="64"/>
       <c r="Y11" s="65"/>
     </row>
-    <row r="12" spans="2:25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B12" s="17" t="s">
         <v>37</v>
       </c>
@@ -27559,18 +27578,18 @@
       <c r="X12" s="64"/>
       <c r="Y12" s="65"/>
     </row>
-    <row r="13" spans="2:25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B13" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="36" t="s">
+      <c r="C13" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="D13" s="37"/>
-      <c r="E13" s="36" t="s">
+      <c r="D13" s="57"/>
+      <c r="E13" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="F13" s="37"/>
+      <c r="F13" s="57"/>
       <c r="G13" s="30" t="s">
         <v>125</v>
       </c>
@@ -27597,7 +27616,7 @@
       <c r="X13" s="64"/>
       <c r="Y13" s="65"/>
     </row>
-    <row r="14" spans="2:25">
+    <row r="14" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B14" s="19" t="s">
         <v>45</v>
       </c>
@@ -27635,7 +27654,7 @@
       <c r="X14" s="64"/>
       <c r="Y14" s="65"/>
     </row>
-    <row r="15" spans="2:25">
+    <row r="15" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B15" s="17" t="s">
         <v>48</v>
       </c>
@@ -27681,7 +27700,7 @@
       <c r="X15" s="64"/>
       <c r="Y15" s="65"/>
     </row>
-    <row r="16" spans="2:25">
+    <row r="16" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B16" s="19" t="s">
         <v>49</v>
       </c>
@@ -27709,7 +27728,7 @@
       <c r="X16" s="64"/>
       <c r="Y16" s="65"/>
     </row>
-    <row r="17" spans="2:25">
+    <row r="17" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B17" s="17" t="s">
         <v>50</v>
       </c>
@@ -27737,7 +27756,7 @@
       <c r="X17" s="64"/>
       <c r="Y17" s="65"/>
     </row>
-    <row r="18" spans="2:25">
+    <row r="18" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B18" s="5"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
@@ -27760,7 +27779,7 @@
       <c r="X18" s="9"/>
       <c r="Y18" s="9"/>
     </row>
-    <row r="19" spans="2:25">
+    <row r="19" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
@@ -27772,7 +27791,7 @@
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
     </row>
-    <row r="20" spans="2:25">
+    <row r="20" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
         <v>361</v>
       </c>
@@ -27840,7 +27859,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="21" spans="2:25">
+    <row r="21" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
@@ -27886,7 +27905,7 @@
       <c r="X21" s="64"/>
       <c r="Y21" s="65"/>
     </row>
-    <row r="22" spans="2:25">
+    <row r="22" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
         <v>10</v>
       </c>
@@ -27914,7 +27933,7 @@
       <c r="X22" s="64"/>
       <c r="Y22" s="65"/>
     </row>
-    <row r="23" spans="2:25">
+    <row r="23" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
         <v>15</v>
       </c>
@@ -27946,7 +27965,7 @@
       <c r="X23" s="64"/>
       <c r="Y23" s="65"/>
     </row>
-    <row r="24" spans="2:25">
+    <row r="24" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="s">
         <v>21</v>
       </c>
@@ -27974,7 +27993,7 @@
       <c r="X24" s="64"/>
       <c r="Y24" s="65"/>
     </row>
-    <row r="25" spans="2:25">
+    <row r="25" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="s">
         <v>24</v>
       </c>
@@ -28020,7 +28039,7 @@
       <c r="X25" s="64"/>
       <c r="Y25" s="65"/>
     </row>
-    <row r="26" spans="2:25">
+    <row r="26" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B26" s="6" t="s">
         <v>26</v>
       </c>
@@ -28048,7 +28067,7 @@
       <c r="X26" s="64"/>
       <c r="Y26" s="65"/>
     </row>
-    <row r="27" spans="2:25">
+    <row r="27" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B27" s="6" t="s">
         <v>28</v>
       </c>
@@ -28078,7 +28097,7 @@
       <c r="X27" s="64"/>
       <c r="Y27" s="65"/>
     </row>
-    <row r="28" spans="2:25">
+    <row r="28" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B28" s="6" t="s">
         <v>32</v>
       </c>
@@ -28112,7 +28131,7 @@
       <c r="X28" s="64"/>
       <c r="Y28" s="65"/>
     </row>
-    <row r="29" spans="2:25">
+    <row r="29" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B29" s="6" t="s">
         <v>35</v>
       </c>
@@ -28140,7 +28159,7 @@
       <c r="X29" s="64"/>
       <c r="Y29" s="65"/>
     </row>
-    <row r="30" spans="2:25">
+    <row r="30" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
         <v>37</v>
       </c>
@@ -28170,7 +28189,7 @@
       <c r="X30" s="64"/>
       <c r="Y30" s="65"/>
     </row>
-    <row r="31" spans="2:25">
+    <row r="31" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B31" s="1" t="s">
         <v>40</v>
       </c>
@@ -28200,7 +28219,7 @@
       <c r="X31" s="64"/>
       <c r="Y31" s="65"/>
     </row>
-    <row r="32" spans="2:25">
+    <row r="32" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B32" s="12" t="s">
         <v>45</v>
       </c>
@@ -28230,7 +28249,7 @@
       <c r="X32" s="64"/>
       <c r="Y32" s="65"/>
     </row>
-    <row r="33" spans="2:25">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B33" s="1" t="s">
         <v>48</v>
       </c>
@@ -28260,7 +28279,7 @@
       <c r="X33" s="64"/>
       <c r="Y33" s="65"/>
     </row>
-    <row r="34" spans="2:25">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B34" s="12" t="s">
         <v>49</v>
       </c>
@@ -28290,7 +28309,7 @@
       <c r="X34" s="64"/>
       <c r="Y34" s="65"/>
     </row>
-    <row r="35" spans="2:25">
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B35" s="1" t="s">
         <v>50</v>
       </c>
@@ -28320,7 +28339,7 @@
       <c r="X35" s="64"/>
       <c r="Y35" s="65"/>
     </row>
-    <row r="36" spans="2:25">
+    <row r="36" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B36" s="5"/>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
@@ -28345,7 +28364,7 @@
       <c r="X36" s="9"/>
       <c r="Y36" s="9"/>
     </row>
-    <row r="37" spans="2:25">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="5"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
@@ -28370,7 +28389,7 @@
       <c r="X37" s="9"/>
       <c r="Y37" s="9"/>
     </row>
-    <row r="38" spans="2:25">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
         <v>363</v>
       </c>
@@ -28417,7 +28436,7 @@
       <c r="X38" s="9"/>
       <c r="Y38" s="9"/>
     </row>
-    <row r="39" spans="2:25">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
@@ -28454,7 +28473,7 @@
       <c r="X39" s="9"/>
       <c r="Y39" s="9"/>
     </row>
-    <row r="40" spans="2:25">
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B40" s="1" t="s">
         <v>10</v>
       </c>
@@ -28481,7 +28500,7 @@
       <c r="X40" s="9"/>
       <c r="Y40" s="9"/>
     </row>
-    <row r="41" spans="2:25">
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B41" s="1" t="s">
         <v>15</v>
       </c>
@@ -28518,7 +28537,7 @@
       <c r="X41" s="9"/>
       <c r="Y41" s="9"/>
     </row>
-    <row r="42" spans="2:25">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B42" s="1" t="s">
         <v>21</v>
       </c>
@@ -28545,7 +28564,7 @@
       <c r="X42" s="9"/>
       <c r="Y42" s="9"/>
     </row>
-    <row r="43" spans="2:25">
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
         <v>24</v>
       </c>
@@ -28582,7 +28601,7 @@
       <c r="X43" s="9"/>
       <c r="Y43" s="9"/>
     </row>
-    <row r="44" spans="2:25">
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B44" s="6" t="s">
         <v>26</v>
       </c>
@@ -28609,7 +28628,7 @@
       <c r="X44" s="9"/>
       <c r="Y44" s="9"/>
     </row>
-    <row r="45" spans="2:25">
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B45" s="6" t="s">
         <v>28</v>
       </c>
@@ -28636,7 +28655,7 @@
       <c r="X45" s="9"/>
       <c r="Y45" s="9"/>
     </row>
-    <row r="46" spans="2:25">
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B46" s="6" t="s">
         <v>32</v>
       </c>
@@ -28663,7 +28682,7 @@
       <c r="X46" s="9"/>
       <c r="Y46" s="9"/>
     </row>
-    <row r="47" spans="2:25">
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B47" s="6" t="s">
         <v>35</v>
       </c>
@@ -28690,7 +28709,7 @@
       <c r="X47" s="9"/>
       <c r="Y47" s="9"/>
     </row>
-    <row r="48" spans="2:25">
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
         <v>37</v>
       </c>
@@ -28717,7 +28736,7 @@
       <c r="X48" s="9"/>
       <c r="Y48" s="9"/>
     </row>
-    <row r="49" spans="2:25">
+    <row r="49" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B49" s="1" t="s">
         <v>40</v>
       </c>
@@ -28744,7 +28763,7 @@
       <c r="X49" s="9"/>
       <c r="Y49" s="9"/>
     </row>
-    <row r="50" spans="2:25">
+    <row r="50" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B50" s="12" t="s">
         <v>45</v>
       </c>
@@ -28773,7 +28792,7 @@
       <c r="X50" s="9"/>
       <c r="Y50" s="9"/>
     </row>
-    <row r="51" spans="2:25">
+    <row r="51" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B51" s="1" t="s">
         <v>48</v>
       </c>
@@ -28800,7 +28819,7 @@
       <c r="X51" s="9"/>
       <c r="Y51" s="9"/>
     </row>
-    <row r="52" spans="2:25">
+    <row r="52" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B52" s="12" t="s">
         <v>49</v>
       </c>
@@ -28827,7 +28846,7 @@
       <c r="X52" s="9"/>
       <c r="Y52" s="9"/>
     </row>
-    <row r="53" spans="2:25">
+    <row r="53" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
         <v>50</v>
       </c>
@@ -28854,7 +28873,7 @@
       <c r="X53" s="9"/>
       <c r="Y53" s="9"/>
     </row>
-    <row r="54" spans="2:25">
+    <row r="54" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B54" s="5"/>
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
@@ -28879,7 +28898,7 @@
       <c r="X54" s="9"/>
       <c r="Y54" s="9"/>
     </row>
-    <row r="55" spans="2:25">
+    <row r="55" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B55" s="5">
         <v>1</v>
       </c>
@@ -28895,7 +28914,7 @@
       <c r="M55" s="7"/>
       <c r="N55" s="7"/>
     </row>
-    <row r="56" spans="2:25">
+    <row r="56" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B56" s="5">
         <v>2</v>
       </c>
@@ -28909,7 +28928,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="57" spans="2:25">
+    <row r="57" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B57" s="8">
         <v>3</v>
       </c>
@@ -28924,7 +28943,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="58" spans="2:25">
+    <row r="58" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B58" s="5">
         <v>4</v>
       </c>
@@ -28938,7 +28957,7 @@
       <c r="M58" s="7"/>
       <c r="N58" s="7"/>
     </row>
-    <row r="59" spans="2:25">
+    <row r="59" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
       <c r="E59" s="5"/>
@@ -28948,7 +28967,7 @@
       <c r="M59" s="7"/>
       <c r="N59" s="7"/>
     </row>
-    <row r="60" spans="2:25">
+    <row r="60" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
       <c r="E60" s="5"/>
@@ -28958,7 +28977,7 @@
       <c r="M60" s="7"/>
       <c r="N60" s="7"/>
     </row>
-    <row r="61" spans="2:25">
+    <row r="61" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
     </row>
@@ -29363,6 +29382,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101001EA62548CDE95149AC1BC8AF3B662818" ma:contentTypeVersion="18" ma:contentTypeDescription="Opprett et nytt dokument." ma:contentTypeScope="" ma:versionID="6b6114bc50e08fd23ab8a89130bf9f95">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="294cf202-ea3b-4503-9866-4c6f0069ff97" xmlns:ns3="8aa5bf20-fe4d-4ec9-a1a3-fcd74c59f201" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dd29bd8d73cdc406ea9db8e88d30c8e6" ns2:_="" ns3:_="">
     <xsd:import namespace="294cf202-ea3b-4503-9866-4c6f0069ff97"/>
@@ -29611,7 +29639,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="294cf202-ea3b-4503-9866-4c6f0069ff97">
@@ -29622,23 +29650,46 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43A824D1-3E40-42BE-9924-6F6DE9E90329}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D158BE0-E8D6-40A3-BD3A-A2FAF7031411}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{179B9B16-67CF-4141-A850-EE327AB51EE2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43A824D1-3E40-42BE-9924-6F6DE9E90329}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="294cf202-ea3b-4503-9866-4c6f0069ff97"/>
+    <ds:schemaRef ds:uri="8aa5bf20-fe4d-4ec9-a1a3-fcd74c59f201"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D158BE0-E8D6-40A3-BD3A-A2FAF7031411}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{179B9B16-67CF-4141-A850-EE327AB51EE2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="8aa5bf20-fe4d-4ec9-a1a3-fcd74c59f201"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="294cf202-ea3b-4503-9866-4c6f0069ff97"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6694" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53BC6E18-9FB4-437F-B5E4-6D44C2976A22}"/>
+  <xr:revisionPtr revIDLastSave="6701" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F01671B3-F58C-4B0E-B7C5-C8D317464BBE}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="38235" yWindow="-165" windowWidth="29130" windowHeight="15810" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38235" yWindow="-165" windowWidth="29130" windowHeight="15810" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Uke 1-6" sheetId="7" r:id="rId1"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4811" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4811" uniqueCount="370">
   <si>
     <t>Uke 01</t>
   </si>
@@ -1103,10 +1103,13 @@
     <t xml:space="preserve">9 SF VD SUR </t>
   </si>
   <si>
+    <t xml:space="preserve">9 SF MS SUR </t>
+  </si>
+  <si>
     <t>TVS</t>
   </si>
   <si>
-    <t xml:space="preserve">9 SF MS SUR </t>
+    <t>NTL/A-vakt</t>
   </si>
   <si>
     <t>SE AN 3</t>
@@ -24535,10 +24538,10 @@
         <v>339</v>
       </c>
       <c r="G10" s="21"/>
-      <c r="H10" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" s="23"/>
+      <c r="H10" s="20" t="s">
+        <v>342</v>
+      </c>
+      <c r="I10" s="21"/>
       <c r="J10" s="22" t="s">
         <v>9</v>
       </c>
@@ -24674,17 +24677,17 @@
       </c>
       <c r="C13" s="21"/>
       <c r="D13" s="44" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E13" s="45"/>
       <c r="F13" s="20" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G13" s="21"/>
-      <c r="H13" s="20" t="s">
-        <v>343</v>
-      </c>
-      <c r="I13" s="21"/>
+      <c r="H13" s="44" t="s">
+        <v>344</v>
+      </c>
+      <c r="I13" s="45"/>
       <c r="J13" s="20" t="s">
         <v>339</v>
       </c>
@@ -24734,7 +24737,7 @@
       </c>
       <c r="I14" s="37"/>
       <c r="J14" s="20" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="K14" s="21"/>
       <c r="N14" s="1" t="s">
@@ -24770,7 +24773,7 @@
       </c>
       <c r="C15" s="21"/>
       <c r="D15" s="20" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E15" s="21"/>
       <c r="F15" s="36" t="s">
@@ -24826,7 +24829,7 @@
       </c>
       <c r="G16" s="47"/>
       <c r="H16" s="78" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I16" s="79"/>
       <c r="J16" s="78" t="s">
@@ -24904,7 +24907,7 @@
     </row>
     <row r="19" spans="1:24">
       <c r="A19" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>1</v>
@@ -24937,7 +24940,7 @@
         <v>46325</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>1</v>
@@ -25031,11 +25034,11 @@
       </c>
       <c r="E21" s="23"/>
       <c r="F21" s="80" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G21" s="81"/>
       <c r="H21" s="80" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="I21" s="81"/>
       <c r="J21" s="22" t="s">
@@ -25190,23 +25193,23 @@
         <v>24</v>
       </c>
       <c r="O24" s="44" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P24" s="45"/>
       <c r="Q24" s="44" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="R24" s="45"/>
       <c r="S24" s="44" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="T24" s="45"/>
       <c r="U24" s="44" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="V24" s="45"/>
       <c r="W24" s="44" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="X24" s="45"/>
     </row>
@@ -25267,11 +25270,11 @@
       </c>
       <c r="C26" s="23"/>
       <c r="D26" s="44" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E26" s="45"/>
       <c r="F26" s="44" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G26" s="45"/>
       <c r="H26" s="22" t="s">
@@ -25279,7 +25282,7 @@
       </c>
       <c r="I26" s="23"/>
       <c r="J26" s="80" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K26" s="81"/>
       <c r="L26" s="7"/>
@@ -25329,7 +25332,7 @@
       </c>
       <c r="I27" s="23"/>
       <c r="J27" s="80" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K27" s="81"/>
       <c r="L27" s="7"/>
@@ -25342,19 +25345,19 @@
       </c>
       <c r="P27" s="47"/>
       <c r="Q27" s="20" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="R27" s="21"/>
       <c r="S27" s="20" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="T27" s="21"/>
       <c r="U27" s="20" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="V27" s="21"/>
       <c r="W27" s="20" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="X27" s="21"/>
     </row>
@@ -25371,11 +25374,11 @@
       </c>
       <c r="E28" s="25"/>
       <c r="F28" s="80" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G28" s="81"/>
       <c r="H28" s="80" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I28" s="81"/>
       <c r="J28" s="22" t="s">
@@ -25388,23 +25391,23 @@
         <v>35</v>
       </c>
       <c r="O28" s="44" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P28" s="45"/>
       <c r="Q28" s="44" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="R28" s="45"/>
       <c r="S28" s="44" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="T28" s="45"/>
       <c r="U28" s="44" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="V28" s="45"/>
       <c r="W28" s="44" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="X28" s="45"/>
     </row>
@@ -25488,23 +25491,23 @@
         <v>40</v>
       </c>
       <c r="O30" s="44" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P30" s="45"/>
       <c r="Q30" s="44" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="R30" s="45"/>
       <c r="S30" s="44" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="T30" s="45"/>
       <c r="U30" s="42" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="V30" s="43"/>
       <c r="W30" s="42" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="X30" s="43"/>
     </row>
@@ -25617,7 +25620,7 @@
       </c>
       <c r="C33" s="21"/>
       <c r="D33" s="20" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E33" s="21"/>
       <c r="F33" s="20" t="s">
@@ -25723,7 +25726,7 @@
       <c r="L35" s="7"/>
       <c r="M35" s="7"/>
       <c r="O35" s="20" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P35" s="21"/>
       <c r="U35" s="9"/>
@@ -25769,7 +25772,7 @@
     </row>
     <row r="38" spans="1:24">
       <c r="A38" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>1</v>
@@ -25804,7 +25807,7 @@
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
       <c r="N38" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>1</v>
@@ -25850,7 +25853,7 @@
       </c>
       <c r="E39" s="39"/>
       <c r="F39" s="38" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G39" s="39"/>
       <c r="H39" s="38" t="s">
@@ -25892,19 +25895,19 @@
         <v>10</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C40" s="21"/>
       <c r="D40" s="20" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E40" s="21"/>
       <c r="F40" s="20" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G40" s="21"/>
       <c r="H40" s="20" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I40" s="21"/>
       <c r="J40" s="20" t="s">
@@ -26138,7 +26141,7 @@
       </c>
       <c r="C45" s="47"/>
       <c r="D45" s="20" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E45" s="21"/>
       <c r="F45" s="22" t="s">
@@ -26182,15 +26185,15 @@
         <v>32</v>
       </c>
       <c r="B46" s="80" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C46" s="81"/>
       <c r="D46" s="80" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E46" s="81"/>
       <c r="F46" s="20" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G46" s="21"/>
       <c r="H46" s="52" t="s">
@@ -26242,7 +26245,7 @@
       </c>
       <c r="G47" s="47"/>
       <c r="H47" s="20" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="I47" s="21"/>
       <c r="J47" s="46" t="s">
@@ -26284,19 +26287,19 @@
       </c>
       <c r="C48" s="21"/>
       <c r="D48" s="20" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E48" s="21"/>
       <c r="F48" s="20" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G48" s="21"/>
       <c r="H48" s="20" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I48" s="21"/>
       <c r="J48" s="20" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="K48" s="21"/>
       <c r="L48" s="7"/>
@@ -26313,15 +26316,15 @@
       </c>
       <c r="R48" s="106"/>
       <c r="S48" s="20" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="T48" s="21"/>
       <c r="U48" s="20" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="V48" s="21"/>
       <c r="W48" s="20" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X48" s="21"/>
     </row>
@@ -26413,15 +26416,15 @@
       </c>
       <c r="R50" s="47"/>
       <c r="S50" s="20" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="T50" s="21"/>
       <c r="U50" s="20" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="V50" s="21"/>
       <c r="W50" s="20" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X50" s="21"/>
     </row>
@@ -26526,11 +26529,11 @@
         <v>50</v>
       </c>
       <c r="B53" s="80" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C53" s="81"/>
       <c r="D53" s="80" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E53" s="81"/>
       <c r="F53" s="22" t="s">
@@ -26636,7 +26639,7 @@
       <c r="C61" s="5"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Css33PBPgs2Vf5fLt8ZXZ1bpjPxJwAsWoE6hSqLq3JYRfd4wyZjNlRxc7vxOEarRpTzjfOunl/zqOue1feLRaA==" saltValue="XHkNcgZrP2AhbnQqsr4Gxw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="451">
     <mergeCell ref="U43:V43"/>
     <mergeCell ref="B33:C33"/>
@@ -27138,7 +27141,7 @@
     <row r="1" spans="2:25" ht="6.75" customHeight="1"/>
     <row r="2" spans="2:25">
       <c r="B2" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>1</v>
@@ -27171,7 +27174,7 @@
         <v>46360</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>1</v>
@@ -27411,11 +27414,11 @@
         <v>26</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D8" s="21"/>
       <c r="E8" s="20" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F8" s="21"/>
       <c r="G8" s="88"/>
@@ -27445,11 +27448,11 @@
         <v>28</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D9" s="21"/>
       <c r="E9" s="20" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F9" s="21"/>
       <c r="G9" s="76"/>
@@ -27457,7 +27460,7 @@
       <c r="I9" s="22"/>
       <c r="J9" s="23"/>
       <c r="K9" s="20" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L9" s="21"/>
       <c r="O9" s="6" t="s">
@@ -27667,19 +27670,19 @@
         <v>48</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D15" s="21"/>
       <c r="E15" s="20" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F15" s="21"/>
       <c r="G15" s="20" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H15" s="21"/>
       <c r="I15" s="20" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J15" s="21"/>
       <c r="K15" s="40" t="s">
@@ -27801,7 +27804,7 @@
     </row>
     <row r="20" spans="2:25">
       <c r="B20" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>1</v>
@@ -27834,7 +27837,7 @@
         <v>46367</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>1</v>
@@ -28399,7 +28402,7 @@
     </row>
     <row r="38" spans="2:25">
       <c r="B38" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>1</v>
@@ -28513,23 +28516,23 @@
         <v>15</v>
       </c>
       <c r="C41" s="109" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D41" s="110"/>
       <c r="E41" s="109" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F41" s="110"/>
       <c r="G41" s="109" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H41" s="110"/>
       <c r="I41" s="109" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J41" s="110"/>
       <c r="K41" s="109" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L41" s="110"/>
       <c r="M41" s="7"/>
@@ -28778,7 +28781,7 @@
       <c r="C50" s="76"/>
       <c r="D50" s="77"/>
       <c r="E50" s="44" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F50" s="45"/>
       <c r="G50" s="76"/>

--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6706" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E00CD81-B9C5-433D-A43F-A5230D29F3CD}"/>
+  <xr:revisionPtr revIDLastSave="6707" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C1F2BCA-35C1-4C89-91E5-17E429338D8A}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Uke 1-6" sheetId="7" r:id="rId1"/>
@@ -26636,6 +26636,7 @@
       <c r="C61" s="5"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="vJCavI+aZcuPd+crq687PVVupl50n2sEBB959auvJXE3oFi7mIGgVTil8e4bCYVuTz8NAnLef1/6LM2iV1JXsA==" saltValue="wh4ROSWIvIZZiaWDQbnCiw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="451">
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="F16:G16"/>

--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6766" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0117AC12-42C0-482A-ACDE-A46CC45A94BD}"/>
+  <xr:revisionPtr revIDLastSave="6768" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2798061A-A00C-4B68-9E7E-B83ED104E888}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -23542,7 +23542,7 @@
       <c r="X67" s="5"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="xV8SaX+JR22ut7LA1GaGNt8UQzYPmoCvAWWiuxf/yVoeCprF+ocLvYYeKGamr2HFBa2DA8N3gx1kDFFi2YJZlw==" saltValue="YM/7IAy2G4PeYaSXZwo5hw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="473">
     <mergeCell ref="S58:T58"/>
     <mergeCell ref="Q17:R17"/>
@@ -26639,6 +26639,7 @@
       <c r="C61" s="5"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="6YQ8lZ0Ph0Egrd1eMGq5/TRWWC3/d5lQOeaMW/w4jZ7vS5YFKgfhAPT/r4oddEoyLRfuhWG6VpkMZ/ZjRN57XA==" saltValue="R6F/C0Zo7ePQ9BsXWCb4Fg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="451">
     <mergeCell ref="U43:V43"/>
     <mergeCell ref="B33:C33"/>

--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6770" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CB06037-BAFD-419A-B9E1-69E58EC7CF83}"/>
+  <xr:revisionPtr revIDLastSave="6773" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6454E0AA-0620-4929-A016-FB25859184C3}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -27361,7 +27361,7 @@
       </c>
       <c r="S6" s="45"/>
       <c r="T6" s="44" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="U6" s="45"/>
       <c r="V6" s="44" t="s">
@@ -28028,7 +28028,7 @@
       </c>
       <c r="S24" s="45"/>
       <c r="T24" s="44" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="U24" s="45"/>
       <c r="V24" s="44" t="s">
@@ -28232,7 +28232,7 @@
       </c>
       <c r="U30" s="45"/>
       <c r="V30" s="44" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="W30" s="45"/>
       <c r="X30" s="60"/>

--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6830" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B617F35-D1B2-4977-B69E-4020B455A29E}"/>
+  <xr:revisionPtr revIDLastSave="6865" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{153C06E8-7468-4615-9572-040EE213A57D}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="7" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Uke 1-6" sheetId="7" r:id="rId1"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4842" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4855" uniqueCount="375">
   <si>
     <t>Uke 01</t>
   </si>
@@ -1112,6 +1112,12 @@
     <t>SE AN 3</t>
   </si>
   <si>
+    <t>Eivind/RY</t>
+  </si>
+  <si>
+    <t>SF ZV 1/opplæring</t>
+  </si>
+  <si>
     <t>Uke 44</t>
   </si>
   <si>
@@ -1133,13 +1139,10 @@
     <t>SE NA 1</t>
   </si>
   <si>
-    <t>A/</t>
+    <t>A/SF ZV 4</t>
   </si>
   <si>
     <t>NTL</t>
-  </si>
-  <si>
-    <t>Eivind</t>
   </si>
   <si>
     <t>SF ZV 4/opplæring</t>
@@ -1408,7 +1411,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -1490,11 +1493,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1827,6 +1845,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -24890,14 +24911,23 @@
       <c r="I17" s="9"/>
       <c r="J17" s="9"/>
       <c r="K17" s="9"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
-      <c r="S17" s="9"/>
-      <c r="T17" s="9"/>
-      <c r="U17" s="9"/>
-      <c r="V17" s="9"/>
-      <c r="W17" s="9"/>
-      <c r="X17" s="9"/>
+      <c r="N17" s="113" t="s">
+        <v>345</v>
+      </c>
+      <c r="O17" s="22" t="s">
+        <v>346</v>
+      </c>
+      <c r="P17" s="23"/>
+      <c r="Q17" s="22" t="s">
+        <v>346</v>
+      </c>
+      <c r="R17" s="23"/>
+      <c r="S17" s="24"/>
+      <c r="T17" s="25"/>
+      <c r="U17" s="24"/>
+      <c r="V17" s="25"/>
+      <c r="W17" s="24"/>
+      <c r="X17" s="25"/>
     </row>
     <row r="18" spans="1:24">
       <c r="A18" s="5"/>
@@ -24925,7 +24955,7 @@
     </row>
     <row r="19" spans="1:24">
       <c r="A19" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>1</v>
@@ -24958,7 +24988,7 @@
         <v>46325</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>1</v>
@@ -25052,11 +25082,11 @@
       </c>
       <c r="E21" s="25"/>
       <c r="F21" s="40" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="G21" s="41"/>
       <c r="H21" s="40" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="I21" s="41"/>
       <c r="J21" s="38" t="s">
@@ -25211,23 +25241,23 @@
         <v>24</v>
       </c>
       <c r="O24" s="26" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="P24" s="27"/>
       <c r="Q24" s="26" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="R24" s="27"/>
       <c r="S24" s="26" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="T24" s="27"/>
       <c r="U24" s="26" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="V24" s="27"/>
       <c r="W24" s="26" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="X24" s="27"/>
     </row>
@@ -25300,7 +25330,7 @@
       </c>
       <c r="I26" s="55"/>
       <c r="J26" s="40" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K26" s="41"/>
       <c r="L26" s="7"/>
@@ -25350,7 +25380,7 @@
       </c>
       <c r="I27" s="25"/>
       <c r="J27" s="40" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="K27" s="41"/>
       <c r="L27" s="7"/>
@@ -25392,15 +25422,15 @@
       </c>
       <c r="E28" s="55"/>
       <c r="F28" s="40" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="G28" s="41"/>
       <c r="H28" s="40" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I28" s="41"/>
       <c r="J28" s="24" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K28" s="25"/>
       <c r="L28" s="7"/>
@@ -25409,23 +25439,23 @@
         <v>35</v>
       </c>
       <c r="O28" s="26" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="P28" s="27"/>
       <c r="Q28" s="26" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="R28" s="27"/>
       <c r="S28" s="26" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="T28" s="27"/>
       <c r="U28" s="26" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="V28" s="27"/>
       <c r="W28" s="26" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="X28" s="27"/>
     </row>
@@ -25509,23 +25539,23 @@
         <v>40</v>
       </c>
       <c r="O30" s="26" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="P30" s="27"/>
       <c r="Q30" s="26" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="R30" s="27"/>
       <c r="S30" s="26" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="T30" s="27"/>
       <c r="U30" s="46" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="V30" s="47"/>
       <c r="W30" s="46" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="X30" s="47"/>
     </row>
@@ -25567,7 +25597,7 @@
       </c>
       <c r="R31" s="21"/>
       <c r="S31" s="26" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="T31" s="27"/>
       <c r="U31" s="20" t="s">
@@ -25730,31 +25760,42 @@
       <c r="X34" s="31"/>
     </row>
     <row r="35" spans="1:24" ht="9.9499999999999993" customHeight="1">
-      <c r="A35" s="5" t="s">
-        <v>354</v>
+      <c r="A35" s="1" t="s">
+        <v>345</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C35" s="23"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9"/>
-      <c r="K35" s="9"/>
+      <c r="D35" s="22" t="s">
+        <v>356</v>
+      </c>
+      <c r="E35" s="23"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="24"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="24"/>
+      <c r="K35" s="25"/>
       <c r="L35" s="7"/>
       <c r="M35" s="7"/>
-      <c r="O35" s="20" t="s">
-        <v>356</v>
-      </c>
-      <c r="P35" s="21"/>
-      <c r="U35" s="9"/>
-      <c r="V35" s="9"/>
-      <c r="W35" s="9"/>
-      <c r="X35" s="9"/>
+      <c r="N35" s="113" t="s">
+        <v>345</v>
+      </c>
+      <c r="O35" s="24"/>
+      <c r="P35" s="25"/>
+      <c r="Q35" s="24"/>
+      <c r="R35" s="25"/>
+      <c r="S35" s="24"/>
+      <c r="T35" s="25"/>
+      <c r="U35" s="22" t="s">
+        <v>346</v>
+      </c>
+      <c r="V35" s="23"/>
+      <c r="W35" s="22" t="s">
+        <v>346</v>
+      </c>
+      <c r="X35" s="23"/>
     </row>
     <row r="36" spans="1:24" ht="9.9499999999999993" customHeight="1">
       <c r="A36" s="5"/>
@@ -25770,8 +25811,10 @@
       <c r="K36" s="9"/>
       <c r="L36" s="7"/>
       <c r="M36" s="7"/>
-      <c r="O36" s="9"/>
-      <c r="P36" s="9"/>
+      <c r="O36" s="20" t="s">
+        <v>357</v>
+      </c>
+      <c r="P36" s="21"/>
       <c r="U36" s="9"/>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
@@ -25794,7 +25837,7 @@
     </row>
     <row r="38" spans="1:24">
       <c r="A38" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>1</v>
@@ -25829,7 +25872,7 @@
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
       <c r="N38" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>1</v>
@@ -25875,7 +25918,7 @@
       </c>
       <c r="E39" s="35"/>
       <c r="F39" s="34" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G39" s="35"/>
       <c r="H39" s="34" t="s">
@@ -25917,19 +25960,19 @@
         <v>10</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C40" s="21"/>
       <c r="D40" s="20" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E40" s="21"/>
       <c r="F40" s="20" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G40" s="21"/>
       <c r="H40" s="20" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="I40" s="21"/>
       <c r="J40" s="20" t="s">
@@ -26123,7 +26166,7 @@
       </c>
       <c r="G44" s="23"/>
       <c r="H44" s="20" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="I44" s="21"/>
       <c r="J44" s="20" t="s">
@@ -26163,7 +26206,7 @@
       </c>
       <c r="C45" s="23"/>
       <c r="D45" s="20" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E45" s="21"/>
       <c r="F45" s="20" t="s">
@@ -26207,15 +26250,15 @@
         <v>32</v>
       </c>
       <c r="B46" s="40" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C46" s="41"/>
       <c r="D46" s="40" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E46" s="41"/>
       <c r="F46" s="20" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G46" s="21"/>
       <c r="H46" s="50" t="s">
@@ -26338,15 +26381,15 @@
       </c>
       <c r="R48" s="31"/>
       <c r="S48" s="20" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="T48" s="21"/>
       <c r="U48" s="20" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="V48" s="21"/>
       <c r="W48" s="20" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="X48" s="21"/>
     </row>
@@ -26430,7 +26473,7 @@
         <v>45</v>
       </c>
       <c r="O50" s="26" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="P50" s="27"/>
       <c r="Q50" s="22" t="s">
@@ -26438,15 +26481,15 @@
       </c>
       <c r="R50" s="23"/>
       <c r="S50" s="20" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="T50" s="21"/>
       <c r="U50" s="20" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="V50" s="21"/>
       <c r="W50" s="20" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="X50" s="21"/>
     </row>
@@ -26551,11 +26594,11 @@
         <v>50</v>
       </c>
       <c r="B53" s="40" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C53" s="41"/>
       <c r="D53" s="40" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E53" s="41"/>
       <c r="F53" s="24" t="s">
@@ -26594,61 +26637,92 @@
       </c>
       <c r="X53" s="29"/>
     </row>
-    <row r="55" spans="1:24">
-      <c r="A55" s="5">
-        <v>1</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="G55" s="5">
-        <v>5</v>
-      </c>
-      <c r="H55" s="5" t="s">
-        <v>80</v>
-      </c>
+    <row r="54" spans="1:24">
+      <c r="A54" s="113" t="s">
+        <v>345</v>
+      </c>
+      <c r="B54" s="24"/>
+      <c r="C54" s="25"/>
+      <c r="D54" s="24"/>
+      <c r="E54" s="25"/>
+      <c r="F54" s="24"/>
+      <c r="G54" s="25"/>
+      <c r="H54" s="22" t="s">
+        <v>346</v>
+      </c>
+      <c r="I54" s="23"/>
+      <c r="J54" s="22" t="s">
+        <v>346</v>
+      </c>
+      <c r="K54" s="23"/>
+      <c r="N54" s="113" t="s">
+        <v>345</v>
+      </c>
+      <c r="O54" s="22" t="s">
+        <v>346</v>
+      </c>
+      <c r="P54" s="23"/>
+      <c r="Q54" s="22" t="s">
+        <v>346</v>
+      </c>
+      <c r="R54" s="23"/>
+      <c r="S54" s="24"/>
+      <c r="T54" s="25"/>
+      <c r="U54" s="24"/>
+      <c r="V54" s="25"/>
+      <c r="W54" s="24"/>
+      <c r="X54" s="25"/>
     </row>
     <row r="56" spans="1:24">
       <c r="A56" s="5">
+        <v>1</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="G56" s="5">
+        <v>5</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24">
+      <c r="A57" s="5">
         <v>2</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B57" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="G56" s="8">
+      <c r="G57" s="8">
         <v>6</v>
       </c>
-      <c r="H56" s="4" t="s">
+      <c r="H57" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="57" spans="1:24">
-      <c r="A57" s="8">
+    <row r="58" spans="1:24">
+      <c r="A58" s="8">
         <v>3</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B58" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C57" s="5"/>
-      <c r="G57" s="8">
-        <v>9</v>
-      </c>
-      <c r="H57" s="4" t="s">
+      <c r="C58" s="5"/>
+      <c r="G58" s="8">
+        <v>9</v>
+      </c>
+      <c r="H58" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="58" spans="1:24">
-      <c r="A58" s="5">
+    <row r="59" spans="1:24">
+      <c r="A59" s="5">
         <v>4</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B59" s="4" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="59" spans="1:24">
-      <c r="A59" s="5"/>
-      <c r="B59" s="5"/>
-      <c r="C59" s="5"/>
     </row>
     <row r="60" spans="1:24">
       <c r="A60" s="5"/>
@@ -26661,7 +26735,30 @@
       <c r="C61" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="452">
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="476">
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="S54:T54"/>
+    <mergeCell ref="U54:V54"/>
+    <mergeCell ref="W54:X54"/>
+    <mergeCell ref="S17:T17"/>
+    <mergeCell ref="U17:V17"/>
+    <mergeCell ref="W17:X17"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="U35:V35"/>
+    <mergeCell ref="W35:X35"/>
+    <mergeCell ref="O54:P54"/>
+    <mergeCell ref="Q54:R54"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="S35:T35"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="J35:K35"/>
     <mergeCell ref="F49:G49"/>
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="F16:G16"/>
@@ -26733,6 +26830,7 @@
     <mergeCell ref="J33:K33"/>
     <mergeCell ref="H40:I40"/>
     <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D35:E35"/>
     <mergeCell ref="H46:I46"/>
     <mergeCell ref="J46:K46"/>
     <mergeCell ref="B47:C47"/>
@@ -26802,6 +26900,7 @@
     <mergeCell ref="O23:P23"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="H25:I25"/>
+    <mergeCell ref="F35:G35"/>
     <mergeCell ref="W43:X43"/>
     <mergeCell ref="O39:P39"/>
     <mergeCell ref="D48:E48"/>
@@ -27019,7 +27118,7 @@
     <mergeCell ref="Q34:R34"/>
     <mergeCell ref="S34:T34"/>
     <mergeCell ref="U34:V34"/>
-    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="O36:P36"/>
     <mergeCell ref="O32:P32"/>
     <mergeCell ref="Q32:R32"/>
     <mergeCell ref="S32:T32"/>
@@ -27162,7 +27261,7 @@
     <row r="1" spans="2:25" ht="6.75" customHeight="1"/>
     <row r="2" spans="2:25">
       <c r="B2" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>1</v>
@@ -27195,7 +27294,7 @@
         <v>46360</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>1</v>
@@ -27443,11 +27542,11 @@
         <v>26</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D8" s="21"/>
       <c r="E8" s="20" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F8" s="21"/>
       <c r="G8" s="96"/>
@@ -27477,11 +27576,11 @@
         <v>28</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D9" s="21"/>
       <c r="E9" s="20" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F9" s="21"/>
       <c r="G9" s="82"/>
@@ -27489,7 +27588,7 @@
       <c r="I9" s="24"/>
       <c r="J9" s="25"/>
       <c r="K9" s="20" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L9" s="21"/>
       <c r="O9" s="6" t="s">
@@ -27599,7 +27698,7 @@
       </c>
       <c r="H12" s="21"/>
       <c r="I12" s="20" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J12" s="21"/>
       <c r="K12" s="22" t="s">
@@ -27717,19 +27816,19 @@
         <v>48</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D15" s="21"/>
       <c r="E15" s="20" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F15" s="21"/>
       <c r="G15" s="20" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H15" s="21"/>
       <c r="I15" s="20" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J15" s="21"/>
       <c r="K15" s="38" t="s">
@@ -27851,7 +27950,7 @@
     </row>
     <row r="20" spans="2:25">
       <c r="B20" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>1</v>
@@ -27884,7 +27983,7 @@
         <v>46367</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>1</v>
@@ -28469,7 +28568,7 @@
     </row>
     <row r="38" spans="2:25">
       <c r="B38" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>1</v>
@@ -28583,23 +28682,23 @@
         <v>15</v>
       </c>
       <c r="C41" s="111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D41" s="112"/>
       <c r="E41" s="111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F41" s="112"/>
       <c r="G41" s="111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H41" s="112"/>
       <c r="I41" s="111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J41" s="112"/>
       <c r="K41" s="111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L41" s="112"/>
       <c r="M41" s="7"/>
@@ -28864,7 +28963,7 @@
       <c r="G50" s="82"/>
       <c r="H50" s="83"/>
       <c r="I50" s="26" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J50" s="27"/>
       <c r="K50" s="24"/>

--- a/input/Arbeidsplan simulatoroperatører.xlsx
+++ b/input/Arbeidsplan simulatoroperatører.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30619"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avinor.sharepoint.com/sites/GRP_Simulatordrift_avd.Vaernes/Delte dokumenter/General/Arbeidsplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6886" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10F2D318-6FA7-4165-8C15-1114E9C67690}"/>
+  <xr:revisionPtr revIDLastSave="6888" documentId="8_{95B923E9-95EE-4F78-B225-2EDB4F75667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E675DF86-C816-4A64-8E57-58E6C9DDE949}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="lgNItpb0Ti65q+mfEUdHXTOz24BuywDWtkFml2UWap2uCRRSwJcP050KCJ16GV7eXwgKeIkDdd7RYQr9U+X8Rw==" workbookSaltValue="526Uxco+d+5gCLKuUY2fsw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="8" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="7" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Uke 1-6" sheetId="7" r:id="rId1"/>
@@ -56,17 +56,17 @@
   <commentList>
     <comment ref="U37" authorId="0" shapeId="0" xr:uid="{65E4B43F-4DA4-4023-9E8A-D4F24A3B2C8C}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentartråd]
+Din versjon av Excel lar deg lese denne kommentartråden. Eventuelle endringer i den vil imidlertid bli fjernet hvis filen åpnes i en nyere versjon av Excel. Finn ut mer: https://go.microsoft.com/fwlink/?linkid=870924
+Kommentar:
     RTC SUR KURS</t>
       </text>
     </comment>
     <comment ref="W37" authorId="1" shapeId="0" xr:uid="{BC2FB818-859F-40F5-95A2-BC57CF0AD42E}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentartråd]
+Din versjon av Excel lar deg lese denne kommentartråden. Eventuelle endringer i den vil imidlertid bli fjernet hvis filen åpnes i en nyere versjon av Excel. Finn ut mer: https://go.microsoft.com/fwlink/?linkid=870924
+Kommentar:
     KUT SUR (RTC)?</t>
       </text>
     </comment>
@@ -1193,20 +1193,20 @@
     <t>Uke 53</t>
   </si>
   <si>
+    <t>Uke 51</t>
+  </si>
+  <si>
+    <t>Kurs simverktøy</t>
+  </si>
+  <si>
     <t>Møte prosjekt</t>
-  </si>
-  <si>
-    <t>Uke 51</t>
-  </si>
-  <si>
-    <t>Kurs simverktøy</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2220,7 +2220,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AA61"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="5" customWidth="1"/>
     <col min="2" max="2" width="6.85546875" style="5" bestFit="1" customWidth="1"/>
@@ -2249,7 +2249,7 @@
     <col min="28" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2322,7 +2322,7 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AA2" s="30"/>
     </row>
-    <row r="3" spans="1:27" ht="9.9499999999999993" customHeight="1">
+    <row r="3" spans="1:27" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AA3" s="44"/>
     </row>
-    <row r="4" spans="1:27">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="AA4" s="30"/>
     </row>
-    <row r="5" spans="1:27" ht="9.9499999999999993" customHeight="1">
+    <row r="5" spans="1:27" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="AA5" s="54"/>
     </row>
-    <row r="6" spans="1:27">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AA6" s="28"/>
     </row>
-    <row r="7" spans="1:27">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="AA7" s="36"/>
     </row>
-    <row r="8" spans="1:27">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="AA8" s="40"/>
     </row>
-    <row r="9" spans="1:27">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AA9" s="54"/>
     </row>
-    <row r="10" spans="1:27">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="AA10" s="28"/>
     </row>
-    <row r="11" spans="1:27">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="AA11" s="44"/>
     </row>
-    <row r="12" spans="1:27">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="AA12" s="40"/>
     </row>
-    <row r="13" spans="1:27">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="AA13" s="40"/>
     </row>
-    <row r="14" spans="1:27">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="AA14" s="54"/>
     </row>
-    <row r="15" spans="1:27">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="AA15" s="30"/>
     </row>
-    <row r="16" spans="1:27">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -3083,7 +3083,7 @@
       <c r="Z16" s="21"/>
       <c r="AA16" s="22"/>
     </row>
-    <row r="17" spans="1:27">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" s="7"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -3118,7 +3118,7 @@
       <c r="Z17" s="21"/>
       <c r="AA17" s="22"/>
     </row>
-    <row r="18" spans="1:27">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" s="7"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -3153,7 +3153,7 @@
       <c r="Z18" s="21"/>
       <c r="AA18" s="22"/>
     </row>
-    <row r="19" spans="1:27">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="U19" s="46"/>
     </row>
-    <row r="20" spans="1:27">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="U20" s="54"/>
     </row>
-    <row r="21" spans="1:27">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -3213,7 +3213,7 @@
       <c r="O21" s="4"/>
       <c r="P21" s="4"/>
     </row>
-    <row r="22" spans="1:27">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -3231,7 +3231,7 @@
       <c r="O22" s="4"/>
       <c r="P22" s="4"/>
     </row>
-    <row r="23" spans="1:27">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>54</v>
       </c>
@@ -3304,7 +3304,7 @@
         <v>46052</v>
       </c>
     </row>
-    <row r="24" spans="1:27">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>7</v>
       </c>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="AA24" s="28"/>
     </row>
-    <row r="25" spans="1:27">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>10</v>
       </c>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="AA25" s="28"/>
     </row>
-    <row r="26" spans="1:27">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>15</v>
       </c>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="AA26" s="54"/>
     </row>
-    <row r="27" spans="1:27">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>21</v>
       </c>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="AA27" s="36"/>
     </row>
-    <row r="28" spans="1:27">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>24</v>
       </c>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="AA28" s="22"/>
     </row>
-    <row r="29" spans="1:27">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>26</v>
       </c>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="AA29" s="70"/>
     </row>
-    <row r="30" spans="1:27">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>28</v>
       </c>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AA30" s="22"/>
     </row>
-    <row r="31" spans="1:27">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
         <v>32</v>
       </c>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="AA31" s="36"/>
     </row>
-    <row r="32" spans="1:27">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
         <v>35</v>
       </c>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AA32" s="54"/>
     </row>
-    <row r="33" spans="1:27">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>37</v>
       </c>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="AA33" s="36"/>
     </row>
-    <row r="34" spans="1:27">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>40</v>
       </c>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="AA34" s="54"/>
     </row>
-    <row r="35" spans="1:27">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
         <v>45</v>
       </c>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AA35" s="40"/>
     </row>
-    <row r="36" spans="1:27">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>48</v>
       </c>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="AA36" s="40"/>
     </row>
-    <row r="37" spans="1:27">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
         <v>49</v>
       </c>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="AA37" s="40"/>
     </row>
-    <row r="38" spans="1:27" ht="9.9499999999999993" customHeight="1">
+    <row r="38" spans="1:27" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>50</v>
       </c>
@@ -4095,7 +4095,7 @@
       <c r="Z38" s="21"/>
       <c r="AA38" s="22"/>
     </row>
-    <row r="39" spans="1:27">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A39" s="4"/>
       <c r="F39" s="7"/>
       <c r="G39" s="7"/>
@@ -4116,7 +4116,7 @@
       <c r="Z39" s="7"/>
       <c r="AA39" s="7"/>
     </row>
-    <row r="40" spans="1:27">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A40" s="7"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
@@ -4134,7 +4134,7 @@
       <c r="O40" s="4"/>
       <c r="P40" s="4"/>
     </row>
-    <row r="41" spans="1:27">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>69</v>
       </c>
@@ -4207,7 +4207,7 @@
         <v>46059</v>
       </c>
     </row>
-    <row r="42" spans="1:27">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>7</v>
       </c>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="AA42" s="38"/>
     </row>
-    <row r="43" spans="1:27">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>10</v>
       </c>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="AA43" s="22"/>
     </row>
-    <row r="44" spans="1:27">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>15</v>
       </c>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="AA44" s="48"/>
     </row>
-    <row r="45" spans="1:27" ht="15" customHeight="1">
+    <row r="45" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>21</v>
       </c>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="AA45" s="36"/>
     </row>
-    <row r="46" spans="1:27">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>24</v>
       </c>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="AA46" s="28"/>
     </row>
-    <row r="47" spans="1:27">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>26</v>
       </c>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="AA47" s="22"/>
     </row>
-    <row r="48" spans="1:27">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>28</v>
       </c>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="AA48" s="36"/>
     </row>
-    <row r="49" spans="1:27">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>32</v>
       </c>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="AA49" s="40"/>
     </row>
-    <row r="50" spans="1:27">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
         <v>35</v>
       </c>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="AA50" s="22"/>
     </row>
-    <row r="51" spans="1:27">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>37</v>
       </c>
@@ -4732,7 +4732,7 @@
       </c>
       <c r="AA51" s="48"/>
     </row>
-    <row r="52" spans="1:27">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>40</v>
       </c>
@@ -4780,7 +4780,7 @@
       </c>
       <c r="AA52" s="40"/>
     </row>
-    <row r="53" spans="1:27">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>45</v>
       </c>
@@ -4828,7 +4828,7 @@
       </c>
       <c r="AA53" s="28"/>
     </row>
-    <row r="54" spans="1:27">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>48</v>
       </c>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AA54" s="40"/>
     </row>
-    <row r="55" spans="1:27">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
         <v>49</v>
       </c>
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AA55" s="48"/>
     </row>
-    <row r="56" spans="1:27">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>50</v>
       </c>
@@ -4964,7 +4964,7 @@
       <c r="Z56" s="21"/>
       <c r="AA56" s="22"/>
     </row>
-    <row r="58" spans="1:27">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
         <v>1</v>
       </c>
@@ -4978,7 +4978,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="59" spans="1:27">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <v>2</v>
       </c>
@@ -4992,7 +4992,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60" spans="1:27">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A60" s="8">
         <v>3</v>
       </c>
@@ -5006,7 +5006,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="61" spans="1:27">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <v>4</v>
       </c>
@@ -5500,7 +5500,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X78"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -5529,7 +5529,7 @@
     <col min="25" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>86</v>
       </c>
@@ -5597,7 +5597,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -5645,7 +5645,7 @@
       </c>
       <c r="X2" s="28"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="X3" s="28"/>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="X4" s="28"/>
     </row>
-    <row r="5" spans="1:24" ht="11.25" customHeight="1">
+    <row r="5" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="X5" s="28"/>
     </row>
-    <row r="6" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="6" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -5837,7 +5837,7 @@
       </c>
       <c r="X6" s="28"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="X7" s="42"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -5933,7 +5933,7 @@
       </c>
       <c r="X8" s="40"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="X9" s="28"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="X10" s="22"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="X11" s="36"/>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="X12" s="40"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -6173,7 +6173,7 @@
       </c>
       <c r="X13" s="36"/>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="X14" s="40"/>
     </row>
-    <row r="15" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="15" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="X15" s="28"/>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -6309,7 +6309,7 @@
       <c r="W16" s="21"/>
       <c r="X16" s="22"/>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="7"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -6333,7 +6333,7 @@
       <c r="W17" s="13"/>
       <c r="X17" s="13"/>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" s="7"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -6357,7 +6357,7 @@
       <c r="W18" s="9"/>
       <c r="X18" s="9"/>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="7"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -6381,7 +6381,7 @@
       <c r="W19" s="9"/>
       <c r="X19" s="9"/>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>97</v>
       </c>
@@ -6449,7 +6449,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>7</v>
       </c>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="X21" s="82"/>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>10</v>
       </c>
@@ -6545,7 +6545,7 @@
       </c>
       <c r="X22" s="28"/>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>15</v>
       </c>
@@ -6593,7 +6593,7 @@
       </c>
       <c r="X23" s="40"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>21</v>
       </c>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="X24" s="40"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
@@ -6689,7 +6689,7 @@
       </c>
       <c r="X25" s="28"/>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>26</v>
       </c>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="X26" s="40"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>28</v>
       </c>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="X27" s="36"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>32</v>
       </c>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="X28" s="56"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>35</v>
       </c>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="X29" s="46"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>37</v>
       </c>
@@ -6931,7 +6931,7 @@
       </c>
       <c r="X30" s="56"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>40</v>
       </c>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="X31" s="36"/>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="s">
         <v>45</v>
       </c>
@@ -7031,7 +7031,7 @@
       </c>
       <c r="X32" s="46"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>48</v>
       </c>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="X33" s="46"/>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
         <v>49</v>
       </c>
@@ -7131,7 +7131,7 @@
       </c>
       <c r="X34" s="56"/>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>50</v>
       </c>
@@ -7171,7 +7171,7 @@
       </c>
       <c r="X35" s="46"/>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>51</v>
       </c>
@@ -7206,7 +7206,7 @@
       <c r="W36" s="9"/>
       <c r="X36" s="9"/>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37" s="5"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
@@ -7229,7 +7229,7 @@
       <c r="W37" s="9"/>
       <c r="X37" s="9"/>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38" s="5"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
@@ -7252,12 +7252,12 @@
       <c r="W38" s="9"/>
       <c r="X38" s="9"/>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="M39" s="7"/>
       <c r="S39" s="9"/>
       <c r="T39" s="9"/>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>109</v>
       </c>
@@ -7326,7 +7326,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>7</v>
       </c>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="X41" s="28"/>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>10</v>
       </c>
@@ -7423,7 +7423,7 @@
       </c>
       <c r="X42" s="28"/>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>15</v>
       </c>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="X43" s="28"/>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>21</v>
       </c>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="X44" s="44"/>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>24</v>
       </c>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="X45" s="28"/>
     </row>
-    <row r="46" spans="1:24" ht="10.5" customHeight="1">
+    <row r="46" spans="1:24" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>26</v>
       </c>
@@ -7616,7 +7616,7 @@
       </c>
       <c r="X46" s="40"/>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>28</v>
       </c>
@@ -7665,7 +7665,7 @@
       </c>
       <c r="X47" s="40"/>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>32</v>
       </c>
@@ -7714,7 +7714,7 @@
       </c>
       <c r="X48" s="46"/>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>35</v>
       </c>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="X49" s="44"/>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>37</v>
       </c>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="X50" s="46"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>40</v>
       </c>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="X51" s="36"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>45</v>
       </c>
@@ -7908,7 +7908,7 @@
       </c>
       <c r="X52" s="40"/>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>48</v>
       </c>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="X53" s="36"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>49</v>
       </c>
@@ -8005,7 +8005,7 @@
       </c>
       <c r="X54" s="36"/>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>50</v>
       </c>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="X55" s="46"/>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>51</v>
       </c>
@@ -8085,7 +8085,7 @@
       <c r="W56" s="9"/>
       <c r="X56" s="9"/>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="7"/>
       <c r="B57" s="9"/>
       <c r="C57" s="9"/>
@@ -8110,7 +8110,7 @@
       <c r="W57" s="9"/>
       <c r="X57" s="9"/>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
         <v>1</v>
       </c>
@@ -8124,7 +8124,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <v>2</v>
       </c>
@@ -8138,7 +8138,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="8">
         <v>3</v>
       </c>
@@ -8158,7 +8158,7 @@
       <c r="W60" s="9"/>
       <c r="X60" s="9"/>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <v>4</v>
       </c>
@@ -8170,34 +8170,34 @@
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
       <c r="O62" s="9"/>
       <c r="P62" s="9"/>
       <c r="Q62" s="9"/>
       <c r="R62" s="9"/>
     </row>
-    <row r="71" spans="13:13">
+    <row r="71" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M71" s="5"/>
     </row>
-    <row r="72" spans="13:13">
+    <row r="72" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M72" s="5"/>
     </row>
-    <row r="73" spans="13:13">
+    <row r="73" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M73" s="5"/>
     </row>
-    <row r="74" spans="13:13">
+    <row r="74" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M74" s="5"/>
     </row>
-    <row r="75" spans="13:13">
+    <row r="75" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M75" s="5"/>
     </row>
-    <row r="76" spans="13:13">
+    <row r="76" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M76" s="5"/>
     </row>
-    <row r="77" spans="13:13">
+    <row r="77" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M77" s="5"/>
     </row>
-    <row r="78" spans="13:13">
+    <row r="78" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M78" s="5"/>
     </row>
   </sheetData>
@@ -8681,7 +8681,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X66"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -8711,7 +8711,7 @@
     <col min="27" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>116</v>
       </c>
@@ -8779,7 +8779,7 @@
         <v>46129</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -8827,7 +8827,7 @@
       </c>
       <c r="X2" s="38"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -8875,7 +8875,7 @@
       </c>
       <c r="X3" s="72"/>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -8923,7 +8923,7 @@
       </c>
       <c r="X4" s="36"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -8971,7 +8971,7 @@
       </c>
       <c r="X5" s="72"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="X6" s="28"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -9067,7 +9067,7 @@
       </c>
       <c r="X7" s="36"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -9115,7 +9115,7 @@
       </c>
       <c r="X8" s="56"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -9163,7 +9163,7 @@
       </c>
       <c r="X9" s="36"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -9211,7 +9211,7 @@
       </c>
       <c r="X10" s="56"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -9259,7 +9259,7 @@
       </c>
       <c r="X11" s="36"/>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -9307,7 +9307,7 @@
       </c>
       <c r="X12" s="36"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -9355,7 +9355,7 @@
       </c>
       <c r="X13" s="36"/>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="X14" s="72"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -9451,7 +9451,7 @@
       </c>
       <c r="X15" s="72"/>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -9491,7 +9491,7 @@
       <c r="W16" s="21"/>
       <c r="X16" s="22"/>
     </row>
-    <row r="17" spans="1:24" ht="11.25" customHeight="1">
+    <row r="17" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
       <c r="N17" s="7"/>
@@ -9504,7 +9504,7 @@
       </c>
       <c r="V17" s="36"/>
     </row>
-    <row r="18" spans="1:24" ht="11.25" customHeight="1">
+    <row r="18" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
       <c r="N18" s="7"/>
@@ -9513,7 +9513,7 @@
       </c>
       <c r="P18" s="36"/>
     </row>
-    <row r="19" spans="1:24" ht="11.25" customHeight="1">
+    <row r="19" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
       <c r="N19" s="7"/>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="P19" s="72"/>
     </row>
-    <row r="20" spans="1:24" ht="11.25" customHeight="1">
+    <row r="20" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
       <c r="N20" s="7"/>
@@ -9531,7 +9531,7 @@
       </c>
       <c r="P20" s="72"/>
     </row>
-    <row r="21" spans="1:24" ht="11.25" customHeight="1">
+    <row r="21" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
       <c r="N21" s="7"/>
@@ -9540,7 +9540,7 @@
       </c>
       <c r="P21" s="72"/>
     </row>
-    <row r="22" spans="1:24" ht="11.25" customHeight="1">
+    <row r="22" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
       <c r="N22" s="7"/>
@@ -9549,17 +9549,17 @@
       </c>
       <c r="P22" s="72"/>
     </row>
-    <row r="23" spans="1:24" ht="11.25" customHeight="1">
+    <row r="23" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
       <c r="N23" s="7"/>
     </row>
-    <row r="24" spans="1:24" ht="11.25" customHeight="1">
+    <row r="24" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
       <c r="N24" s="7"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>154</v>
       </c>
@@ -9629,7 +9629,7 @@
         <v>46136</v>
       </c>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>7</v>
       </c>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="X26" s="28"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>10</v>
       </c>
@@ -9721,7 +9721,7 @@
       </c>
       <c r="X27" s="30"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>15</v>
       </c>
@@ -9767,7 +9767,7 @@
       </c>
       <c r="X28" s="78"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>21</v>
       </c>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="X29" s="40"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>24</v>
       </c>
@@ -9859,7 +9859,7 @@
       </c>
       <c r="X30" s="28"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
         <v>26</v>
       </c>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="X31" s="40"/>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
         <v>28</v>
       </c>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="X32" s="78"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
         <v>32</v>
       </c>
@@ -9993,7 +9993,7 @@
       </c>
       <c r="X33" s="54"/>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
         <v>35</v>
       </c>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="X34" s="28"/>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>37</v>
       </c>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="X35" s="36"/>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>40</v>
       </c>
@@ -10131,7 +10131,7 @@
       </c>
       <c r="X36" s="54"/>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
         <v>45</v>
       </c>
@@ -10177,7 +10177,7 @@
       </c>
       <c r="X37" s="36"/>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>48</v>
       </c>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="X38" s="40"/>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39" s="12" t="s">
         <v>49</v>
       </c>
@@ -10269,7 +10269,7 @@
       </c>
       <c r="X39" s="54"/>
     </row>
-    <row r="40" spans="1:24" ht="11.25" customHeight="1">
+    <row r="40" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>50</v>
       </c>
@@ -10311,7 +10311,7 @@
       <c r="W40" s="21"/>
       <c r="X40" s="22"/>
     </row>
-    <row r="41" spans="1:24" ht="11.25" customHeight="1">
+    <row r="41" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -10326,7 +10326,7 @@
       <c r="L41" s="5"/>
       <c r="M41" s="5"/>
     </row>
-    <row r="42" spans="1:24" ht="11.25" customHeight="1">
+    <row r="42" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -10341,7 +10341,7 @@
       <c r="L42" s="5"/>
       <c r="M42" s="5"/>
     </row>
-    <row r="43" spans="1:24" ht="11.25" customHeight="1">
+    <row r="43" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>166</v>
       </c>
@@ -10411,7 +10411,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="44" spans="1:24" ht="11.25" customHeight="1">
+    <row r="44" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>7</v>
       </c>
@@ -10457,7 +10457,7 @@
       <c r="W44" s="33"/>
       <c r="X44" s="34"/>
     </row>
-    <row r="45" spans="1:24" ht="11.25" customHeight="1">
+    <row r="45" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>10</v>
       </c>
@@ -10503,7 +10503,7 @@
       <c r="W45" s="33"/>
       <c r="X45" s="34"/>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>15</v>
       </c>
@@ -10549,7 +10549,7 @@
       <c r="W46" s="33"/>
       <c r="X46" s="34"/>
     </row>
-    <row r="47" spans="1:24" ht="11.25" customHeight="1">
+    <row r="47" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>21</v>
       </c>
@@ -10593,7 +10593,7 @@
       <c r="W47" s="33"/>
       <c r="X47" s="34"/>
     </row>
-    <row r="48" spans="1:24" ht="11.25" customHeight="1">
+    <row r="48" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>24</v>
       </c>
@@ -10637,7 +10637,7 @@
       <c r="W48" s="33"/>
       <c r="X48" s="34"/>
     </row>
-    <row r="49" spans="1:24" ht="11.25" customHeight="1">
+    <row r="49" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>26</v>
       </c>
@@ -10681,7 +10681,7 @@
       <c r="W49" s="33"/>
       <c r="X49" s="34"/>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
         <v>28</v>
       </c>
@@ -10725,7 +10725,7 @@
       <c r="W50" s="33"/>
       <c r="X50" s="34"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
         <v>32</v>
       </c>
@@ -10771,7 +10771,7 @@
       <c r="W51" s="33"/>
       <c r="X51" s="34"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
         <v>35</v>
       </c>
@@ -10817,7 +10817,7 @@
       <c r="W52" s="33"/>
       <c r="X52" s="34"/>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>37</v>
       </c>
@@ -10863,7 +10863,7 @@
       <c r="W53" s="33"/>
       <c r="X53" s="34"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>40</v>
       </c>
@@ -10909,7 +10909,7 @@
       <c r="W54" s="33"/>
       <c r="X54" s="34"/>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
         <v>45</v>
       </c>
@@ -10955,7 +10955,7 @@
       <c r="W55" s="33"/>
       <c r="X55" s="34"/>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>48</v>
       </c>
@@ -11001,7 +11001,7 @@
       <c r="W56" s="33"/>
       <c r="X56" s="34"/>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
         <v>49</v>
       </c>
@@ -11047,7 +11047,7 @@
       <c r="W57" s="33"/>
       <c r="X57" s="34"/>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>50</v>
       </c>
@@ -11087,7 +11087,7 @@
       <c r="W58" s="33"/>
       <c r="X58" s="34"/>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="O59" s="43" t="s">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="T59" s="44"/>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="5">
         <v>1</v>
       </c>
@@ -11121,7 +11121,7 @@
       </c>
       <c r="P60" s="40"/>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <v>2</v>
       </c>
@@ -11135,7 +11135,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A62" s="8">
         <v>3</v>
       </c>
@@ -11149,7 +11149,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="63" spans="1:24">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A63" s="5">
         <v>4</v>
       </c>
@@ -11157,17 +11157,17 @@
         <v>85</v>
       </c>
     </row>
-    <row r="64" spans="1:24">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
@@ -11655,7 +11655,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X62"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -11684,7 +11684,7 @@
     <col min="25" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>178</v>
       </c>
@@ -11752,7 +11752,7 @@
         <v>46171</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="X2" s="38"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="X3" s="28"/>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="X4" s="22"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -11937,7 +11937,7 @@
       </c>
       <c r="X5" s="44"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -11983,7 +11983,7 @@
       </c>
       <c r="X6" s="28"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -12029,7 +12029,7 @@
       </c>
       <c r="X7" s="78"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -12075,7 +12075,7 @@
       </c>
       <c r="X8" s="78"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -12121,7 +12121,7 @@
       </c>
       <c r="X9" s="95"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -12167,7 +12167,7 @@
       </c>
       <c r="X10" s="56"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -12213,7 +12213,7 @@
       </c>
       <c r="X11" s="44"/>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -12259,7 +12259,7 @@
       </c>
       <c r="X12" s="56"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -12305,7 +12305,7 @@
       </c>
       <c r="X13" s="95"/>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -12351,7 +12351,7 @@
       </c>
       <c r="X14" s="56"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -12397,7 +12397,7 @@
       </c>
       <c r="X15" s="44"/>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -12437,7 +12437,7 @@
       <c r="W16" s="21"/>
       <c r="X16" s="22"/>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>195</v>
       </c>
@@ -12464,7 +12464,7 @@
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B18" s="35" t="s">
         <v>196</v>
       </c>
@@ -12476,7 +12476,7 @@
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
@@ -12485,7 +12485,7 @@
       <c r="R19" s="4"/>
       <c r="S19" s="4"/>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -12496,7 +12496,7 @@
       <c r="R20" s="4"/>
       <c r="S20" s="4"/>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>197</v>
       </c>
@@ -12564,7 +12564,7 @@
         <v>46178</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
@@ -12610,7 +12610,7 @@
       </c>
       <c r="X22" s="38"/>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>10</v>
       </c>
@@ -12656,7 +12656,7 @@
       </c>
       <c r="X23" s="30"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>15</v>
       </c>
@@ -12702,7 +12702,7 @@
       </c>
       <c r="X24" s="22"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>21</v>
       </c>
@@ -12748,7 +12748,7 @@
       </c>
       <c r="X25" s="95"/>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
@@ -12794,7 +12794,7 @@
       </c>
       <c r="X26" s="28"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
@@ -12840,7 +12840,7 @@
       </c>
       <c r="X27" s="56"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>28</v>
       </c>
@@ -12886,7 +12886,7 @@
       </c>
       <c r="X28" s="95"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>32</v>
       </c>
@@ -12932,7 +12932,7 @@
       </c>
       <c r="X29" s="28"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>35</v>
       </c>
@@ -12978,7 +12978,7 @@
       </c>
       <c r="X30" s="28"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
@@ -13024,7 +13024,7 @@
       </c>
       <c r="X31" s="44"/>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>40</v>
       </c>
@@ -13072,7 +13072,7 @@
       </c>
       <c r="X32" s="36"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>45</v>
       </c>
@@ -13120,7 +13120,7 @@
       </c>
       <c r="X33" s="56"/>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>48</v>
       </c>
@@ -13168,7 +13168,7 @@
       </c>
       <c r="X34" s="44"/>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
         <v>49</v>
       </c>
@@ -13216,7 +13216,7 @@
       </c>
       <c r="X35" s="56"/>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>50</v>
       </c>
@@ -13258,7 +13258,7 @@
       </c>
       <c r="X36" s="44"/>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
       <c r="N37" s="4"/>
@@ -13266,7 +13266,7 @@
       <c r="Q37" s="4"/>
       <c r="R37" s="4"/>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
       <c r="N38" s="4"/>
@@ -13274,7 +13274,7 @@
       <c r="Q38" s="4"/>
       <c r="R38" s="4"/>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L39" s="7"/>
       <c r="M39" s="7"/>
       <c r="N39" s="4"/>
@@ -13282,7 +13282,7 @@
       <c r="Q39" s="4"/>
       <c r="R39" s="4"/>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>212</v>
       </c>
@@ -13352,7 +13352,7 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>7</v>
       </c>
@@ -13402,7 +13402,7 @@
       </c>
       <c r="X41" s="38"/>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>10</v>
       </c>
@@ -13452,7 +13452,7 @@
       </c>
       <c r="X42" s="22"/>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>15</v>
       </c>
@@ -13502,7 +13502,7 @@
       </c>
       <c r="X43" s="22"/>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>21</v>
       </c>
@@ -13550,7 +13550,7 @@
       </c>
       <c r="X44" s="54"/>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>24</v>
       </c>
@@ -13598,7 +13598,7 @@
       </c>
       <c r="X45" s="28"/>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>26</v>
       </c>
@@ -13646,7 +13646,7 @@
       </c>
       <c r="X46" s="28"/>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>28</v>
       </c>
@@ -13694,7 +13694,7 @@
       </c>
       <c r="X47" s="62"/>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>32</v>
       </c>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="X48" s="30"/>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>35</v>
       </c>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="X49" s="28"/>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>37</v>
       </c>
@@ -13838,7 +13838,7 @@
       </c>
       <c r="X50" s="28"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>40</v>
       </c>
@@ -13888,7 +13888,7 @@
       </c>
       <c r="X51" s="28"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>45</v>
       </c>
@@ -13938,7 +13938,7 @@
       </c>
       <c r="X52" s="54"/>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>48</v>
       </c>
@@ -13988,7 +13988,7 @@
       </c>
       <c r="X53" s="54"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>49</v>
       </c>
@@ -14036,7 +14036,7 @@
       </c>
       <c r="X54" s="30"/>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>50</v>
       </c>
@@ -14078,7 +14078,7 @@
       <c r="W55" s="21"/>
       <c r="X55" s="22"/>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="8"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -14108,7 +14108,7 @@
       <c r="W56" s="21"/>
       <c r="X56" s="22"/>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="8"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -14133,7 +14133,7 @@
       <c r="W57" s="9"/>
       <c r="X57" s="9"/>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="8"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -14146,7 +14146,7 @@
       <c r="L58" s="7"/>
       <c r="M58" s="7"/>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <v>1</v>
       </c>
@@ -14171,7 +14171,7 @@
       <c r="W59" s="4"/>
       <c r="X59" s="4"/>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="5">
         <v>2</v>
       </c>
@@ -14185,7 +14185,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="8">
         <v>3</v>
       </c>
@@ -14199,7 +14199,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A62" s="5">
         <v>4</v>
       </c>
@@ -14691,7 +14691,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X61"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -14720,7 +14720,7 @@
     <col min="25" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>229</v>
       </c>
@@ -14788,7 +14788,7 @@
         <v>46213</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -14836,7 +14836,7 @@
       </c>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -14884,7 +14884,7 @@
       </c>
       <c r="X3" s="30"/>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -14932,7 +14932,7 @@
       </c>
       <c r="X4" s="42"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -14980,7 +14980,7 @@
       </c>
       <c r="X5" s="30"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -15028,7 +15028,7 @@
       </c>
       <c r="X6" s="42"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -15076,7 +15076,7 @@
       </c>
       <c r="X7" s="22"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -15124,7 +15124,7 @@
       </c>
       <c r="X8" s="22"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -15172,7 +15172,7 @@
       </c>
       <c r="X9" s="22"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -15220,7 +15220,7 @@
       </c>
       <c r="X10" s="30"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -15268,7 +15268,7 @@
       </c>
       <c r="X11" s="30"/>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -15316,7 +15316,7 @@
       </c>
       <c r="X12" s="22"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -15364,7 +15364,7 @@
       </c>
       <c r="X13" s="22"/>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -15412,7 +15412,7 @@
       </c>
       <c r="X14" s="22"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -15460,7 +15460,7 @@
       </c>
       <c r="X15" s="22"/>
     </row>
-    <row r="16" spans="1:24" ht="11.25" customHeight="1">
+    <row r="16" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -15504,9 +15504,9 @@
       </c>
       <c r="X16" s="30"/>
     </row>
-    <row r="17" spans="1:24" ht="11.25" customHeight="1"/>
-    <row r="18" spans="1:24" ht="11.25" customHeight="1"/>
-    <row r="19" spans="1:24" ht="11.25" customHeight="1">
+    <row r="17" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>233</v>
       </c>
@@ -15574,7 +15574,7 @@
         <v>46220</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="11.25" customHeight="1">
+    <row r="20" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>7</v>
       </c>
@@ -15622,7 +15622,7 @@
       </c>
       <c r="X20" s="30"/>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -15670,7 +15670,7 @@
       </c>
       <c r="X21" s="30"/>
     </row>
-    <row r="22" spans="1:24" ht="11.25" customHeight="1">
+    <row r="22" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>15</v>
       </c>
@@ -15718,7 +15718,7 @@
       </c>
       <c r="X22" s="30"/>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -15766,7 +15766,7 @@
       </c>
       <c r="X23" s="30"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>24</v>
       </c>
@@ -15814,7 +15814,7 @@
       </c>
       <c r="X24" s="30"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>26</v>
       </c>
@@ -15862,7 +15862,7 @@
       </c>
       <c r="X25" s="30"/>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>28</v>
       </c>
@@ -15910,7 +15910,7 @@
       </c>
       <c r="X26" s="22"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>32</v>
       </c>
@@ -15958,7 +15958,7 @@
       </c>
       <c r="X27" s="22"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>35</v>
       </c>
@@ -16006,7 +16006,7 @@
       </c>
       <c r="X28" s="30"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>37</v>
       </c>
@@ -16056,7 +16056,7 @@
       </c>
       <c r="X29" s="30"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>40</v>
       </c>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="X30" s="30"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
         <v>45</v>
       </c>
@@ -16156,7 +16156,7 @@
       </c>
       <c r="X31" s="22"/>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>48</v>
       </c>
@@ -16206,7 +16206,7 @@
       </c>
       <c r="X32" s="30"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>49</v>
       </c>
@@ -16256,7 +16256,7 @@
       </c>
       <c r="X33" s="22"/>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>50</v>
       </c>
@@ -16306,7 +16306,7 @@
       </c>
       <c r="X34" s="30"/>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="5"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -16331,11 +16331,11 @@
       <c r="W35" s="9"/>
       <c r="X35" s="9"/>
     </row>
-    <row r="36" spans="1:24" ht="11.25" customHeight="1">
+    <row r="36" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L36" s="7"/>
       <c r="M36" s="7"/>
     </row>
-    <row r="37" spans="1:24" ht="11.25" customHeight="1">
+    <row r="37" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>236</v>
       </c>
@@ -16405,7 +16405,7 @@
         <v>46227</v>
       </c>
     </row>
-    <row r="38" spans="1:24" ht="11.25" customHeight="1">
+    <row r="38" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>7</v>
       </c>
@@ -16455,7 +16455,7 @@
       </c>
       <c r="X38" s="30"/>
     </row>
-    <row r="39" spans="1:24" ht="10.5" customHeight="1">
+    <row r="39" spans="1:24" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>10</v>
       </c>
@@ -16505,7 +16505,7 @@
       </c>
       <c r="X39" s="30"/>
     </row>
-    <row r="40" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="40" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>15</v>
       </c>
@@ -16555,7 +16555,7 @@
       </c>
       <c r="X40" s="30"/>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>21</v>
       </c>
@@ -16603,7 +16603,7 @@
       </c>
       <c r="X41" s="30"/>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>24</v>
       </c>
@@ -16651,7 +16651,7 @@
       </c>
       <c r="X42" s="30"/>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
         <v>26</v>
       </c>
@@ -16699,7 +16699,7 @@
       </c>
       <c r="X43" s="30"/>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
         <v>28</v>
       </c>
@@ -16747,7 +16747,7 @@
       </c>
       <c r="X44" s="22"/>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
         <v>32</v>
       </c>
@@ -16795,7 +16795,7 @@
       </c>
       <c r="X45" s="22"/>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>35</v>
       </c>
@@ -16843,7 +16843,7 @@
       </c>
       <c r="X46" s="30"/>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>37</v>
       </c>
@@ -16891,7 +16891,7 @@
       </c>
       <c r="X47" s="22"/>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>40</v>
       </c>
@@ -16939,7 +16939,7 @@
       </c>
       <c r="X48" s="30"/>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>45</v>
       </c>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="X49" s="22"/>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>48</v>
       </c>
@@ -17035,7 +17035,7 @@
       </c>
       <c r="X50" s="30"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>49</v>
       </c>
@@ -17083,7 +17083,7 @@
       </c>
       <c r="X51" s="22"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>50</v>
       </c>
@@ -17131,7 +17131,7 @@
       </c>
       <c r="X52" s="30"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="5">
         <v>1</v>
       </c>
@@ -17145,7 +17145,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="5">
         <v>2</v>
       </c>
@@ -17161,7 +17161,7 @@
       <c r="L55" s="7"/>
       <c r="M55" s="7"/>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="8">
         <v>3</v>
       </c>
@@ -17177,7 +17177,7 @@
       <c r="L56" s="7"/>
       <c r="M56" s="7"/>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="5">
         <v>4</v>
       </c>
@@ -17187,15 +17187,15 @@
       <c r="L57" s="7"/>
       <c r="M57" s="7"/>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L59" s="7"/>
       <c r="M59" s="7"/>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L60" s="7"/>
       <c r="M60" s="7"/>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -17678,7 +17678,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X65"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -17707,7 +17707,7 @@
     <col min="25" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>240</v>
       </c>
@@ -17775,7 +17775,7 @@
         <v>46255</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -17823,7 +17823,7 @@
       </c>
       <c r="X2" s="38"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -17871,7 +17871,7 @@
       </c>
       <c r="X3" s="22"/>
     </row>
-    <row r="4" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="4" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -17919,7 +17919,7 @@
       </c>
       <c r="X4" s="28"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -17967,7 +17967,7 @@
       </c>
       <c r="X5" s="40"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -18015,7 +18015,7 @@
       </c>
       <c r="X6" s="28"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -18063,7 +18063,7 @@
       </c>
       <c r="X7" s="22"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -18111,7 +18111,7 @@
       </c>
       <c r="X8" s="22"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -18159,7 +18159,7 @@
       </c>
       <c r="X9" s="30"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -18207,7 +18207,7 @@
       </c>
       <c r="X10" s="28"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -18255,7 +18255,7 @@
       </c>
       <c r="X11" s="28"/>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -18303,7 +18303,7 @@
       </c>
       <c r="X12" s="30"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -18351,7 +18351,7 @@
       </c>
       <c r="X13" s="30"/>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -18399,7 +18399,7 @@
       </c>
       <c r="X14" s="28"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -18447,7 +18447,7 @@
       </c>
       <c r="X15" s="30"/>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -18493,7 +18493,7 @@
       </c>
       <c r="X16" s="40"/>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -18521,7 +18521,7 @@
       <c r="W17" s="21"/>
       <c r="X17" s="22"/>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -18549,7 +18549,7 @@
       <c r="W18" s="21"/>
       <c r="X18" s="22"/>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -18573,7 +18573,7 @@
       <c r="W19" s="4"/>
       <c r="X19" s="4"/>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -18597,7 +18597,7 @@
       <c r="W20" s="4"/>
       <c r="X20" s="4"/>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>249</v>
       </c>
@@ -18665,7 +18665,7 @@
         <v>46262</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
@@ -18713,7 +18713,7 @@
       </c>
       <c r="X22" s="38"/>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>10</v>
       </c>
@@ -18761,7 +18761,7 @@
       </c>
       <c r="X23" s="22"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>15</v>
       </c>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="X24" s="40"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>21</v>
       </c>
@@ -18857,7 +18857,7 @@
       </c>
       <c r="X25" s="40"/>
     </row>
-    <row r="26" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="26" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
@@ -18905,7 +18905,7 @@
       </c>
       <c r="X26" s="99"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
@@ -18953,7 +18953,7 @@
       </c>
       <c r="X27" s="72"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>28</v>
       </c>
@@ -19001,7 +19001,7 @@
       </c>
       <c r="X28" s="28"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>32</v>
       </c>
@@ -19049,7 +19049,7 @@
       </c>
       <c r="X29" s="30"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>35</v>
       </c>
@@ -19097,7 +19097,7 @@
       </c>
       <c r="X30" s="72"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
@@ -19145,7 +19145,7 @@
       </c>
       <c r="X31" s="28"/>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>40</v>
       </c>
@@ -19193,7 +19193,7 @@
       </c>
       <c r="X32" s="46"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>45</v>
       </c>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="X33" s="46"/>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>48</v>
       </c>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="X34" s="46"/>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
         <v>49</v>
       </c>
@@ -19337,7 +19337,7 @@
       </c>
       <c r="X35" s="30"/>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>50</v>
       </c>
@@ -19385,15 +19385,15 @@
       <c r="W36" s="21"/>
       <c r="X36" s="22"/>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>264</v>
       </c>
@@ -19463,7 +19463,7 @@
         <v>46269</v>
       </c>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>7</v>
       </c>
@@ -19513,7 +19513,7 @@
       </c>
       <c r="X40" s="48"/>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>10</v>
       </c>
@@ -19563,7 +19563,7 @@
       </c>
       <c r="X41" s="22"/>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>15</v>
       </c>
@@ -19611,7 +19611,7 @@
       </c>
       <c r="X42" s="46"/>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>21</v>
       </c>
@@ -19659,7 +19659,7 @@
       </c>
       <c r="X43" s="72"/>
     </row>
-    <row r="44" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="44" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>24</v>
       </c>
@@ -19707,7 +19707,7 @@
       </c>
       <c r="X44" s="28"/>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
         <v>26</v>
       </c>
@@ -19755,7 +19755,7 @@
       </c>
       <c r="X45" s="46"/>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>28</v>
       </c>
@@ -19805,7 +19805,7 @@
       </c>
       <c r="X46" s="40"/>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>32</v>
       </c>
@@ -19853,7 +19853,7 @@
       </c>
       <c r="X47" s="46"/>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>35</v>
       </c>
@@ -19901,7 +19901,7 @@
       </c>
       <c r="X48" s="40"/>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>37</v>
       </c>
@@ -19949,7 +19949,7 @@
       </c>
       <c r="X49" s="56"/>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>40</v>
       </c>
@@ -19997,7 +19997,7 @@
       </c>
       <c r="X50" s="36"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>45</v>
       </c>
@@ -20045,7 +20045,7 @@
       </c>
       <c r="X51" s="70"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>48</v>
       </c>
@@ -20093,7 +20093,7 @@
       </c>
       <c r="X52" s="72"/>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>49</v>
       </c>
@@ -20141,7 +20141,7 @@
       </c>
       <c r="X53" s="56"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>50</v>
       </c>
@@ -20187,7 +20187,7 @@
       </c>
       <c r="X54" s="56"/>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="5"/>
       <c r="B55" s="9"/>
       <c r="C55" s="9"/>
@@ -20223,7 +20223,7 @@
       </c>
       <c r="X55" s="70"/>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="5"/>
       <c r="B56" s="9"/>
       <c r="C56" s="9"/>
@@ -20251,7 +20251,7 @@
       <c r="W56" s="21"/>
       <c r="X56" s="22"/>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="5"/>
       <c r="B57" s="9"/>
       <c r="C57" s="9"/>
@@ -20274,7 +20274,7 @@
       <c r="W57" s="9"/>
       <c r="X57" s="9"/>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
         <v>1</v>
       </c>
@@ -20288,7 +20288,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <v>2</v>
       </c>
@@ -20302,7 +20302,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="8">
         <v>3</v>
       </c>
@@ -20316,7 +20316,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <v>4</v>
       </c>
@@ -20324,22 +20324,22 @@
         <v>85</v>
       </c>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
     </row>
-    <row r="63" spans="1:24">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
     </row>
-    <row r="64" spans="1:24">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
     </row>
-    <row r="65" spans="1:1">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A65" s="8"/>
     </row>
   </sheetData>
@@ -20834,7 +20834,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X67"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -20864,7 +20864,7 @@
     <col min="26" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>271</v>
       </c>
@@ -20932,7 +20932,7 @@
         <v>46297</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -20980,7 +20980,7 @@
       </c>
       <c r="X2" s="38"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -21028,7 +21028,7 @@
       </c>
       <c r="X3" s="22"/>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -21076,7 +21076,7 @@
       </c>
       <c r="X4" s="36"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -21124,7 +21124,7 @@
       </c>
       <c r="X5" s="36"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -21172,7 +21172,7 @@
       </c>
       <c r="X6" s="28"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -21220,7 +21220,7 @@
       </c>
       <c r="X7" s="30"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -21268,7 +21268,7 @@
       </c>
       <c r="X8" s="22"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -21316,7 +21316,7 @@
       </c>
       <c r="X9" s="44"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -21364,7 +21364,7 @@
       </c>
       <c r="X10" s="28"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -21412,7 +21412,7 @@
       </c>
       <c r="X11" s="22"/>
     </row>
-    <row r="12" spans="1:24" ht="11.25" customHeight="1">
+    <row r="12" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -21460,7 +21460,7 @@
       </c>
       <c r="X12" s="28"/>
     </row>
-    <row r="13" spans="1:24" ht="11.25" customHeight="1">
+    <row r="13" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -21508,7 +21508,7 @@
       </c>
       <c r="X13" s="36"/>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -21556,7 +21556,7 @@
       </c>
       <c r="X14" s="44"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -21604,7 +21604,7 @@
       </c>
       <c r="X15" s="22"/>
     </row>
-    <row r="16" spans="1:24" ht="11.25" customHeight="1">
+    <row r="16" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -21652,7 +21652,7 @@
       </c>
       <c r="X16" s="22"/>
     </row>
-    <row r="17" spans="1:24" ht="11.25" customHeight="1">
+    <row r="17" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -21673,7 +21673,7 @@
       </c>
       <c r="T17" s="40"/>
     </row>
-    <row r="18" spans="1:24" ht="11.25" customHeight="1">
+    <row r="18" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -21690,7 +21690,7 @@
       </c>
       <c r="T18" s="40"/>
     </row>
-    <row r="19" spans="1:24" ht="11.25" customHeight="1">
+    <row r="19" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -21707,7 +21707,7 @@
       </c>
       <c r="T19" s="46"/>
     </row>
-    <row r="20" spans="1:24" ht="11.25" customHeight="1">
+    <row r="20" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -21720,7 +21720,7 @@
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
     </row>
-    <row r="21" spans="1:24" ht="11.25" customHeight="1">
+    <row r="21" spans="1:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -21733,7 +21733,7 @@
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>295</v>
       </c>
@@ -21801,7 +21801,7 @@
         <v>46304</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>7</v>
       </c>
@@ -21849,7 +21849,7 @@
       </c>
       <c r="X23" s="38"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>10</v>
       </c>
@@ -21897,7 +21897,7 @@
       </c>
       <c r="X24" s="22"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>15</v>
       </c>
@@ -21945,7 +21945,7 @@
       </c>
       <c r="X25" s="30"/>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>21</v>
       </c>
@@ -21993,7 +21993,7 @@
       </c>
       <c r="X26" s="36"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>24</v>
       </c>
@@ -22041,7 +22041,7 @@
       </c>
       <c r="X27" s="28"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>26</v>
       </c>
@@ -22089,7 +22089,7 @@
       </c>
       <c r="X28" s="30"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>28</v>
       </c>
@@ -22137,7 +22137,7 @@
       </c>
       <c r="X29" s="28"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>32</v>
       </c>
@@ -22185,7 +22185,7 @@
       </c>
       <c r="X30" s="36"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
         <v>35</v>
       </c>
@@ -22233,7 +22233,7 @@
       </c>
       <c r="X31" s="28"/>
     </row>
-    <row r="32" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="32" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>37</v>
       </c>
@@ -22283,7 +22283,7 @@
       </c>
       <c r="X32" s="95"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>40</v>
       </c>
@@ -22333,7 +22333,7 @@
       </c>
       <c r="X33" s="36"/>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
         <v>45</v>
       </c>
@@ -22383,7 +22383,7 @@
       </c>
       <c r="X34" s="36"/>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>48</v>
       </c>
@@ -22433,7 +22433,7 @@
       </c>
       <c r="X35" s="36"/>
     </row>
-    <row r="36" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="36" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="12" t="s">
         <v>49</v>
       </c>
@@ -22483,7 +22483,7 @@
       </c>
       <c r="X36" s="36"/>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>50</v>
       </c>
@@ -22533,7 +22533,7 @@
       </c>
       <c r="X37" s="95"/>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>51</v>
       </c>
@@ -22570,7 +22570,7 @@
       <c r="W38" s="9"/>
       <c r="X38" s="9"/>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39" s="5"/>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
@@ -22595,7 +22595,7 @@
       <c r="W39" s="9"/>
       <c r="X39" s="9"/>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -22621,7 +22621,7 @@
       <c r="W40" s="4"/>
       <c r="X40" s="4"/>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>310</v>
       </c>
@@ -22691,7 +22691,7 @@
         <v>46311</v>
       </c>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>7</v>
       </c>
@@ -22741,7 +22741,7 @@
       </c>
       <c r="X42" s="38"/>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>10</v>
       </c>
@@ -22791,7 +22791,7 @@
       </c>
       <c r="X43" s="22"/>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>15</v>
       </c>
@@ -22841,7 +22841,7 @@
       </c>
       <c r="X44" s="22"/>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>21</v>
       </c>
@@ -22891,7 +22891,7 @@
       </c>
       <c r="X45" s="46"/>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>24</v>
       </c>
@@ -22939,7 +22939,7 @@
       </c>
       <c r="X46" s="28"/>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>26</v>
       </c>
@@ -22987,7 +22987,7 @@
       </c>
       <c r="X47" s="36"/>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>28</v>
       </c>
@@ -23035,7 +23035,7 @@
       </c>
       <c r="X48" s="30"/>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>32</v>
       </c>
@@ -23083,7 +23083,7 @@
       </c>
       <c r="X49" s="105"/>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
         <v>35</v>
       </c>
@@ -23131,7 +23131,7 @@
       </c>
       <c r="X50" s="30"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>37</v>
       </c>
@@ -23179,7 +23179,7 @@
       </c>
       <c r="X51" s="105"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>40</v>
       </c>
@@ -23227,7 +23227,7 @@
       </c>
       <c r="X52" s="28"/>
     </row>
-    <row r="53" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="53" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>45</v>
       </c>
@@ -23275,7 +23275,7 @@
       </c>
       <c r="X53" s="36"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>48</v>
       </c>
@@ -23323,7 +23323,7 @@
       </c>
       <c r="X54" s="36"/>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
         <v>49</v>
       </c>
@@ -23371,7 +23371,7 @@
       </c>
       <c r="X55" s="46"/>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>50</v>
       </c>
@@ -23419,7 +23419,7 @@
       </c>
       <c r="X56" s="22"/>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>51</v>
       </c>
@@ -23456,7 +23456,7 @@
       </c>
       <c r="T57" s="70"/>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>51</v>
       </c>
@@ -23481,10 +23481,10 @@
       </c>
       <c r="T58" s="36"/>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="7"/>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="5">
         <v>1</v>
       </c>
@@ -23498,7 +23498,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <v>2</v>
       </c>
@@ -23512,7 +23512,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A62" s="8">
         <v>3</v>
       </c>
@@ -23527,7 +23527,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="63" spans="1:24">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A63" s="5">
         <v>4</v>
       </c>
@@ -23535,13 +23535,13 @@
         <v>85</v>
       </c>
     </row>
-    <row r="64" spans="1:24">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
       <c r="D64" s="5"/>
     </row>
-    <row r="65" spans="14:24" s="4" customFormat="1">
+    <row r="65" spans="14:24" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="N65" s="5"/>
       <c r="O65" s="5"/>
       <c r="P65" s="5"/>
@@ -23554,7 +23554,7 @@
       <c r="W65" s="5"/>
       <c r="X65" s="5"/>
     </row>
-    <row r="66" spans="14:24" s="4" customFormat="1">
+    <row r="66" spans="14:24" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="N66" s="5"/>
       <c r="O66" s="5"/>
       <c r="P66" s="5"/>
@@ -23567,7 +23567,7 @@
       <c r="W66" s="5"/>
       <c r="X66" s="5"/>
     </row>
-    <row r="67" spans="14:24" s="4" customFormat="1">
+    <row r="67" spans="14:24" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="N67" s="5"/>
       <c r="O67" s="5"/>
       <c r="P67" s="5"/>
@@ -24075,7 +24075,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X61"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="4" customWidth="1"/>
@@ -24105,7 +24105,7 @@
     <col min="26" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>328</v>
       </c>
@@ -24173,7 +24173,7 @@
         <v>46339</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -24221,7 +24221,7 @@
       </c>
       <c r="X2" s="38"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -24269,7 +24269,7 @@
       </c>
       <c r="X3" s="30"/>
     </row>
-    <row r="4" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="4" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -24317,7 +24317,7 @@
       </c>
       <c r="X4" s="44"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -24365,7 +24365,7 @@
       </c>
       <c r="X5" s="36"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -24413,7 +24413,7 @@
       </c>
       <c r="X6" s="28"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -24461,7 +24461,7 @@
       </c>
       <c r="X7" s="22"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
@@ -24511,7 +24511,7 @@
       </c>
       <c r="X8" s="36"/>
     </row>
-    <row r="9" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="9" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -24561,7 +24561,7 @@
       </c>
       <c r="X9" s="44"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -24611,7 +24611,7 @@
       </c>
       <c r="X10" s="28"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -24659,7 +24659,7 @@
       </c>
       <c r="X11" s="22"/>
     </row>
-    <row r="12" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="12" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -24707,7 +24707,7 @@
       </c>
       <c r="X12" s="28"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -24755,7 +24755,7 @@
       </c>
       <c r="X13" s="113"/>
     </row>
-    <row r="14" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="14" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -24803,7 +24803,7 @@
       </c>
       <c r="X14" s="36"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -24851,7 +24851,7 @@
       </c>
       <c r="X15" s="22"/>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="X16" s="22"/>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -24929,7 +24929,7 @@
       <c r="W17" s="21"/>
       <c r="X17" s="22"/>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -24953,7 +24953,7 @@
       <c r="W18" s="7"/>
       <c r="X18" s="7"/>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>347</v>
       </c>
@@ -25021,7 +25021,7 @@
         <v>46346</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="20" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>7</v>
       </c>
@@ -25069,7 +25069,7 @@
       </c>
       <c r="X20" s="38"/>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -25117,7 +25117,7 @@
       </c>
       <c r="X21" s="113"/>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>15</v>
       </c>
@@ -25165,7 +25165,7 @@
       </c>
       <c r="X22" s="44"/>
     </row>
-    <row r="23" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="23" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -25213,7 +25213,7 @@
       </c>
       <c r="X23" s="44"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>24</v>
       </c>
@@ -25261,7 +25261,7 @@
       </c>
       <c r="X24" s="28"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>26</v>
       </c>
@@ -25309,7 +25309,7 @@
       </c>
       <c r="X25" s="40"/>
     </row>
-    <row r="26" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="26" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>28</v>
       </c>
@@ -25359,7 +25359,7 @@
       </c>
       <c r="X26" s="109"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>32</v>
       </c>
@@ -25409,7 +25409,7 @@
       </c>
       <c r="X27" s="36"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>35</v>
       </c>
@@ -25459,7 +25459,7 @@
       </c>
       <c r="X28" s="28"/>
     </row>
-    <row r="29" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="29" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>37</v>
       </c>
@@ -25509,7 +25509,7 @@
       </c>
       <c r="X29" s="40"/>
     </row>
-    <row r="30" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="30" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>40</v>
       </c>
@@ -25559,7 +25559,7 @@
       </c>
       <c r="X30" s="42"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
         <v>45</v>
       </c>
@@ -25609,7 +25609,7 @@
       </c>
       <c r="X31" s="36"/>
     </row>
-    <row r="32" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="32" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>48</v>
       </c>
@@ -25659,7 +25659,7 @@
       </c>
       <c r="X32" s="40"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>49</v>
       </c>
@@ -25709,7 +25709,7 @@
       </c>
       <c r="X33" s="36"/>
     </row>
-    <row r="34" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="34" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>50</v>
       </c>
@@ -25759,7 +25759,7 @@
       </c>
       <c r="X34" s="109"/>
     </row>
-    <row r="35" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="35" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>345</v>
       </c>
@@ -25797,7 +25797,7 @@
       </c>
       <c r="X35" s="40"/>
     </row>
-    <row r="36" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="36" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
@@ -25820,7 +25820,7 @@
       <c r="W36" s="9"/>
       <c r="X36" s="9"/>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -25835,7 +25835,7 @@
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>357</v>
       </c>
@@ -25905,7 +25905,7 @@
         <v>46353</v>
       </c>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>7</v>
       </c>
@@ -25955,7 +25955,7 @@
       </c>
       <c r="X39" s="38"/>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>10</v>
       </c>
@@ -26005,7 +26005,7 @@
       </c>
       <c r="X40" s="22"/>
     </row>
-    <row r="41" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="41" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>15</v>
       </c>
@@ -26053,7 +26053,7 @@
       </c>
       <c r="X41" s="40"/>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>21</v>
       </c>
@@ -26101,7 +26101,7 @@
       </c>
       <c r="X42" s="40"/>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>24</v>
       </c>
@@ -26149,7 +26149,7 @@
       </c>
       <c r="X43" s="28"/>
     </row>
-    <row r="44" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="44" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
         <v>26</v>
       </c>
@@ -26197,7 +26197,7 @@
       </c>
       <c r="X44" s="44"/>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
         <v>28</v>
       </c>
@@ -26245,7 +26245,7 @@
       </c>
       <c r="X45" s="44"/>
     </row>
-    <row r="46" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="46" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>32</v>
       </c>
@@ -26293,7 +26293,7 @@
       </c>
       <c r="X46" s="40"/>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>35</v>
       </c>
@@ -26343,7 +26343,7 @@
       </c>
       <c r="X47" s="28"/>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>37</v>
       </c>
@@ -26393,7 +26393,7 @@
       </c>
       <c r="X48" s="36"/>
     </row>
-    <row r="49" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="49" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>40</v>
       </c>
@@ -26443,7 +26443,7 @@
       </c>
       <c r="X49" s="28"/>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
         <v>45</v>
       </c>
@@ -26493,7 +26493,7 @@
       </c>
       <c r="X50" s="36"/>
     </row>
-    <row r="51" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="51" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>48</v>
       </c>
@@ -26541,7 +26541,7 @@
       </c>
       <c r="X51" s="72"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>49</v>
       </c>
@@ -26589,7 +26589,7 @@
       </c>
       <c r="X52" s="72"/>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>50</v>
       </c>
@@ -26637,7 +26637,7 @@
       </c>
       <c r="X53" s="44"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="20" t="s">
         <v>345</v>
       </c>
@@ -26673,7 +26673,7 @@
       <c r="W54" s="21"/>
       <c r="X54" s="22"/>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="5">
         <v>1</v>
       </c>
@@ -26687,7 +26687,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="5">
         <v>2</v>
       </c>
@@ -26701,7 +26701,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="8">
         <v>3</v>
       </c>
@@ -26716,7 +26716,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <v>4</v>
       </c>
@@ -26724,12 +26724,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -27229,7 +27229,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="B1:Y61"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1" style="5" customWidth="1"/>
     <col min="2" max="2" width="9" style="4" bestFit="1" customWidth="1"/>
@@ -27258,8 +27258,8 @@
     <col min="26" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:25" ht="6.75" customHeight="1"/>
-    <row r="2" spans="2:25">
+    <row r="1" spans="2:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>364</v>
       </c>
@@ -27327,7 +27327,7 @@
         <v>46381</v>
       </c>
     </row>
-    <row r="3" spans="2:25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B3" s="17" t="s">
         <v>7</v>
       </c>
@@ -27373,7 +27373,7 @@
       <c r="X3" s="33"/>
       <c r="Y3" s="34"/>
     </row>
-    <row r="4" spans="2:25">
+    <row r="4" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B4" s="17" t="s">
         <v>10</v>
       </c>
@@ -27409,7 +27409,7 @@
       <c r="X4" s="33"/>
       <c r="Y4" s="34"/>
     </row>
-    <row r="5" spans="2:25">
+    <row r="5" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B5" s="17" t="s">
         <v>15</v>
       </c>
@@ -27447,7 +27447,7 @@
       <c r="X5" s="33"/>
       <c r="Y5" s="34"/>
     </row>
-    <row r="6" spans="2:25">
+    <row r="6" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B6" s="17" t="s">
         <v>21</v>
       </c>
@@ -27491,7 +27491,7 @@
       <c r="X6" s="33"/>
       <c r="Y6" s="34"/>
     </row>
-    <row r="7" spans="2:25">
+    <row r="7" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B7" s="17" t="s">
         <v>24</v>
       </c>
@@ -27537,7 +27537,7 @@
       <c r="X7" s="33"/>
       <c r="Y7" s="34"/>
     </row>
-    <row r="8" spans="2:25">
+    <row r="8" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B8" s="18" t="s">
         <v>26</v>
       </c>
@@ -27549,14 +27549,10 @@
         <v>366</v>
       </c>
       <c r="F8" s="36"/>
-      <c r="G8" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="44"/>
-      <c r="I8" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8" s="44"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="22"/>
       <c r="K8" s="39" t="s">
         <v>31</v>
       </c>
@@ -27575,7 +27571,7 @@
       <c r="X8" s="33"/>
       <c r="Y8" s="34"/>
     </row>
-    <row r="9" spans="2:25">
+    <row r="9" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B9" s="18" t="s">
         <v>28</v>
       </c>
@@ -27587,14 +27583,10 @@
         <v>367</v>
       </c>
       <c r="F9" s="36"/>
-      <c r="G9" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="44"/>
-      <c r="I9" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" s="44"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="22"/>
       <c r="K9" s="35" t="s">
         <v>368</v>
       </c>
@@ -27613,7 +27605,7 @@
       <c r="X9" s="33"/>
       <c r="Y9" s="34"/>
     </row>
-    <row r="10" spans="2:25">
+    <row r="10" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B10" s="18" t="s">
         <v>32</v>
       </c>
@@ -27651,7 +27643,7 @@
       <c r="X10" s="33"/>
       <c r="Y10" s="34"/>
     </row>
-    <row r="11" spans="2:25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B11" s="18" t="s">
         <v>35</v>
       </c>
@@ -27689,7 +27681,7 @@
       <c r="X11" s="33"/>
       <c r="Y11" s="34"/>
     </row>
-    <row r="12" spans="2:25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B12" s="17" t="s">
         <v>37</v>
       </c>
@@ -27735,7 +27727,7 @@
       <c r="X12" s="33"/>
       <c r="Y12" s="34"/>
     </row>
-    <row r="13" spans="2:25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B13" s="17" t="s">
         <v>40</v>
       </c>
@@ -27781,7 +27773,7 @@
       <c r="X13" s="33"/>
       <c r="Y13" s="34"/>
     </row>
-    <row r="14" spans="2:25">
+    <row r="14" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B14" s="19" t="s">
         <v>45</v>
       </c>
@@ -27819,7 +27811,7 @@
       <c r="X14" s="33"/>
       <c r="Y14" s="34"/>
     </row>
-    <row r="15" spans="2:25">
+    <row r="15" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B15" s="17" t="s">
         <v>48</v>
       </c>
@@ -27865,7 +27857,7 @@
       <c r="X15" s="33"/>
       <c r="Y15" s="34"/>
     </row>
-    <row r="16" spans="2:25">
+    <row r="16" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B16" s="19" t="s">
         <v>49</v>
       </c>
@@ -27893,7 +27885,7 @@
       <c r="X16" s="33"/>
       <c r="Y16" s="34"/>
     </row>
-    <row r="17" spans="2:25">
+    <row r="17" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B17" s="17" t="s">
         <v>50</v>
       </c>
@@ -27921,7 +27913,7 @@
       <c r="X17" s="33"/>
       <c r="Y17" s="34"/>
     </row>
-    <row r="18" spans="2:25">
+    <row r="18" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B18" s="5"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
@@ -27944,7 +27936,7 @@
       <c r="X18" s="9"/>
       <c r="Y18" s="9"/>
     </row>
-    <row r="19" spans="2:25">
+    <row r="19" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
@@ -27956,7 +27948,7 @@
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
     </row>
-    <row r="20" spans="2:25">
+    <row r="20" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
         <v>370</v>
       </c>
@@ -28024,7 +28016,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="21" spans="2:25">
+    <row r="21" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
@@ -28041,7 +28033,7 @@
       </c>
       <c r="H21" s="38"/>
       <c r="I21" s="27" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J21" s="28"/>
       <c r="K21" s="37" t="s">
@@ -28070,7 +28062,7 @@
       <c r="X21" s="33"/>
       <c r="Y21" s="34"/>
     </row>
-    <row r="22" spans="2:25">
+    <row r="22" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
         <v>10</v>
       </c>
@@ -28081,7 +28073,7 @@
       <c r="G22" s="21"/>
       <c r="H22" s="22"/>
       <c r="I22" s="27" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J22" s="28"/>
       <c r="K22" s="21"/>
@@ -28100,7 +28092,7 @@
       <c r="X22" s="33"/>
       <c r="Y22" s="34"/>
     </row>
-    <row r="23" spans="2:25">
+    <row r="23" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
         <v>15</v>
       </c>
@@ -28132,7 +28124,7 @@
       <c r="X23" s="33"/>
       <c r="Y23" s="34"/>
     </row>
-    <row r="24" spans="2:25">
+    <row r="24" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="s">
         <v>21</v>
       </c>
@@ -28168,7 +28160,7 @@
       <c r="X24" s="33"/>
       <c r="Y24" s="34"/>
     </row>
-    <row r="25" spans="2:25">
+    <row r="25" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="s">
         <v>24</v>
       </c>
@@ -28185,7 +28177,7 @@
       </c>
       <c r="H25" s="28"/>
       <c r="I25" s="27" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J25" s="28"/>
       <c r="K25" s="27" t="s">
@@ -28214,7 +28206,7 @@
       <c r="X25" s="33"/>
       <c r="Y25" s="34"/>
     </row>
-    <row r="26" spans="2:25">
+    <row r="26" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B26" s="6" t="s">
         <v>26</v>
       </c>
@@ -28225,7 +28217,7 @@
       <c r="G26" s="23"/>
       <c r="H26" s="24"/>
       <c r="I26" s="27" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J26" s="28"/>
       <c r="K26" s="21"/>
@@ -28244,7 +28236,7 @@
       <c r="X26" s="33"/>
       <c r="Y26" s="34"/>
     </row>
-    <row r="27" spans="2:25">
+    <row r="27" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B27" s="6" t="s">
         <v>28</v>
       </c>
@@ -28274,7 +28266,7 @@
       <c r="X27" s="33"/>
       <c r="Y27" s="34"/>
     </row>
-    <row r="28" spans="2:25">
+    <row r="28" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B28" s="6" t="s">
         <v>32</v>
       </c>
@@ -28308,7 +28300,7 @@
       <c r="X28" s="33"/>
       <c r="Y28" s="34"/>
     </row>
-    <row r="29" spans="2:25">
+    <row r="29" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B29" s="6" t="s">
         <v>35</v>
       </c>
@@ -28319,7 +28311,7 @@
       <c r="G29" s="25"/>
       <c r="H29" s="26"/>
       <c r="I29" s="27" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J29" s="28"/>
       <c r="K29" s="21"/>
@@ -28338,7 +28330,7 @@
       <c r="X29" s="33"/>
       <c r="Y29" s="34"/>
     </row>
-    <row r="30" spans="2:25">
+    <row r="30" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
         <v>37</v>
       </c>
@@ -28372,7 +28364,7 @@
       <c r="X30" s="33"/>
       <c r="Y30" s="34"/>
     </row>
-    <row r="31" spans="2:25">
+    <row r="31" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B31" s="1" t="s">
         <v>40</v>
       </c>
@@ -28383,7 +28375,7 @@
       <c r="G31" s="21"/>
       <c r="H31" s="22"/>
       <c r="I31" s="27" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J31" s="28"/>
       <c r="K31" s="21"/>
@@ -28412,7 +28404,7 @@
       <c r="X31" s="33"/>
       <c r="Y31" s="34"/>
     </row>
-    <row r="32" spans="2:25">
+    <row r="32" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B32" s="12" t="s">
         <v>45</v>
       </c>
@@ -28420,10 +28412,14 @@
       <c r="D32" s="26"/>
       <c r="E32" s="25"/>
       <c r="F32" s="26"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="21"/>
-      <c r="J32" s="22"/>
+      <c r="G32" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="H32" s="44"/>
+      <c r="I32" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="J32" s="44"/>
       <c r="K32" s="21"/>
       <c r="L32" s="22"/>
       <c r="M32" s="7"/>
@@ -28442,7 +28438,7 @@
       <c r="X32" s="33"/>
       <c r="Y32" s="34"/>
     </row>
-    <row r="33" spans="2:25">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B33" s="1" t="s">
         <v>48</v>
       </c>
@@ -28450,10 +28446,14 @@
       <c r="D33" s="22"/>
       <c r="E33" s="21"/>
       <c r="F33" s="22"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="22"/>
+      <c r="G33" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" s="44"/>
+      <c r="I33" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="J33" s="44"/>
       <c r="K33" s="21"/>
       <c r="L33" s="22"/>
       <c r="M33" s="7"/>
@@ -28472,7 +28472,7 @@
       <c r="X33" s="33"/>
       <c r="Y33" s="34"/>
     </row>
-    <row r="34" spans="2:25">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B34" s="12" t="s">
         <v>49</v>
       </c>
@@ -28502,7 +28502,7 @@
       <c r="X34" s="33"/>
       <c r="Y34" s="34"/>
     </row>
-    <row r="35" spans="2:25">
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B35" s="1" t="s">
         <v>50</v>
       </c>
@@ -28532,7 +28532,7 @@
       <c r="X35" s="33"/>
       <c r="Y35" s="34"/>
     </row>
-    <row r="36" spans="2:25">
+    <row r="36" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B36" s="5"/>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
@@ -28557,7 +28557,7 @@
       <c r="X36" s="9"/>
       <c r="Y36" s="9"/>
     </row>
-    <row r="37" spans="2:25">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="5"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
@@ -28582,9 +28582,9 @@
       <c r="X37" s="9"/>
       <c r="Y37" s="9"/>
     </row>
-    <row r="38" spans="2:25">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>1</v>
@@ -28629,7 +28629,7 @@
       <c r="X38" s="9"/>
       <c r="Y38" s="9"/>
     </row>
-    <row r="39" spans="2:25">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
@@ -28666,7 +28666,7 @@
       <c r="X39" s="9"/>
       <c r="Y39" s="9"/>
     </row>
-    <row r="40" spans="2:25">
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B40" s="1" t="s">
         <v>10</v>
       </c>
@@ -28693,28 +28693,28 @@
       <c r="X40" s="9"/>
       <c r="Y40" s="9"/>
     </row>
-    <row r="41" spans="2:25">
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B41" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C41" s="31" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D41" s="32"/>
       <c r="E41" s="31" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F41" s="32"/>
       <c r="G41" s="31" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H41" s="32"/>
       <c r="I41" s="31" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J41" s="32"/>
       <c r="K41" s="31" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="L41" s="32"/>
       <c r="M41" s="7"/>
@@ -28730,7 +28730,7 @@
       <c r="X41" s="9"/>
       <c r="Y41" s="9"/>
     </row>
-    <row r="42" spans="2:25">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B42" s="1" t="s">
         <v>21</v>
       </c>
@@ -28757,7 +28757,7 @@
       <c r="X42" s="9"/>
       <c r="Y42" s="9"/>
     </row>
-    <row r="43" spans="2:25">
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
         <v>24</v>
       </c>
@@ -28794,7 +28794,7 @@
       <c r="X43" s="9"/>
       <c r="Y43" s="9"/>
     </row>
-    <row r="44" spans="2:25">
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B44" s="6" t="s">
         <v>26</v>
       </c>
@@ -28821,7 +28821,7 @@
       <c r="X44" s="9"/>
       <c r="Y44" s="9"/>
     </row>
-    <row r="45" spans="2:25">
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B45" s="6" t="s">
         <v>28</v>
       </c>
@@ -28848,7 +28848,7 @@
       <c r="X45" s="9"/>
       <c r="Y45" s="9"/>
     </row>
-    <row r="46" spans="2:25">
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B46" s="6" t="s">
         <v>32</v>
       </c>
@@ -28885,7 +28885,7 @@
       <c r="X46" s="9"/>
       <c r="Y46" s="9"/>
     </row>
-    <row r="47" spans="2:25">
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B47" s="6" t="s">
         <v>35</v>
       </c>
@@ -28912,7 +28912,7 @@
       <c r="X47" s="9"/>
       <c r="Y47" s="9"/>
     </row>
-    <row r="48" spans="2:25">
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
         <v>37</v>
       </c>
@@ -28939,7 +28939,7 @@
       <c r="X48" s="9"/>
       <c r="Y48" s="9"/>
     </row>
-    <row r="49" spans="2:25">
+    <row r="49" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B49" s="1" t="s">
         <v>40</v>
       </c>
@@ -28966,7 +28966,7 @@
       <c r="X49" s="9"/>
       <c r="Y49" s="9"/>
     </row>
-    <row r="50" spans="2:25">
+    <row r="50" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B50" s="12" t="s">
         <v>45</v>
       </c>
@@ -28997,7 +28997,7 @@
       <c r="X50" s="9"/>
       <c r="Y50" s="9"/>
     </row>
-    <row r="51" spans="2:25">
+    <row r="51" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B51" s="1" t="s">
         <v>48</v>
       </c>
@@ -29024,7 +29024,7 @@
       <c r="X51" s="9"/>
       <c r="Y51" s="9"/>
     </row>
-    <row r="52" spans="2:25">
+    <row r="52" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B52" s="12" t="s">
         <v>49</v>
       </c>
@@ -29051,7 +29051,7 @@
       <c r="X52" s="9"/>
       <c r="Y52" s="9"/>
     </row>
-    <row r="53" spans="2:25">
+    <row r="53" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
         <v>50</v>
       </c>
@@ -29078,7 +29078,7 @@
       <c r="X53" s="9"/>
       <c r="Y53" s="9"/>
     </row>
-    <row r="54" spans="2:25">
+    <row r="54" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B54" s="5"/>
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
@@ -29103,7 +29103,7 @@
       <c r="X54" s="9"/>
       <c r="Y54" s="9"/>
     </row>
-    <row r="55" spans="2:25">
+    <row r="55" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B55" s="5">
         <v>1</v>
       </c>
@@ -29119,7 +29119,7 @@
       <c r="M55" s="7"/>
       <c r="N55" s="7"/>
     </row>
-    <row r="56" spans="2:25">
+    <row r="56" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B56" s="5">
         <v>2</v>
       </c>
@@ -29133,7 +29133,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="57" spans="2:25">
+    <row r="57" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B57" s="8">
         <v>3</v>
       </c>
@@ -29148,7 +29148,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="58" spans="2:25">
+    <row r="58" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B58" s="5">
         <v>4</v>
       </c>
@@ -29162,7 +29162,7 @@
       <c r="M58" s="7"/>
       <c r="N58" s="7"/>
     </row>
-    <row r="59" spans="2:25">
+    <row r="59" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
       <c r="E59" s="5"/>
@@ -29172,7 +29172,7 @@
       <c r="M59" s="7"/>
       <c r="N59" s="7"/>
     </row>
-    <row r="60" spans="2:25">
+    <row r="60" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
       <c r="E60" s="5"/>
@@ -29182,7 +29182,7 @@
       <c r="M60" s="7"/>
       <c r="N60" s="7"/>
     </row>
-    <row r="61" spans="2:25">
+    <row r="61" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
     </row>
@@ -29856,13 +29856,45 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43A824D1-3E40-42BE-9924-6F6DE9E90329}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43A824D1-3E40-42BE-9924-6F6DE9E90329}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="294cf202-ea3b-4503-9866-4c6f0069ff97"/>
+    <ds:schemaRef ds:uri="8aa5bf20-fe4d-4ec9-a1a3-fcd74c59f201"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{179B9B16-67CF-4141-A850-EE327AB51EE2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{179B9B16-67CF-4141-A850-EE327AB51EE2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="8aa5bf20-fe4d-4ec9-a1a3-fcd74c59f201"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="294cf202-ea3b-4503-9866-4c6f0069ff97"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D158BE0-E8D6-40A3-BD3A-A2FAF7031411}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D158BE0-E8D6-40A3-BD3A-A2FAF7031411}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>